--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H193"/>
+  <dimension ref="A1:H194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -483,73 +483,80 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 1</t>
+          <t>Подключение бытовки на строительном объекте</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>7200</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>46154</v>
+        <v>3200</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
-        </is>
-      </c>
+          <t>Источник: первый лист нового прайса, строка 3. Исходное кол-во: 1.0. price_code не найден автоматически: нужно сопоставить вручную.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 1</t>
+          <t>Устройство строительного городка (Строительная бытовка, бытовые и подсобные помещения на период строительства)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
+          <t>мес</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>1</v>
       </c>
       <c r="E3" t="n">
-        <v>1000</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>46154</v>
+        <v>3000</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
-        </is>
-      </c>
+          <t>Источник: первый лист нового прайса, строка 4. Исходное кол-во: 1.0. price_code не найден автоматически: нужно сопоставить вручную.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 1</t>
+          <t>Вынос осей фундамента, котлована на участок</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -557,116 +564,147 @@
           <t>смена</t>
         </is>
       </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
       <c r="E4" t="n">
-        <v>44500</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>46154</v>
+        <v>20000</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Источник: первый лист нового прайса, строка 5. Исходное кол-во: 1.0.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>axis_marking_shift</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 2</t>
+          <t>Вывоз мусора с объекта</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>6500</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>46154</v>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>1</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Источник: первый лист нового прайса, строка 26. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>waste_removal_loading_work_truck</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 2</t>
+          <t>Вывоз мусора с объекта, контейнер/машина</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>1</v>
       </c>
       <c r="E6" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>46154</v>
+        <v>10000</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Перенесено из v3 и уточнено 2026-07-30: контейнер/машина идет в материальной колонке сметы.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>waste_removal_container_truck</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Земляные работы</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 2</t>
+          <t>Материалы для устройства входов коммуникаций</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>38000</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>46154</v>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>communications_material_m</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Земляные работы</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 3</t>
+          <t>Песок строительный</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -674,24 +712,31 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="E8" t="n">
-        <v>6500</v>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1000</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>sand_m3</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Земляные работы</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 3</t>
+          <t>Перемещение песка вручную</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -699,143 +744,180 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>750</v>
-      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>sand_manual_moving_m3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 3</t>
+          <t>Закладка технологических входов коммуникаций до границы дома. Канализация, водоснабжение (ориентировочно)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>40000</v>
+        <v>350</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Источник: первый лист нового прайса, строка 10. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>communications_installation_m</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 4</t>
+          <t>Экскаватор-погрузчик JCB (раскопка "корыта" под устройство дороги) /Контроль за механизированной разработкой грунта</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>6600</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>46154</v>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>3 500</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Источник: первый лист нового прайса, строка 6. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>excavator_jcb_shift</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 4</t>
+          <t>Укладка геотекстиля</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 8 м3</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
       </c>
       <c r="E12" t="n">
-        <v>1100</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>46154</v>
+        <v>35</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Источник: первый лист нового прайса, строка 8. Исходное кол-во: 1.0.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>geotextile_laying_m2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 4</t>
+          <t>Разработка грунта вручную (в т.ч. Копка траншей под коммуникации)</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>45000</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>46154</v>
+        <v>1400</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Источник: первый лист нового прайса, строка 7. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>manual_excavation_m3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 5</t>
+          <t>Отсыпка дна котлована песком с трамбованием механизировано с применением виброплиты (коэф.упл. 1,3)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -843,12 +925,25 @@
           <t>м3</t>
         </is>
       </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
       <c r="E14" t="n">
-        <v>6150</v>
+        <v>1200</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Источник: первый лист нового прайса, строка 9. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>sand_filling_work_m3</t>
         </is>
       </c>
     </row>
@@ -860,7 +955,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 5</t>
+          <t>Бетон B22.5 зона 1</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -868,17 +963,15 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
       <c r="E15" t="n">
-        <v>900</v>
+        <v>7200</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -890,20 +983,28 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 5</t>
+          <t>Доставка бетона B22.5 зона 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>39500</v>
+        <v>1000</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -915,20 +1016,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 6</t>
+          <t>Насос 36м + гаситель зона 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6550</v>
+        <v>44500</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -940,7 +1044,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 6</t>
+          <t>Бетон B22.5 зона 2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -948,17 +1052,15 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 8 м3</t>
-        </is>
-      </c>
       <c r="E18" t="n">
-        <v>950</v>
+        <v>6500</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -970,20 +1072,28 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 6</t>
+          <t>Доставка бетона B22.5 зона 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>40500</v>
+        <v>1100</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -995,20 +1105,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 7</t>
+          <t>Насос 36м + гаситель зона 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6550</v>
+        <v>38000</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1133,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 7</t>
+          <t>Бетон B22.5 зона 3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1028,17 +1141,12 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 8 м3</t>
-        </is>
-      </c>
       <c r="E21" t="n">
-        <v>950</v>
+        <v>6500</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1050,20 +1158,25 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 7</t>
+          <t>Доставка бетона B22.5 зона 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>40500</v>
+        <v>750</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1075,20 +1188,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 8</t>
+          <t>Насос 36м + гаситель зона 3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>7690</v>
+        <v>40000</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1100,7 +1213,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 8</t>
+          <t>Бетон B22.5 зона 4</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1108,17 +1221,15 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 6 м3</t>
-        </is>
-      </c>
       <c r="E24" t="n">
-        <v>1400</v>
+        <v>6600</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1130,62 +1241,68 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 8</t>
+          <t>Доставка бетона B22.5 зона 4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 8 м3</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>48000</v>
+        <v>1100</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 1</t>
+          <t>Насос 36м + гаситель зона 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>20 м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1400</v>
+        <v>45000</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 2</t>
+          <t>Бетон B22.5 зона 5</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1193,29 +1310,24 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>20 м3</t>
-        </is>
-      </c>
       <c r="E27" t="n">
-        <v>1300</v>
+        <v>6150</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 3</t>
+          <t>Доставка бетона B22.5 зона 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1225,57 +1337,52 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>20 м3</t>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1300</v>
+        <v>900</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 4</t>
+          <t>Насос 36м + гаситель зона 5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>20 м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1300</v>
+        <v>39500</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 5</t>
+          <t>Бетон B22.5 зона 6</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1283,29 +1390,24 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>20 м3</t>
-        </is>
-      </c>
       <c r="E30" t="n">
-        <v>1300</v>
+        <v>6550</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 6</t>
+          <t>Доставка бетона B22.5 зона 6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1315,57 +1417,52 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>20 м3</t>
+          <t>Минимальный миксер 8 м3</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 7</t>
+          <t>Насос 36м + гаситель зона 6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>20 м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1300</v>
+        <v>40500</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 8</t>
+          <t>Бетон B22.5 зона 7</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1373,29 +1470,24 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>20 м3</t>
-        </is>
-      </c>
       <c r="E33" t="n">
-        <v>1300</v>
+        <v>6550</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона ГФК/ЛПК и т.д./А108</t>
+          <t>Доставка бетона B22.5 зона 7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1405,771 +1497,858 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>20 м3</t>
+          <t>Минимальный миксер 8 м3</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1300</v>
+        <v>950</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Доска обрезная 25х100х6000мм 1-сорт ГОСТ</t>
+          <t>Насос 36м + гаситель зона 7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>265</v>
-      </c>
-      <c r="F35" s="2" t="n">
-        <v>46154</v>
+        <v>40500</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Доска обрезная 25х150х6000мм 1-сорт ГОСТ</t>
+          <t>Бетон B22.5 зона 8</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>397</v>
-      </c>
-      <c r="F36" s="2" t="n">
-        <v>46154</v>
+        <v>7690</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доставка бетона B22.5 зона 8</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 6 м3</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>530</v>
-      </c>
-      <c r="F37" s="2" t="n">
-        <v>46154</v>
+        <v>1400</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х150х6000мм 1-сорт ГОСТ</t>
+          <t>Насос 36м + гаситель зона 8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>795</v>
-      </c>
-      <c r="F38" s="2" t="n">
-        <v>46154</v>
+        <v>48000</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х200х6000мм 1-сорт ГОСТ</t>
+          <t>Песок 20м3 зона 1</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>20 м3</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1093</v>
-      </c>
-      <c r="F39" s="2" t="n">
-        <v>46154</v>
+        <v>1400</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Брус обрезной 100х100х6000мм 1-сорт ГОСТ</t>
+          <t>Песок 20м3 зона 2</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>20 м3</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1093</v>
-      </c>
-      <c r="F40" s="2" t="n">
-        <v>46154</v>
+        <v>1300</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Брус обрезной 100х150х6000мм 1-сорт ГОСТ</t>
+          <t>Песок 20м3 зона 3</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>20 м3</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1590</v>
-      </c>
-      <c r="F41" s="2" t="n">
-        <v>46154</v>
+        <v>1300</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Брус обрезной 150х150х6000мм 1-сорт ГОСТ</t>
+          <t>Песок 20м3 зона 4</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>20 м3</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F42" s="2" t="n">
-        <v>46154</v>
+        <v>1300</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 50х300х6000мм</t>
+          <t>Песок 20м3 зона 5</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>20 м3</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>3800</v>
-      </c>
-      <c r="F43" s="2" t="n">
-        <v>46154</v>
+        <v>1300</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 20х90х6000мм</t>
+          <t>Песок 20м3 зона 6</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>20 м3</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>360</v>
-      </c>
-      <c r="F44" s="2" t="n">
-        <v>46154</v>
+        <v>1300</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 20х140х6000мм</t>
+          <t>Песок 20м3 зона 7</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>20 м3</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>540</v>
-      </c>
-      <c r="F45" s="2" t="n">
-        <v>46154</v>
+        <v>1300</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х90х6000мм</t>
+          <t>Песок 20м3 зона 8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>20 м3</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>682</v>
-      </c>
-      <c r="F46" s="2" t="n">
-        <v>46154</v>
+        <v>1300</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х140х6000мм</t>
+          <t>Песок 20м3 зона ГФК/ЛПК и т.д./А108</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>20 м3</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1022</v>
-      </c>
-      <c r="F47" s="2" t="n">
-        <v>46154</v>
+        <v>1300</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х190х6000мм</t>
+          <t>Бетонирование монолитной плиты перекрытия бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>1</v>
       </c>
       <c r="E48" t="n">
-        <v>1406</v>
-      </c>
-      <c r="F48" s="2" t="n">
-        <v>46154</v>
+        <v>12000</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.0.</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>concrete_placing_work_m3</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 90х90х6000мм</t>
+          <t>Перенос, подъем бетона вручную</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E49" t="n">
-        <v>1406</v>
-      </c>
-      <c r="F49" s="2" t="n">
-        <v>46154</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>1</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.0.</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>manual_concrete_lifting_m3</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 90х140х6000мм</t>
+          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой до 250мм)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>2045</v>
-      </c>
-      <c r="F50" s="2" t="n">
-        <v>46154</v>
+        <v>1500</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>beam_concrete_placing_work_m</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 140х140х6000мм</t>
+          <t>Бетон марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>3214</v>
-      </c>
-      <c r="F51" s="2" t="n">
-        <v>46154</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>6400.000000</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>concrete_b22_5_m3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 140х190х6000мм</t>
+          <t>Доставка бетона до объекта</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E52" t="n">
-        <v>4500</v>
-      </c>
-      <c r="F52" s="2" t="n">
-        <v>46154</v>
+          <t>рейс</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>7500.000000</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>concrete_delivery_trip</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 50х50х3000мм</t>
+          <t>Работа бетононасоса 32м + гаситель</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E53" t="n">
-        <v>200</v>
-      </c>
-      <c r="F53" s="2" t="n">
-        <v>46154</v>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>38000.000000</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>concrete_pump_32m_shift</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 45х45х3000мм</t>
+          <t>Подача опалубки, арматуры автокраном</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E54" t="n">
-        <v>175</v>
-      </c>
-      <c r="F54" s="2" t="n">
-        <v>46154</v>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>30000.000000</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>crane_shift</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 40х50х3000мм</t>
+          <t>Экструдированный пенополистирол Пеноплэкс Основа 100х585х1185 мм</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E55" t="n">
-        <v>175</v>
-      </c>
-      <c r="F55" s="2" t="n">
-        <v>46154</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>9020.000000</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>eps_penoplex_osnova_100_m3</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 25х100х6000мм 1-сорт ГОСТ</t>
+          <t>Расходные материалы для установки опалубки (смазка; звездочки ПВХ, трубки)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E56" t="n">
-        <v>310</v>
-      </c>
-      <c r="F56" s="2" t="n">
-        <v>46154</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>9759.080000</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>formwork_consumables_m2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 25х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доставка, вывоз опалубки манипулятором</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E57" t="n">
-        <v>465</v>
-      </c>
-      <c r="F57" s="2" t="n">
-        <v>46154</v>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>20000.000000</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>formwork_delivery_truck</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 50х100х6000мм 1-сорт ГОСТ</t>
+          <t>Комплект опалубки (телескопические стойки, унивилки, треноги, водостойкая фанера, поперечные и продольные балки двутавровые)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E58" t="n">
-        <v>621</v>
-      </c>
-      <c r="F58" s="2" t="n">
-        <v>46154</v>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>600.000000</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>formwork_rental_m2</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием  50х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доставка арматуры, металла</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E59" t="n">
-        <v>931</v>
-      </c>
-      <c r="F59" s="2" t="n">
-        <v>46154</v>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>22000.000000</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>metal_delivery_truck</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 50х200х6000мм 1-сорт ГОСТ</t>
+          <t>Технический надзор</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E60" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F60" s="2" t="n">
-        <v>46154</v>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>5000.000000</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>technical_supervision_fixed</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 100х100х6000мм 1-сорт ГОСТ</t>
+          <t>Пиломатериал обрезной для устройства опалубки ГОСТ</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E61" t="n">
-        <v>1281</v>
-      </c>
-      <c r="F61" s="2" t="n">
-        <v>46154</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>21499.997319</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>timber_m3</t>
         </is>
       </c>
     </row>
@@ -2181,7 +2360,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 100х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 25х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2190,7 +2369,7 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1863</v>
+        <v>265</v>
       </c>
       <c r="F62" s="2" t="n">
         <v>46154</v>
@@ -2209,7 +2388,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 150х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 25х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2218,7 +2397,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>2928</v>
+        <v>397</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>46154</v>
@@ -2237,7 +2416,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 50х300х6000мм</t>
+          <t>Доска обрезная 50х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2246,7 +2425,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4200</v>
+        <v>530</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>46154</v>
@@ -2265,7 +2444,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 20х90х6000мм</t>
+          <t>Доска обрезная 50х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2274,7 +2453,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>420</v>
+        <v>795</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>46154</v>
@@ -2293,7 +2472,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 20х140х6000мм</t>
+          <t>Доска обрезная 50х200х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2302,7 +2481,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>620</v>
+        <v>1093</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>46154</v>
@@ -2321,7 +2500,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х90х6000мм</t>
+          <t>Брус обрезной 100х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2330,7 +2509,7 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>772</v>
+        <v>1093</v>
       </c>
       <c r="F67" s="2" t="n">
         <v>46154</v>
@@ -2349,7 +2528,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х140х6000мм</t>
+          <t>Брус обрезной 100х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2358,7 +2537,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1159</v>
+        <v>1590</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>46154</v>
@@ -2377,7 +2556,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х190х6000мм</t>
+          <t>Брус обрезной 150х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2386,7 +2565,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1593</v>
+        <v>2500</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>46154</v>
@@ -2405,7 +2584,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 90х90х6000мм</t>
+          <t>Доска сухая строганная 50х300х6000мм</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2414,7 +2593,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1593</v>
+        <v>3800</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>46154</v>
@@ -2433,7 +2612,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 90х140х6000мм</t>
+          <t>Доска сухая строганная 20х90х6000мм</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2442,7 +2621,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2318</v>
+        <v>360</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>46154</v>
@@ -2461,7 +2640,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 140х140х6000мм</t>
+          <t>Доска сухая строганная 20х140х6000мм</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2470,7 +2649,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>3642</v>
+        <v>540</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>46154</v>
@@ -2489,7 +2668,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 140х190х6000мм</t>
+          <t>Доска сухая строганная 45х90х6000мм</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2498,7 +2677,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5100</v>
+        <v>682</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>46154</v>
@@ -2517,7 +2696,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 50х50х3000мм</t>
+          <t>Доска сухая строганная 45х140х6000мм</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2526,7 +2705,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>270</v>
+        <v>1022</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>46154</v>
@@ -2545,7 +2724,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 45х45х3000мм</t>
+          <t>Доска сухая строганная 45х190х6000мм</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2554,7 +2733,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220</v>
+        <v>1406</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>46154</v>
@@ -2573,7 +2752,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 40х50х3000мм</t>
+          <t>Брус сухой строганный 90х90х6000мм</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2582,7 +2761,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220</v>
+        <v>1406</v>
       </c>
       <c r="F76" s="2" t="n">
         <v>46154</v>
@@ -2596,237 +2775,208 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Блок D 400</t>
+          <t>Брус сухой строганный 90х140х6000мм</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>34,56 м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5900</v>
+        <v>2045</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Блок D 500</t>
+          <t>Брус сухой строганный 140х140х6000мм</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>32,4 м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5200</v>
+        <v>3214</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Блок D 400</t>
+          <t>Брус сухой строганный 140х190х6000мм</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>1,8 м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6300</v>
+        <v>4500</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Блок D 500</t>
+          <t>Брус сухой строганный 50х50х3000мм</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>1,8 м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5800</v>
+        <v>200</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Брус сухой строганный 45х45х3000мм</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E81" t="n">
-        <v>659.77</v>
+        <v>175</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Сетка 5/0.4/100</t>
+          <t>Брус сухой строганный 40х50х3000мм</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>рулон</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E82" t="n">
-        <v>1304.63</v>
+        <v>175</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Сетка 5/0.5/100</t>
+          <t>Доска обрезная с антисептированием 25х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>рулон</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E83" t="n">
-        <v>1729.38</v>
+        <v>310</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>PTH 8</t>
+          <t>Доска обрезная с антисептированием 25х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2834,30 +2984,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D84" t="n">
-        <v>120</v>
-      </c>
       <c r="E84" t="n">
-        <v>100.62</v>
+        <v>465</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>PTH 12</t>
+          <t>Доска обрезная с антисептированием 50х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -2865,30 +3012,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D85" t="n">
-        <v>80</v>
-      </c>
       <c r="E85" t="n">
-        <v>150.62</v>
+        <v>621</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>PTH 20</t>
+          <t>Доска обрезная с антисептированием  50х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -2896,30 +3040,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D86" t="n">
-        <v>72</v>
-      </c>
       <c r="E86" t="n">
-        <v>171.17</v>
+        <v>931</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>PTH 25М</t>
+          <t>Доска обрезная с антисептированием 50х200х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -2927,30 +3068,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D87" t="n">
-        <v>60</v>
-      </c>
       <c r="E87" t="n">
-        <v>180.89</v>
+        <v>1281</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>PTH 38</t>
+          <t>Брус обрезной с антисептированием 100х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -2958,30 +3096,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D88" t="n">
-        <v>60</v>
-      </c>
       <c r="E88" t="n">
-        <v>155.66</v>
+        <v>1281</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>PTH 38 Termo</t>
+          <t>Брус обрезной с антисептированием 100х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -2989,30 +3124,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D89" t="n">
-        <v>60</v>
-      </c>
       <c r="E89" t="n">
-        <v>201.14</v>
+        <v>1863</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PTH 44</t>
+          <t>Брус обрезной с антисептированием 150х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3020,30 +3152,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D90" t="n">
-        <v>50</v>
-      </c>
       <c r="E90" t="n">
-        <v>176.58</v>
+        <v>2928</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>PTH 51</t>
+          <t>Доска сухая строганная с антисептированием 50х300х6000мм</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3051,30 +3180,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D91" t="n">
-        <v>50</v>
-      </c>
       <c r="E91" t="n">
-        <v>225.53</v>
+        <v>4200</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+          <t>Доска сухая строганная с антисептированием 20х90х6000мм</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3082,30 +3208,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D92" t="n">
-        <v>1</v>
-      </c>
       <c r="E92" t="n">
-        <v>268.4</v>
+        <v>420</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+          <t>Доска сухая строганная с антисептированием 20х140х6000мм</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3113,30 +3236,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D93" t="n">
-        <v>1</v>
-      </c>
       <c r="E93" t="n">
-        <v>902.8</v>
+        <v>620</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
+          <t>Доска сухая строганная с антисептированием 45х90х6000мм</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3144,30 +3264,27 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D94" t="n">
-        <v>1</v>
-      </c>
       <c r="E94" t="n">
-        <v>264</v>
+        <v>772</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
+          <t>Доска сухая строганная с антисептированием 45х140х6000мм</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3175,83 +3292,83 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D95" t="n">
-        <v>1</v>
-      </c>
       <c r="E95" t="n">
-        <v>672</v>
+        <v>1159</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Проволока</t>
+          <t>Доска сухая строганная с антисептированием 45х190х6000мм</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E96" t="n">
-        <v>75</v>
+        <v>1593</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
+          <t>Брус сухой строганный с антисептированием 90х90х6000мм</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6610</v>
+        <v>1593</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
+          <t>Брус сухой строганный с антисептированием 90х140х6000мм</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3260,48 +3377,54 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>450</v>
+        <v>2318</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
+          <t>Брус сухой строганный с антисептированием 140х140х6000мм</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>59.55</v>
+        <v>3642</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
+          <t>Брус сухой строганный с антисептированием 140х190х6000мм</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3310,23 +3433,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6001.23</v>
+        <v>5100</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
+          <t>Брус сухой строганный с антисептированием 50х50х3000мм</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3335,23 +3461,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>2060</v>
+        <v>270</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Подключение бытовки на строительном объекте</t>
+          <t>Брус сухой строганный с антисептированием 45х45х3000мм</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3359,452 +3488,432 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D102" t="n">
-        <v>1</v>
-      </c>
       <c r="E102" t="n">
-        <v>3200</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>220</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 3. Исходное кол-во: 1.0. price_code не найден автоматически: нужно сопоставить вручную.</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr"/>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Устройство строительного городка (Строительная бытовка, бытовые и подсобные помещения на период строительства)</t>
+          <t>Брус сухой строганный с антисептированием 40х50х3000мм</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>мес</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E103" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>220</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 4. Исходное кол-во: 1.0. price_code не найден автоматически: нужно сопоставить вручную.</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr"/>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой более 250мм)</t>
+          <t>Фанера 1,52х1,52*18</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E104" t="n">
-        <v>25000</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>1400</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 29. Исходное кол-во: 1.0. price_code не найден автоматически: нужно сопоставить вручную.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr"/>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>plywood_1520x1520_18mm_sheet</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Устройство фундаментной плиты</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Фанера 1,52х1,52*18</t>
+          <t>Демонтаж опалубки после завершения бетонирования</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E105" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F105" s="2" t="n">
-        <v>46154</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>plywood_1520x1520_18mm_sheet</t>
+          <t>formwork_dismantling_work_m2</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Устройство фундаментной плиты</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Монтаж опалубки из пиломатериалов для отбортовки плиты</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>1</v>
-      </c>
-      <c r="E106" t="n">
-        <v>360</v>
-      </c>
-      <c r="F106" s="2" t="n">
-        <v>46146</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>block_adhesive_bag</t>
+          <t>timber_formwork_installation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
+          <t>Устройство утепления низа плиты</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D107" t="n">
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>512.4</v>
-      </c>
-      <c r="F107" s="2" t="n">
-        <v>46146</v>
+        <v>900</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
+          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.0.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_2x_36_25_item</t>
+          <t>eps_bottom_slab_insulation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
+          <t>Утепление торца плиты ЭППС 100мм</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D108" t="n">
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>732</v>
-      </c>
-      <c r="F108" s="2" t="n">
-        <v>46146</v>
+        <v>500</v>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
+          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_3x_52_25_item</t>
+          <t>eps_wall_insulation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 25 мм</t>
+          <t>Устройство и монтаж термовкладыша</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>1п.м</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.7</v>
+        <v>1</v>
       </c>
       <c r="E109" t="n">
-        <v>155.8</v>
-      </c>
-      <c r="F109" s="2" t="n">
-        <v>46214</v>
+        <v>100</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>rebar_a500_d25_m</t>
+          <t>thermal_insert_installation_work_m</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 20мм</t>
+          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>1п.м</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.7</v>
+        <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>100.25</v>
-      </c>
-      <c r="F110" s="2" t="n">
-        <v>46214</v>
+        <v>770</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
+          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>rebar_a500_d20_m</t>
+          <t>roof_eps_insulation_installation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 16 мм</t>
+          <t>Planter Standard Технониколь 40м2-1рул</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.7</v>
+          <t>рул</t>
+        </is>
       </c>
       <c r="E111" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="F111" s="2" t="n">
-        <v>46214</v>
+        <v>4738</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>rebar_a500_d16_m</t>
+          <t>planter_standard_roll</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 12мм</t>
+          <t>PLANTERBAND 10м х 10см-1шт</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.7</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E112" t="n">
-        <v>36.85</v>
-      </c>
-      <c r="F112" s="2" t="n">
-        <v>46214</v>
+        <v>750</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>rebar_a500_d12_m</t>
+          <t>planterband_item</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 10 мм</t>
+          <t>Праймер битумный AquaMast, 18 л-1шт</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.7</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E113" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="F113" s="2" t="n">
-        <v>46214</v>
+        <v>2865</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>rebar_a500_d10_m</t>
+          <t>bitumen_primer_aquamast_18l_item</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 8 мм</t>
+          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.7</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E114" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F114" s="2" t="n">
-        <v>46214</v>
+        <v>2828.21</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>rebar_a240_d8_m</t>
+          <t>bitumen_mastic_aquamast_18kg_item</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 6 мм</t>
+          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.7</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E115" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>46214</v>
+        <v>8800</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>rebar_a240_d6_m</t>
+          <t>eps_geo_50_m3</t>
         </is>
       </c>
     </row>
@@ -3816,16 +3925,16 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Planter Standard Технониколь 40м2-1рул</t>
+          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>рул</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4738</v>
+        <v>8900</v>
       </c>
       <c r="G116" t="inlineStr">
         <is>
@@ -3834,7 +3943,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>planter_standard_roll</t>
+          <t>eps_geo_100_m3</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3955,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>PLANTERBAND 10м х 10см-1шт</t>
+          <t>Клей-пена для ЭППС-1шт</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3855,7 +3964,7 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -3864,7 +3973,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>planterband_item</t>
+          <t>eps_foam_glue_can</t>
         </is>
       </c>
     </row>
@@ -3876,332 +3985,363 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Праймер битумный AquaMast, 18 л-1шт</t>
+          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>2865</v>
+        <v>109</v>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>bitumen_primer_aquamast_18l_item</t>
+          <t>geotextile_dornit_300_m2</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
+          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>2828.21</v>
+        <v>350</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>bitumen_mastic_aquamast_18kg_item</t>
+          <t>bitumen_waterproofing_work_m2</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
+          <t>Монтаж мембраны PLANTER стандарт</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>8800</v>
+        <v>100</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.0.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>eps_geo_50_m3</t>
+          <t>planter_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
+          <t>Проволока</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>8900</v>
+        <v>75</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>eps_geo_100_m3</t>
+          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Клей-пена для ЭППС-1шт</t>
+          <t>Арматура класса А500 диаметром 25 мм</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.7</v>
       </c>
       <c r="E122" t="n">
-        <v>450</v>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>Обновлено 04.05</t>
-        </is>
+        <v>155.8</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>eps_foam_glue_can</t>
+          <t>rebar_a500_d25_m</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
+          <t>Арматура класса А500 диаметром 20мм</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.7</v>
       </c>
       <c r="E123" t="n">
-        <v>109</v>
+        <v>100.25</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
+          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>geotextile_dornit_300_m2</t>
+          <t>rebar_a500_d20_m</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
+          <t>Арматура класса А500 диаметром 16 мм</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.7</v>
       </c>
       <c r="E124" t="n">
-        <v>23.12</v>
+        <v>64.90000000000001</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
+          <t>rebar_a500_d16_m</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
+          <t>Арматура класса А500 диаметром 12мм</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.7</v>
       </c>
       <c r="E125" t="n">
-        <v>7377.89</v>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
+        <v>36.85</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>roof_eps100_technonikol_carbon_eco_m3</t>
+          <t>rebar_a500_d12_m</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
+          <t>Арматура класса А500 диаметром 10 мм</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.7</v>
       </c>
       <c r="E126" t="n">
-        <v>7155.34</v>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
+        <v>27.16</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>roof_eps50_technonikol_carbon_eco_m3</t>
+          <t>rebar_a500_d10_m</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
+          <t>Арматура класса А240 диаметром 8 мм</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.7</v>
       </c>
       <c r="E127" t="n">
-        <v>9888.67</v>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
+        <v>18.5</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_a_m3</t>
+          <t>rebar_a240_d8_m</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
+          <t>Арматура класса А240 диаметром 6 мм</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.7</v>
       </c>
       <c r="E128" t="n">
-        <v>9888.67</v>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
+        <v>10.25</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_b_m3</t>
+          <t>rebar_a240_d6_m</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
+          <t>Блок D 400</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4209,29 +4349,32 @@
           <t>м3</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>34,56 м3</t>
+        </is>
+      </c>
       <c r="E129" t="n">
-        <v>9888.67</v>
+        <v>5900</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H129" t="inlineStr">
-        <is>
-          <t>roof_eps_slope_4_2_plate_j_m3</t>
+          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
+          <t>Блок D 500</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4239,98 +4382,113 @@
           <t>м3</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>32,4 м3</t>
+        </is>
+      </c>
       <c r="E130" t="n">
-        <v>9888.67</v>
+        <v>5200</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>roof_eps_slope_4_2_plate_k_m3</t>
+          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
+          <t>Блок D 400</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>1,8 м3</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>57.56</v>
+        <v>6300</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H131" t="inlineStr">
-        <is>
-          <t>roof_geotextile_technonikol_prof_150_m2</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Рейка прижимная, 2 м</t>
+          <t>Блок D 500</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>пог. м</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1,8 м3</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>90</v>
+        <v>5800</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>roof_aluminum_pressure_rail_m</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Рейка краевая, 2 м</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>пог. м</t>
-        </is>
+          <t>мешок 25 кг</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>95</v>
+        <v>360</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
@@ -4339,112 +4497,115 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>roof_aluminum_edge_rail_m</t>
+          <t>block_adhesive_bag</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
+          <t>Доставка блоков, смеси</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="E134" t="n">
-        <v>1146.91</v>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>28000</t>
+        </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
+          <t>block_delivery_truck</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Аэратор кровельный PVC, А75х375</t>
+          <t>Разгрузка блоков, смеси манипулятором</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E135" t="n">
-        <v>587</v>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>roof_pvc_aerator_75x375_item</t>
+          <t>block_unloading_manipulator_truck</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Вынос осей фундамента, котлована на участок</t>
+          <t>Газобетонный блок D400 600x400x250 мм</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>1</v>
-      </c>
-      <c r="E136" t="n">
-        <v>20000</v>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>6000</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 5. Исходное кол-во: 1.0.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>axis_marking_shift</t>
+          <t>gas_block_d400_m3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Бетонирование балки бетоном марки В22,5 (М300)</t>
+          <t>Газобетонный блок D500 600x150x250 мм</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4454,7 +4615,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>20000.000000</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
@@ -4464,45 +4625,39 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>beam_concrete_placing_work_m3</t>
+          <t>gas_block_d500_150_m3</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
+          <t>Газобетонный блок D500 600x250x250 мм</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>1</v>
-      </c>
-      <c r="E138" t="n">
-        <v>350</v>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>5500</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>bitumen_waterproofing_work_m2</t>
+          <t>gas_block_d500_m3</t>
         </is>
       </c>
     </row>
@@ -4514,17 +4669,17 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Доставка блоков, смеси</t>
+          <t>Пескобетон М300 40 кг</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>28000</t>
+          <t>375</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -4534,389 +4689,348 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>block_delivery_truck</t>
+          <t>sand_concrete_bag</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Разгрузка блоков, смеси манипулятором</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
+          <t>мешок 25 кг</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+      <c r="E140" t="n">
+        <v>659.77</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>block_unloading_manipulator_truck</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Закладка технологических входов коммуникаций до границы дома. Канализация, водоснабжение (ориентировочно)</t>
+          <t>Сетка 5/0.4/100</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>рулон</t>
         </is>
       </c>
       <c r="D141" t="n">
         <v>1</v>
       </c>
       <c r="E141" t="n">
-        <v>350</v>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>1304.63</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 10. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>communications_installation_m</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Земляные работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Материалы для устройства входов коммуникаций</t>
+          <t>Сетка 5/0.5/100</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>650</t>
-        </is>
+          <t>рулон</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>1</v>
+      </c>
+      <c r="E142" t="n">
+        <v>1729.38</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>communications_material_m</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Бетон марки В22,5 (М300)</t>
+          <t>PTH 8</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>6400.000000</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>120</v>
+      </c>
+      <c r="E143" t="n">
+        <v>100.62</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>concrete_b22_5_m3</t>
+          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Доставка бетона до объекта</t>
+          <t>PTH 12</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>рейс</t>
-        </is>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>7500.000000</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>80</v>
+      </c>
+      <c r="E144" t="n">
+        <v>150.62</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>concrete_delivery_trip</t>
+          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Бетонирование монолитной плиты перекрытия бетоном марки В22,5 (М300)</t>
+          <t>PTH 20</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E145" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>171.17</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>concrete_placing_work_m3</t>
+          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Работа бетононасоса 32м + гаситель</t>
+          <t>PTH 25М</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>38000.000000</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>60</v>
+      </c>
+      <c r="E146" t="n">
+        <v>180.89</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
-      </c>
-      <c r="H146" t="inlineStr">
-        <is>
-          <t>concrete_pump_32m_shift</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Подача опалубки, арматуры автокраном</t>
+          <t>PTH 38</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>30000.000000</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>60</v>
+      </c>
+      <c r="E147" t="n">
+        <v>155.66</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr">
-        <is>
-          <t>crane_shift</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Гидроизоляция поверхности под первый ряд блоков</t>
+          <t>PTH 38 Termo</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E148" t="n">
-        <v>100</v>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>201.14</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>cutoff_waterproofing_under_blocks_m2</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Устройство утепления по наружной стороне торцов плиты, балок</t>
+          <t>PTH 44</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E149" t="n">
-        <v>450</v>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>176.58</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>edge_insulation_work_m</t>
+          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Устройство утепления низа плиты</t>
+          <t>PTH 51</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E150" t="n">
-        <v>900</v>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>225.53</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H150" t="inlineStr">
-        <is>
-          <t>eps_bottom_slab_insulation_work_m2</t>
+          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -4928,7 +5042,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Укладка ЭППС 50мм под плитой</t>
+          <t>Гидроизоляция поверхности под первый ряд блоков</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4940,53 +5054,59 @@
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.0.</t>
+          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.0.</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>eps_laying_work_m2</t>
+          <t>cutoff_waterproofing_under_blocks_m2</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Экструдированный пенополистирол Пеноплэкс Основа 100х585х1185 мм</t>
+          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>9020.000000</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>1</v>
+      </c>
+      <c r="E152" t="n">
+        <v>450</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.0.</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>eps_penoplex_osnova_100_m3</t>
+          <t>edge_insulation_work_m</t>
         </is>
       </c>
     </row>
@@ -4998,7 +5118,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Утепление торца плиты ЭППС 100мм</t>
+          <t>Укладка ЭППС 50мм под плитой</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5010,21 +5130,21 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.0.</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>eps_wall_insulation_work_m2</t>
+          <t>eps_laying_work_m2</t>
         </is>
       </c>
     </row>
@@ -5036,12 +5156,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Экскаватор-погрузчик JCB (раскопка "корыта" под устройство дороги) /Контроль за механизированной разработкой грунта</t>
+          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5049,145 +5169,176 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>3 500</t>
+          <t>1 200</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 6. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>excavator_jcb_shift</t>
+          <t>gas_block_cladding_work_m2</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Расходные материалы для установки опалубки (смазка; звездочки ПВХ, трубки)</t>
+          <t>Кладка парапета из газобетонных блоков</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>9759.080000</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>1</v>
+      </c>
+      <c r="E155" t="n">
+        <v>7000</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>formwork_consumables_m2</t>
+          <t>gas_block_masonry_work_m3</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Доставка, вывоз опалубки манипулятором</t>
+          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>20000.000000</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+      <c r="E156" t="n">
+        <v>1200</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>formwork_delivery_truck</t>
+          <t>lintel_concreting_work_m</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Устройство фундаментной плиты</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Демонтаж опалубки после завершения бетонирования</t>
+          <t>Установка воронки парапетной</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>1</v>
+      </c>
+      <c r="E157" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>formwork_dismantling_work_m2</t>
+          <t>roof_parapet_drain_item</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Комплект опалубки (телескопические стойки, унивилки, треноги, водостойкая фанера, поперечные и продольные балки двутавровые)</t>
+          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>600.000000</t>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>formwork_rental_m2</t>
+          <t>scaffolding_setup_dismantling_work_set</t>
         </is>
       </c>
     </row>
@@ -5199,131 +5350,147 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
+          <t>Резка блока под перемычку (U-блок)</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D159" t="n">
         <v>1</v>
       </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>1 200</t>
-        </is>
+      <c r="E159" t="n">
+        <v>400</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.0.</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>gas_block_cladding_work_m2</t>
+          <t>u_block_lintel_cutting_item</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Газобетонный блок D400 600x400x250 мм</t>
+          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>6000</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>1</v>
+      </c>
+      <c r="E160" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>gas_block_d400_m3</t>
+          <t>lintel_monolithic_concreting_work_m</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x150x250 мм</t>
+          <t>Укладка ПВХ Мембраны</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>5600</t>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>1</v>
+      </c>
+      <c r="E161" t="n">
+        <v>630</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>gas_block_d500_150_m3</t>
+          <t>roof_pvc_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x250x250 мм</t>
+          <t>Кладка вентканалов Schiedel</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>5500</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>1</v>
+      </c>
+      <c r="E162" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>gas_block_d500_m3</t>
+          <t>schiedel_masonry_work_m</t>
         </is>
       </c>
     </row>
@@ -5335,45 +5502,45 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Кладка парапета из газобетонных блоков</t>
+          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D163" t="n">
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>7000</v>
+        <v>450</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: ставка такая же, как утепление балок и торца плиты.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>gas_block_masonry_work_m3</t>
+          <t>lintel_edge_insulation_work_m</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Укладка геотекстиля</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5381,439 +5548,331 @@
           <t>м2</t>
         </is>
       </c>
-      <c r="D164" t="n">
-        <v>1</v>
-      </c>
-      <c r="E164" t="n">
-        <v>35</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>111.76</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 8. Исходное кол-во: 1.0.</t>
+          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>geotextile_laying_m2</t>
+          <t>roof_geotextile_technonikol_prof_300_m2</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
+          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E165" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>6610</v>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H165" t="inlineStr">
-        <is>
-          <t>lintel_concreting_work_m</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Перенос, подъем бетона вручную</t>
+          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>1</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>5 000</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>450</v>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H166" t="inlineStr">
-        <is>
-          <t>manual_concrete_lifting_m3</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Разработка грунта вручную (в т.ч. Копка траншей под коммуникации)</t>
+          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>1</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="E167" t="n">
-        <v>1400</v>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>59.55</v>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 7. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H167" t="inlineStr">
-        <is>
-          <t>manual_excavation_m3</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Доставка арматуры, металла</t>
+          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>22000.000000</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>6001.23</v>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
-      </c>
-      <c r="H168" t="inlineStr">
-        <is>
-          <t>metal_delivery_truck</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Монтаж мембраны PLANTER стандарт</t>
+          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E169" t="n">
-        <v>100</v>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>2060</v>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H169" t="inlineStr">
-        <is>
-          <t>planter_membrane_installation_work_m2</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
+          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>1</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="E170" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
+        <v>23.12</v>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>roof_crane_lifting_shift</t>
+          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>111.76</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>7377.89</v>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>roof_geotextile_technonikol_prof_300_m2</t>
+          <t>roof_eps100_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E172" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>7155.34</v>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.0.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>roof_internal_drain_pvc_110mm_m</t>
+          <t>roof_eps50_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E173" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>9888.67</v>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1.0.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>roof_internal_drain_with_heating_item</t>
+          <t>roof_eps_slope_2_1_plate_a_m3</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Установка воронки парапетной</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E174" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>9888.67</v>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>roof_parapet_drain_item</t>
+          <t>roof_eps_slope_2_1_plate_b_m3</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Пескобетон М300 40 кг</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>9888.67</v>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>sand_concrete_bag</t>
+          <t>roof_eps_slope_4_2_plate_j_m3</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Отсыпка дна котлована песком с трамбованием механизировано с применением виброплиты (коэф.упл. 1,3)</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5821,196 +5880,162 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D176" t="n">
-        <v>1</v>
-      </c>
       <c r="E176" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>9888.67</v>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 9. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>sand_filling_work_m3</t>
+          <t>roof_eps_slope_4_2_plate_k_m3</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Земляные работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Песок строительный</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>1000</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>57.56</v>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>sand_m3</t>
+          <t>roof_geotextile_technonikol_prof_150_m2</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Земляные работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Перемещение песка вручную</t>
+          <t>Рейка прижимная, 2 м</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>пог. м</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>90</v>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>sand_manual_moving_m3</t>
+          <t>roof_aluminum_pressure_rail_m</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
+          <t>Рейка краевая, 2 м</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>компл</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+          <t>пог. м</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>95</v>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>scaffolding_setup_dismantling_work_set</t>
+          <t>roof_aluminum_edge_rail_m</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Доставка вентканалов/ разгрузка в ручную на объекте</t>
+          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>1</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>2 500</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>1146.91</v>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>schiedel_delivery_truck</t>
+          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Технический надзор</t>
+          <t>Аэратор кровельный PVC, А75х375</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>5000.000000</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>587</v>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>technical_supervision_fixed</t>
+          <t>roof_pvc_aerator_75x375_item</t>
         </is>
       </c>
     </row>
@@ -6022,92 +6047,109 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовкладыша</t>
+          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D182" t="n">
         <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>100</v>
+        <v>15000</v>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>thermal_insert_installation_work_m</t>
+          <t>roof_crane_lifting_shift</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Устройство фундаментной плиты</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Монтаж опалубки из пиломатериалов для отбортовки плиты</t>
+          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
+      </c>
+      <c r="E183" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.0.</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>timber_formwork_installation_work_m2</t>
+          <t>roof_internal_drain_pvc_110mm_m</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Пиломатериал обрезной для устройства опалубки ГОСТ</t>
+          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>21499.997319</t>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>1</v>
+      </c>
+      <c r="E184" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1.0.</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>timber_m3</t>
+          <t>roof_internal_drain_with_heating_item</t>
         </is>
       </c>
     </row>
@@ -6119,33 +6161,33 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Резка блока под перемычку (U-блок)</t>
+          <t>Пароизоляция основания плёнкой ПВХ</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D185" t="n">
         <v>1</v>
       </c>
       <c r="E185" t="n">
-        <v>400</v>
+        <v>77</v>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.0.</t>
+          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>u_block_lintel_cutting_item</t>
+          <t>roof_vapor_barrier_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -6157,35 +6199,33 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Вывоз мусора с объекта</t>
+          <t>Монтаж примыкания к вентшахтам</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D186" t="n">
         <v>1</v>
       </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
+      <c r="E186" t="n">
+        <v>5000</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 26. Исходное кол-во: 1.0.</t>
+          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>waste_removal_truck</t>
+          <t>roof_pvc_membrane_abutment_work_m</t>
         </is>
       </c>
     </row>
@@ -6197,197 +6237,169 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
+          <t>Установка аэратора кровельного PVC, А75х375</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D187" t="n">
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>1500</v>
+        <v>2500</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>lintel_monolithic_concreting_work_m</t>
+          <t>roof_pvc_aerator_75x375_installation_item</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Schiedel</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой до 250мм)</t>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D188" t="n">
         <v>1</v>
       </c>
       <c r="E188" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>268.4</v>
+      </c>
+      <c r="F188" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>beam_concrete_placing_work_m</t>
+          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Schiedel</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Пароизоляция основания плёнкой ПВХ</t>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D189" t="n">
         <v>1</v>
       </c>
       <c r="E189" t="n">
-        <v>77</v>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>902.8</v>
+      </c>
+      <c r="F189" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H189" t="inlineStr">
-        <is>
-          <t>roof_vapor_barrier_installation_work_m2</t>
+          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Schiedel</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
+          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D190" t="n">
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>770</v>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>264</v>
+      </c>
+      <c r="F190" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H190" t="inlineStr">
-        <is>
-          <t>roof_eps_insulation_installation_work_m2</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Schiedel</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Укладка ПВХ Мембраны</t>
+          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D191" t="n">
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>630</v>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>672</v>
+      </c>
+      <c r="F191" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>roof_pvc_membrane_installation_work_m2</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Schiedel</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Монтаж примыкания к вентшахтам</t>
+          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6399,59 +6411,95 @@
         <v>1</v>
       </c>
       <c r="E192" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>512.4</v>
+      </c>
+      <c r="F192" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_abutment_work_m</t>
+          <t>schiedel_vent_channel_2x_36_25_item</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Schiedel</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Кладка вентканалов Schiedel</t>
+          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D193" t="n">
         <v>1</v>
       </c>
       <c r="E193" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F193" t="inlineStr">
-        <is>
-          <t>2026-07-28</t>
-        </is>
+        <v>732</v>
+      </c>
+      <c r="F193" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>schiedel_masonry_work_m</t>
+          <t>schiedel_vent_channel_3x_52_25_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Доставка вентканалов/ разгрузка в ручную на объекте</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>1</v>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>2 500</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>2026-07-30</t>
+        </is>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>schiedel_delivery_truck</t>
         </is>
       </c>
     </row>

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H194"/>
+  <dimension ref="A1:H195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -1948,7 +1948,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -1986,7 +1986,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3639,7 +3639,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3677,7 +3677,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -3715,7 +3715,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
@@ -4069,7 +4069,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -5058,7 +5058,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -5134,7 +5134,7 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
@@ -5212,7 +5212,7 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
@@ -5250,7 +5250,7 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
@@ -5328,7 +5328,7 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
@@ -5366,7 +5366,7 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
@@ -5442,7 +5442,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -5480,7 +5480,7 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6101,7 +6101,7 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
@@ -6139,7 +6139,7 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
@@ -6177,7 +6177,7 @@
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
@@ -6199,28 +6199,28 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Монтаж примыкания к вентшахтам</t>
+          <t>Монтаж примыкания кровли из ПВХ мембраны</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D186" t="n">
         <v>1</v>
       </c>
       <c r="E186" t="n">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Добавлено 2026-08-02 по сверке эталонных смет: общее линейное примыкание кровли к парапетам/стенам/ВК считается в м.п.; отдельное примыкание к вентшахтам в шт остается optional legacy.</t>
         </is>
       </c>
       <c r="H186" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Установка аэратора кровельного PVC, А75х375</t>
+          <t>Монтаж примыкания к вентшахтам</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -6249,33 +6249,33 @@
         <v>1</v>
       </c>
       <c r="E187" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>roof_pvc_aerator_75x375_installation_item</t>
+          <t>roof_vent_shaft_abutment_installation_item</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+          <t>Установка аэратора кровельного PVC, А75х375</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6287,14 +6287,21 @@
         <v>1</v>
       </c>
       <c r="E188" t="n">
-        <v>268.4</v>
-      </c>
-      <c r="F188" s="2" t="n">
-        <v>46146</v>
+        <v>2500</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>roof_pvc_aerator_75x375_installation_item</t>
         </is>
       </c>
     </row>
@@ -6306,7 +6313,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6318,14 +6325,14 @@
         <v>1</v>
       </c>
       <c r="E189" t="n">
-        <v>902.8</v>
+        <v>268.4</v>
       </c>
       <c r="F189" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -6337,7 +6344,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6349,14 +6356,14 @@
         <v>1</v>
       </c>
       <c r="E190" t="n">
-        <v>264</v>
+        <v>902.8</v>
       </c>
       <c r="F190" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6375,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
+          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6380,7 +6387,7 @@
         <v>1</v>
       </c>
       <c r="E191" t="n">
-        <v>672</v>
+        <v>264</v>
       </c>
       <c r="F191" s="2" t="n">
         <v>46146</v>
@@ -6399,7 +6406,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
+          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6411,19 +6418,14 @@
         <v>1</v>
       </c>
       <c r="E192" t="n">
-        <v>512.4</v>
+        <v>672</v>
       </c>
       <c r="F192" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
-        </is>
-      </c>
-      <c r="H192" t="inlineStr">
-        <is>
-          <t>schiedel_vent_channel_2x_36_25_item</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -6435,7 +6437,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
+          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6447,57 +6449,93 @@
         <v>1</v>
       </c>
       <c r="E193" t="n">
-        <v>732</v>
+        <v>512.4</v>
       </c>
       <c r="F193" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
+          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_3x_52_25_item</t>
+          <t>schiedel_vent_channel_2x_36_25_item</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Schiedel</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Доставка вентканалов/ разгрузка в ручную на объекте</t>
+          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D194" t="n">
         <v>1</v>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E194" t="n">
+        <v>732</v>
+      </c>
+      <c r="F194" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_3x_52_25_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Доставка вентканалов/ разгрузка в ручную на объекте</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>1</v>
+      </c>
+      <c r="E195" t="inlineStr">
         <is>
           <t>2 500</t>
         </is>
       </c>
-      <c r="F194" t="inlineStr">
-        <is>
-          <t>2026-07-30</t>
-        </is>
-      </c>
-      <c r="G194" t="inlineStr">
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="G195" t="inlineStr">
         <is>
           <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H195" t="inlineStr">
         <is>
           <t>schiedel_delivery_truck</t>
         </is>

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H195"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -504,12 +504,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 3. Исходное кол-во: 1.0. price_code не найден автоматически: нужно сопоставить вручную.</t>
+          <t>Источник: первый лист нового прайса, строка 3. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr"/>
@@ -538,12 +538,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 4. Исходное кол-во: 1.0. price_code не найден автоматически: нужно сопоставить вручную.</t>
+          <t>Источник: первый лист нового прайса, строка 4. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr"/>
@@ -572,12 +572,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 5. Исходное кол-во: 1.0.</t>
+          <t>Источник: первый лист нового прайса, строка 5. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -612,12 +612,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 26. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 26. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -744,9 +744,20 @@
           <t>м3</t>
         </is>
       </c>
+      <c r="D9" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 200 руб./м3 из ТРЦ (лист 'НС 29.06.26', строка 32), но это была ЛЕВАЯ/белая (клиентская) колонка. Правая/серая (реальная внутренняя себестоимость) колонка для этой же строки = 0. См. подробное объяснение серая/белая структура в комментарии к timber_formwork_installation_work_m2 выше - тот же класс ошибки. Пользователь подтвердила 2026-08-06: 0 верно, работа не тарифицируется отдельно внутри.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -779,12 +790,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 10. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 10. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -819,12 +830,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 6. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 6. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -857,12 +868,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 8. Исходное кол-во: 1.0.</t>
+          <t>Источник: первый лист нового прайса, строка 8. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -895,12 +906,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 7. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 7. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -933,12 +944,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 9. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 9. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1908,12 +1919,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.0.</t>
+          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -1948,12 +1959,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.0.</t>
+          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
@@ -1986,12 +1997,12 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2355,28 +2366,38 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Доска обрезная 25х100х6000мм 1-сорт ГОСТ</t>
+          <t>Пиломатериал обрезной для устройства опалубки ГОСТ (для опалубки монолитных перемычек)</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>265</v>
-      </c>
-      <c r="F62" s="2" t="n">
-        <v>46154</v>
+        <v>21499.997319</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>Добавлено 2026-08-06: та же цена, что и timber_m3 - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>lintel_formwork_timber_m3</t>
         </is>
       </c>
     </row>
@@ -2388,7 +2409,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Доска обрезная 25х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 25х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2397,7 +2418,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>397</v>
+        <v>265</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>46154</v>
@@ -2416,7 +2437,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 25х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2425,7 +2446,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>530</v>
+        <v>397</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>46154</v>
@@ -2444,7 +2465,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 50х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2453,7 +2474,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>795</v>
+        <v>530</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>46154</v>
@@ -2472,7 +2493,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х200х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 50х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2481,7 +2502,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1093</v>
+        <v>795</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>46154</v>
@@ -2500,7 +2521,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Брус обрезной 100х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 50х200х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2528,7 +2549,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Брус обрезной 100х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной 100х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2537,7 +2558,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1590</v>
+        <v>1093</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>46154</v>
@@ -2556,7 +2577,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Брус обрезной 150х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной 100х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2565,7 +2586,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>2500</v>
+        <v>1590</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>46154</v>
@@ -2584,7 +2605,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 50х300х6000мм</t>
+          <t>Брус обрезной 150х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2593,7 +2614,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3800</v>
+        <v>2500</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>46154</v>
@@ -2612,7 +2633,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 20х90х6000мм</t>
+          <t>Доска сухая строганная 50х300х6000мм</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2621,7 +2642,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>360</v>
+        <v>3800</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>46154</v>
@@ -2640,7 +2661,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 20х140х6000мм</t>
+          <t>Доска сухая строганная 20х90х6000мм</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2649,7 +2670,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>540</v>
+        <v>360</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>46154</v>
@@ -2668,7 +2689,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х90х6000мм</t>
+          <t>Доска сухая строганная 20х140х6000мм</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2677,7 +2698,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>682</v>
+        <v>540</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>46154</v>
@@ -2696,7 +2717,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х140х6000мм</t>
+          <t>Доска сухая строганная 45х90х6000мм</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2705,7 +2726,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1022</v>
+        <v>682</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>46154</v>
@@ -2724,7 +2745,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х190х6000мм</t>
+          <t>Доска сухая строганная 45х140х6000мм</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2733,7 +2754,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1406</v>
+        <v>1022</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>46154</v>
@@ -2752,7 +2773,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 90х90х6000мм</t>
+          <t>Доска сухая строганная 45х190х6000мм</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2780,7 +2801,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 90х140х6000мм</t>
+          <t>Брус сухой строганный 90х90х6000мм</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2789,7 +2810,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2045</v>
+        <v>1406</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>46154</v>
@@ -2808,7 +2829,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 140х140х6000мм</t>
+          <t>Брус сухой строганный 90х140х6000мм</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2817,7 +2838,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>3214</v>
+        <v>2045</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>46154</v>
@@ -2836,7 +2857,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 140х190х6000мм</t>
+          <t>Брус сухой строганный 140х140х6000мм</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2845,7 +2866,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4500</v>
+        <v>3214</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>46154</v>
@@ -2864,7 +2885,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 50х50х3000мм</t>
+          <t>Брус сухой строганный 140х190х6000мм</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2873,7 +2894,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>200</v>
+        <v>4500</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>46154</v>
@@ -2892,7 +2913,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 45х45х3000мм</t>
+          <t>Брус сухой строганный 50х50х3000мм</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2901,7 +2922,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>46154</v>
@@ -2920,7 +2941,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 40х50х3000мм</t>
+          <t>Брус сухой строганный 45х45х3000мм</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2948,7 +2969,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 25х100х6000мм 1-сорт ГОСТ</t>
+          <t>Брус сухой строганный 40х50х3000мм</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2957,7 +2978,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>310</v>
+        <v>175</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>46154</v>
@@ -2976,7 +2997,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 25х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 25х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2985,7 +3006,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>465</v>
+        <v>310</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>46154</v>
@@ -3004,7 +3025,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 50х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 25х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3013,7 +3034,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>621</v>
+        <v>465</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>46154</v>
@@ -3032,7 +3053,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием  50х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 50х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3041,7 +3062,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>931</v>
+        <v>621</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>46154</v>
@@ -3060,7 +3081,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 50х200х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием  50х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3069,7 +3090,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>1281</v>
+        <v>931</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>46154</v>
@@ -3088,7 +3109,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 100х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 50х200х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3116,7 +3137,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 100х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной с антисептированием 100х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3125,7 +3146,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1863</v>
+        <v>1281</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>46154</v>
@@ -3144,7 +3165,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 150х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной с антисептированием 100х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3153,7 +3174,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2928</v>
+        <v>1863</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>46154</v>
@@ -3172,7 +3193,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 50х300х6000мм</t>
+          <t>Брус обрезной с антисептированием 150х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3181,7 +3202,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>4200</v>
+        <v>2928</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>46154</v>
@@ -3200,7 +3221,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 20х90х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 50х300х6000мм</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3209,7 +3230,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>420</v>
+        <v>4200</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>46154</v>
@@ -3228,7 +3249,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 20х140х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 20х90х6000мм</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3237,7 +3258,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>620</v>
+        <v>420</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>46154</v>
@@ -3256,7 +3277,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х90х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 20х140х6000мм</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3265,7 +3286,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>772</v>
+        <v>620</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>46154</v>
@@ -3284,7 +3305,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х140х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 45х90х6000мм</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3293,7 +3314,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1159</v>
+        <v>772</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>46154</v>
@@ -3312,7 +3333,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х190х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 45х140х6000мм</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3321,7 +3342,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1593</v>
+        <v>1159</v>
       </c>
       <c r="F96" s="2" t="n">
         <v>46154</v>
@@ -3340,7 +3361,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 90х90х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 45х190х6000мм</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3368,7 +3389,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 90х140х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 90х90х6000мм</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3377,7 +3398,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>2318</v>
+        <v>1593</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>46154</v>
@@ -3396,7 +3417,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 140х140х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 90х140х6000мм</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3405,7 +3426,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3642</v>
+        <v>2318</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>46154</v>
@@ -3424,7 +3445,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 140х190х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 140х140х6000мм</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3433,7 +3454,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5100</v>
+        <v>3642</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>46154</v>
@@ -3452,7 +3473,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 50х50х3000мм</t>
+          <t>Брус сухой строганный с антисептированием 140х190х6000мм</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3461,7 +3482,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>270</v>
+        <v>5100</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>46154</v>
@@ -3480,7 +3501,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 45х45х3000мм</t>
+          <t>Брус сухой строганный с антисептированием 50х50х3000мм</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3489,7 +3510,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>46154</v>
@@ -3508,7 +3529,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 40х50х3000мм</t>
+          <t>Брус сухой строганный с антисептированием 45х45х3000мм</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3536,7 +3557,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Фанера 1,52х1,52*18</t>
+          <t>Брус сухой строганный с антисептированием 40х50х3000мм</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3545,73 +3566,85 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1400</v>
+        <v>220</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>plywood_1520x1520_18mm_sheet</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Устройство фундаментной плиты</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Демонтаж опалубки после завершения бетонирования</t>
+          <t>Фанера 1,52х1,52*18</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>formwork_dismantling_work_m2</t>
+          <t>plywood_1520x1520_18mm_sheet</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Устройство фундаментной плиты</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Монтаж опалубки из пиломатериалов для отбортовки плиты</t>
+          <t>Фанера 1,52х1,52*18 (для опалубки монолитных перемычек)</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>1400</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Добавлено 2026-08-06: тот же лист фанеры, что и plywood_1520x1520_18mm_sheet (прайс Елены, лист 'Пиломатериалы (Олег)', строка 23) - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>timber_formwork_installation_work_m2</t>
+          <t>lintel_formwork_plywood_sheet</t>
         </is>
       </c>
     </row>
@@ -3623,7 +3656,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Устройство утепления низа плиты</t>
+          <t>Монтаж опалубки из доски для отбортовки плиты</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3635,33 +3668,33 @@
         <v>1</v>
       </c>
       <c r="E107" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.0.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 580 руб./м2 из ТРЦ (лист 'НС 29.06.26', строка 42), но это была ЛЕВАЯ/белая (клиентская) колонка сметы. У каждой строки в реальных сметах два параллельных блока колонок - левый (белый, с накруткой для клиента) и правый (серый, настоящая внутренняя себестоимость Елены; в ТРЦ правый блок физически закрашен заливкой, в АРК/ЮСВ заливки нет, но структура та же и подтверждается арифметикой - левое/правое = Коэф-т Рентабельности листа, обычно 1.32). Правая/серая колонка для этой строки = 0 в ТРЦ. Пользователь подтвердила 2026-08-06: 0 - это реальный ответ, эта работа у Елены отдельно не тарифицируется внутри (входит в другую работу/бригадо-день), клиенту просто показывается отдельной строкой для формы.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>eps_bottom_slab_insulation_work_m2</t>
+          <t>timber_formwork_installation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Устройство фундаментной плиты</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Утепление торца плиты ЭППС 100мм</t>
+          <t>Демонтаж опалубки после завершения бетонирования</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3673,33 +3706,33 @@
         <v>1</v>
       </c>
       <c r="E108" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 120 руб./м2 из АРК/ЮСВ (левая/белая колонка на нескольких строках 'Демонтаж опалубки после завершения бетонирования'). Проверила правую/серую колонку в АРК на тех же строках - везде 0. Тот же класс ошибки, что и timber_formwork_installation_work_m2/sand_manual_moving_m3 (см. их комментарии). Пользователь подтвердила 2026-08-06: 0 верно.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>eps_wall_insulation_work_m2</t>
+          <t>formwork_dismantling_work_m2</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Устройство фундаментной плиты</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовкладыша</t>
+          <t>Устройство и монтаж термовкладыша 150*400*250мм шаг 200мм</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3707,20 +3740,14 @@
           <t>мп</t>
         </is>
       </c>
-      <c r="D109" t="n">
-        <v>1</v>
-      </c>
-      <c r="E109" t="n">
-        <v>100</v>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
@@ -3732,12 +3759,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Гидроизоляция</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
+          <t>Утепление стен ЭППС 50мм, работа (ВРЕМЕННО 0 - ждет ответа Елены)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3749,261 +3776,325 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>770</v>
+        <v>0</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>ВРЕМЕННОЕ РЕШЕНИЕ 2026-08-06, требует уточнения у Елены: в смете ТРЦ утепление стен 50мм+100мм считается ОДНОЙ работой (680 руб./м2 на оба слоя сразу, лист 'НС 29.06.26' строка 73), а не двумя отдельными монтажными работами как в наших калькуляторах. АРК и ЮСВ вообще не имеют слоя 50мм на стенах (только 100мм), сверить не с чем. Поставлено 0, чтобы не задвоить деньги поверх уже существующей (возможно тоже неточной - см. eps_wall_insulation_work_m2) цены на монтаж 100мм-слоя. НЕ ИСПОЛЬЗОВАТЬ КАК ОКОНЧАТЕЛЬНОЕ ЗНАЧЕНИЕ - заменить, когда Елена ответит на вопрос от 2026-08-06 (один проход маляра на оба слоя или два отдельных).</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>roof_eps_insulation_installation_work_m2</t>
+          <t>eps_wall_insulation_work_50_m2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Planter Standard Технониколь 40м2-1рул</t>
+          <t>Устройство утепления низа плиты</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>рул</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>4738</v>
+        <v>900</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>planter_standard_roll</t>
+          <t>eps_bottom_slab_insulation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>PLANTERBAND 10м х 10см-1шт</t>
+          <t>Утепление торца плиты ЭППС 100мм</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>750</v>
+        <v>500</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>planterband_item</t>
+          <t>eps_wall_insulation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Праймер битумный AquaMast, 18 л-1шт</t>
+          <t>Устройство и монтаж термовкладыша</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>2865</v>
+        <v>100</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>bitumen_primer_aquamast_18l_item</t>
+          <t>thermal_insert_combined_installation_work_m</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
+          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>2828.21</v>
+        <v>770</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>bitumen_mastic_aquamast_18kg_item</t>
+          <t>roof_eps_insulation_installation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
+          <t>Пеноплэкс ГЕО 50 мм (для термовставок)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
           <t>м3</t>
         </is>
+      </c>
+      <c r="D115" t="n">
+        <v>1</v>
       </c>
       <c r="E115" t="n">
         <v>8800</v>
       </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Источник: первый лист нового прайса, строка 43. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>eps_geo_50_m3</t>
+          <t>thermal_insert_50_material_m3</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
+          <t>Пеноплэкс ГЕО 100 мм (для термовставок)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
           <t>м3</t>
         </is>
+      </c>
+      <c r="D116" t="n">
+        <v>1</v>
       </c>
       <c r="E116" t="n">
         <v>8900</v>
       </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Источник: первый лист нового прайса, строка 44. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>eps_geo_100_m3</t>
+          <t>thermal_insert_100_material_m3</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Клей-пена для ЭППС-1шт</t>
+          <t>Устройство и монтаж термовставок 50 мм</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>450</v>
+        <v>100</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Добавлено 2026-08-07: новый прайс Елены содержит одну универсальную строку 'Устройство и монтаж термовкладыша' = 100 руб./мп. В реальных эталонных сметах АРК/ТРЦ/ЮСВ работа термовставок также считается по длине с этой ставкой; для production-раздельного режима 50/100 нужен отдельный price_code, поэтому цена размножена из той же универсальной строки прайса.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>eps_foam_glue_can</t>
+          <t>thermal_insert_50_installation_work_m</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
+          <t>Устройство и монтаж термовставок 100 мм</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>109</v>
+        <v>100</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
+          <t>Добавлено 2026-08-07: та же универсальная работа 'Устройство и монтаж термовкладыша' = 100 руб./мп из нового прайса Елены. Толщина слоя меняет материал, но не ставку монтажной работы по м.п.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>geotextile_dornit_300_m2</t>
+          <t>thermal_insert_100_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -4015,33 +4106,33 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
+          <t>Устройство и монтаж термовставок (произвольный типоразмер)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D119" t="n">
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>350</v>
+        <v>100</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Добавлено 2026-08-07: для режима thermal_insert_mode='items' калькулятор считает одну работу по суммарной длине всех термовставок произвольных типоразмеров. Ставка берется из той же универсальной строки нового прайса Елены 'Устройство и монтаж термовкладыша' = 100 руб./мп.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>bitumen_waterproofing_work_m2</t>
+          <t>thermal_insert_items_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -4053,698 +4144,691 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Монтаж мембраны PLANTER стандарт</t>
+          <t>Материал термовставок (произвольный типоразмер)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D120" t="n">
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>100</v>
+        <v>8900</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.0.</t>
+          <t>Добавлено 2026-08-07: общий fallback для thermal_insert_items произвольного типоразмера. Новый прайс Елены дает Пеноплэкс ГЕО 100 мм (для термовставок) = 8900 руб./м3 и Пеноплэкс ГЕО 50 мм = 8800 руб./м3; для произвольных типоразмеров без отдельного толщинного price_code используем базовую цену 100 мм как более частый материал термовставок. Если в будущем появятся разные цены по eps_size, заменить на построчный price_code.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>planter_membrane_installation_work_m2</t>
+          <t>thermal_insert_item_material_m3</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Проволока</t>
+          <t>Planter Standard Технониколь 40м2-1рул</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>кг</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>1</v>
+          <t>рул</t>
+        </is>
       </c>
       <c r="E121" t="n">
-        <v>75</v>
+        <v>4738</v>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
+          <t>Обновлено 04.05</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>planter_standard_roll</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 25 мм</t>
+          <t>PLANTERBAND 10м х 10см-1шт</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.7</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E122" t="n">
-        <v>155.8</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>46214</v>
+        <v>750</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>rebar_a500_d25_m</t>
+          <t>planterband_item</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 20мм</t>
+          <t>Праймер битумный AquaMast, 18 л-1шт</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.7</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E123" t="n">
-        <v>100.25</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>46214</v>
+        <v>2865</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
+          <t>Обновлено 04.05</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>rebar_a500_d20_m</t>
+          <t>bitumen_primer_aquamast_18l_item</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 16 мм</t>
+          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.7</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E124" t="n">
-        <v>64.90000000000001</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>46214</v>
+        <v>2828.21</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>rebar_a500_d16_m</t>
+          <t>bitumen_mastic_aquamast_18kg_item</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 12мм</t>
+          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.7</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E125" t="n">
-        <v>36.85</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>46214</v>
+        <v>8800</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>rebar_a500_d12_m</t>
+          <t>eps_geo_50_m3</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 10 мм</t>
+          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>11.7</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E126" t="n">
-        <v>27.16</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>46214</v>
+        <v>8900</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>rebar_a500_d10_m</t>
+          <t>eps_geo_100_m3</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 8 мм</t>
+          <t>Клей-пена для ЭППС-1шт</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>11.7</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E127" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>46214</v>
+        <v>450</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Обновлено 04.05</t>
+        </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>rebar_a240_d8_m</t>
+          <t>eps_foam_glue_can</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 6 мм</t>
+          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>1п.м</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>11.7</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="E128" t="n">
-        <v>10.25</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>46214</v>
+        <v>109</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
+        </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>rebar_a240_d6_m</t>
+          <t>geotextile_dornit_300_m2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Блок D 400</t>
+          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>34,56 м3</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
       </c>
       <c r="E129" t="n">
-        <v>5900</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>46146</v>
+        <v>350</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>bitumen_waterproofing_work_m2</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Блок D 500</t>
+          <t>Монтаж мембраны PLANTER стандарт</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>32,4 м3</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>5200</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>46146</v>
+        <v>100</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>planter_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Блок D 400</t>
+          <t>Проволока</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>1,8 м3</t>
-        </is>
+          <t>кг</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>6300</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>46146</v>
+        <v>75</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Блок D 500</t>
+          <t>Арматура класса А500 диаметром 25 мм</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>1,8 м3</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.7</v>
       </c>
       <c r="E132" t="n">
-        <v>5800</v>
+        <v>155.8</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+        <v>46214</v>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>rebar_a500_d25_m</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Арматура класса А500 диаметром 20мм</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
+          <t>1п.м</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>11.7</v>
       </c>
       <c r="E133" t="n">
-        <v>360</v>
+        <v>100.25</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>46146</v>
+        <v>46214</v>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>block_adhesive_bag</t>
+          <t>rebar_a500_d20_m</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Доставка блоков, смеси</t>
+          <t>Арматура класса А500 диаметром 16 мм</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E134" t="n">
+        <v>64.90000000000001</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>block_delivery_truck</t>
+          <t>rebar_a500_d16_m</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Разгрузка блоков, смеси манипулятором</t>
+          <t>Арматура класса А500 диаметром 12мм</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E135" t="n">
+        <v>36.85</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>block_unloading_manipulator_truck</t>
+          <t>rebar_a500_d12_m</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Газобетонный блок D400 600x400x250 мм</t>
+          <t>Арматура класса А500 диаметром 10 мм</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>6000</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E136" t="n">
+        <v>27.16</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>gas_block_d400_m3</t>
+          <t>rebar_a500_d10_m</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x150x250 мм</t>
+          <t>Арматура класса А240 диаметром 8 мм</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>5600</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E137" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>gas_block_d500_150_m3</t>
+          <t>rebar_a240_d8_m</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x250x250 мм</t>
+          <t>Арматура класса А240 диаметром 6 мм</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>5500</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>11.7</v>
+      </c>
+      <c r="E138" t="n">
+        <v>10.25</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>46214</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>gas_block_d500_m3</t>
+          <t>rebar_a240_d6_m</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Пескобетон М300 40 кг</t>
+          <t>Блок D 400</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>34,56 м3</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>5900</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>sand_concrete_bag</t>
+          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Блок D 500</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>32,4 м3</t>
+        </is>
       </c>
       <c r="E140" t="n">
-        <v>659.77</v>
+        <v>5200</v>
       </c>
       <c r="F140" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Сетка 5/0.4/100</t>
+          <t>Блок D 400</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>рулон</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>1,8 м3</t>
+        </is>
       </c>
       <c r="E141" t="n">
-        <v>1304.63</v>
+        <v>6300</v>
       </c>
       <c r="F141" s="2" t="n">
         <v>46146</v>
@@ -4758,24 +4842,26 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Сетка 5/0.5/100</t>
+          <t>Блок D 500</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>рулон</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>1,8 м3</t>
+        </is>
       </c>
       <c r="E142" t="n">
-        <v>1729.38</v>
+        <v>5800</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>46146</v>
@@ -4789,43 +4875,48 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>PTH 8</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мешок 25 кг</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="E143" t="n">
-        <v>100.62</v>
+        <v>360</v>
       </c>
       <c r="F143" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>block_adhesive_bag</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>PTH 12</t>
+          <t>Воронка парапетная с листвоуловителем (материал)</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4834,184 +4925,196 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>150.62</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>46146</v>
+        <v>6001.23</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Добавлено 2026-08-06: та же причина, что и у внутренней воронки - материалы не читаются автоматическим скриптом, цена взята напрямую из листа 'Утеплителипленкимастика (Олег)', строка 31 ('Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650') = 6001.23 руб./шт. До этой правки код ошибочно получал цену РАБОТЫ монтажа (5000 руб.) через устаревшее сопоставление в MANUAL_WORK_PRICE_CODES - реальная цена материала выше, это была настоящая ошибка в деньгах, не совпадение.</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>roof_parapet_drain_item</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>PTH 20</t>
+          <t>Доставка блоков, смеси</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>72</v>
-      </c>
-      <c r="E145" t="n">
-        <v>171.17</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>46146</v>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>28000</t>
+        </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>block_delivery_truck</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>PTH 25М</t>
+          <t>Разгрузка блоков, смеси манипулятором</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>60</v>
-      </c>
-      <c r="E146" t="n">
-        <v>180.89</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>46146</v>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>block_unloading_manipulator_truck</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>PTH 38</t>
+          <t>Газобетонный блок D400 600x400x250 мм</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>60</v>
-      </c>
-      <c r="E147" t="n">
-        <v>155.66</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>46146</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>6000</t>
+        </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>gas_block_d400_m3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>PTH 38 Termo</t>
+          <t>Газобетонный блок D500 600x150x250 мм</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>60</v>
-      </c>
-      <c r="E148" t="n">
-        <v>201.14</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>46146</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>5600</t>
+        </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>gas_block_d500_150_m3</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>PTH 44</t>
+          <t>Газобетонный блок D500 600x250x250 мм</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>50</v>
-      </c>
-      <c r="E149" t="n">
-        <v>176.58</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>46146</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>gas_block_d500_m3</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>PTH 51</t>
+          <t>Пескобетон М300 40 кг</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5019,260 +5122,217 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D150" t="n">
-        <v>50</v>
-      </c>
-      <c r="E150" t="n">
-        <v>225.53</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>46146</v>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>sand_concrete_bag</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Гидроизоляция поверхности под первый ряд блоков</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мешок 25 кг</t>
         </is>
       </c>
       <c r="D151" t="n">
         <v>1</v>
       </c>
       <c r="E151" t="n">
-        <v>100</v>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>659.77</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>cutoff_waterproofing_under_blocks_m2</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
+          <t>Сетка 5/0.4/100</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>рулон</t>
         </is>
       </c>
       <c r="D152" t="n">
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>450</v>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>1304.63</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr">
-        <is>
-          <t>edge_insulation_work_m</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Укладка ЭППС 50мм под плитой</t>
+          <t>Сетка 5/0.5/100</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>рулон</t>
         </is>
       </c>
       <c r="D153" t="n">
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>250</v>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>1729.38</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr">
-        <is>
-          <t>eps_laying_work_m2</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
+          <t>PTH 8</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>1 200</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>120</v>
+      </c>
+      <c r="E154" t="n">
+        <v>100.62</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>gas_block_cladding_work_m2</t>
+          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Кладка парапета из газобетонных блоков</t>
+          <t>PTH 12</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="E155" t="n">
-        <v>7000</v>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>150.62</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr">
-        <is>
-          <t>gas_block_masonry_work_m3</t>
+          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
+          <t>PTH 20</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>72</v>
       </c>
       <c r="E156" t="n">
-        <v>1200</v>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>171.17</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H156" t="inlineStr">
-        <is>
-          <t>lintel_concreting_work_m</t>
+          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Установка воронки парапетной</t>
+          <t>PTH 25М</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5281,76 +5341,60 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E157" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>180.89</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>roof_parapet_drain_item</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
+          <t>PTH 38</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>60</v>
+      </c>
+      <c r="E158" t="n">
+        <v>155.66</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr">
-        <is>
-          <t>scaffolding_setup_dismantling_work_set</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Резка блока под перемычку (U-блок)</t>
+          <t>PTH 38 Termo</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5359,100 +5403,79 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>60</v>
       </c>
       <c r="E159" t="n">
-        <v>400</v>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>201.14</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H159" t="inlineStr">
-        <is>
-          <t>u_block_lintel_cutting_item</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
+          <t>PTH 44</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E160" t="n">
-        <v>1500</v>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>176.58</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>lintel_monolithic_concreting_work_m</t>
+          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Укладка ПВХ Мембраны</t>
+          <t>PTH 51</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E161" t="n">
-        <v>630</v>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>225.53</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>roof_pvc_membrane_installation_work_m2</t>
+          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5464,33 +5487,33 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Кладка вентканалов Schiedel</t>
+          <t>Гидроизоляция поверхности под первый ряд блоков</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D162" t="n">
         <v>1</v>
       </c>
       <c r="E162" t="n">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>schiedel_masonry_work_m</t>
+          <t>cutoff_waterproofing_under_blocks_m2</t>
         </is>
       </c>
     </row>
@@ -5518,29 +5541,29 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Добавлено по ответу Елены 2026-07-30: ставка такая же, как утепление балок и торца плиты.</t>
+          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>lintel_edge_insulation_work_m</t>
+          <t>edge_insulation_work_m</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
+          <t>Укладка ЭППС 50мм под плитой</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -5548,131 +5571,193 @@
           <t>м2</t>
         </is>
       </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>111.76</t>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+      <c r="E164" t="n">
+        <v>250</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>roof_geotextile_technonikol_prof_300_m2</t>
+          <t>eps_laying_work_m2</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
+          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
-        <v>6610</v>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>1 200</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>gas_block_cladding_work_m2</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
+          <t>Кладка парапета из газобетонных блоков</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>1</v>
       </c>
       <c r="E166" t="n">
-        <v>450</v>
+        <v>7000</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>gas_block_masonry_work_m3</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
+          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>59.55</v>
+        <v>1200</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>lintel_concreting_work_m</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
+          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>6001.23</v>
+          <t>компл</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>1</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>scaffolding_setup_dismantling_work_set</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
+          <t>Резка блока под перемычку (U-блок)</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -5680,139 +5765,189 @@
           <t>шт</t>
         </is>
       </c>
+      <c r="D169" t="n">
+        <v>1</v>
+      </c>
       <c r="E169" t="n">
-        <v>2060</v>
+        <v>400</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>u_block_lintel_cutting_item</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
+          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>23.12</v>
+        <v>1500</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
+          <t>lintel_monolithic_concreting_work_m</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
+          <t>Укладка ПВХ Мембраны</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>7377.89</v>
+        <v>630</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>roof_eps100_technonikol_carbon_eco_m3</t>
+          <t>roof_pvc_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
+          <t>Установка воронки парапетной</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>7155.34</v>
+        <v>5000</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>roof_eps50_technonikol_carbon_eco_m3</t>
+          <t>roof_parapet_drain_installation_item</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
+          <t>Кладка вентканалов Schiedel</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>9888.67</v>
+        <v>5000</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_a_m3</t>
+          <t>schiedel_masonry_work_m</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
+          <t>Блок D400 (для кладки шахты вентканалов)</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5820,29 +5955,37 @@
           <t>м3</t>
         </is>
       </c>
+      <c r="D174" t="n">
+        <v>1</v>
+      </c>
       <c r="E174" t="n">
-        <v>9888.67</v>
+        <v>6100</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Источник: первый лист нового прайса, строка 45. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_b_m3</t>
+          <t>schiedel_masonry_gas_block_d400_m3</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
+          <t>Блок D500 (для кладки шахты вентканалов)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5850,167 +5993,209 @@
           <t>м3</t>
         </is>
       </c>
+      <c r="D175" t="n">
+        <v>1</v>
+      </c>
       <c r="E175" t="n">
-        <v>9888.67</v>
+        <v>5400</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Источник: первый лист нового прайса, строка 46. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>roof_eps_slope_4_2_plate_j_m3</t>
+          <t>schiedel_masonry_gas_block_d500_m3</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
+          <t>Штробление блоков под дополнительное усиление, армирование арматурой диаметром 10 мм</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>9888.67</v>
+        <v>250</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Добавлено 2026-08-07 по сверке АРК/ТРЦ/ЮСВ: в эталонных сметах это платная работа в правой части себестоимости. Временная production-ставка 250 руб./мп до отдельного подтверждения Елены.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>roof_eps_slope_4_2_plate_k_m3</t>
+          <t>block_chasing_reinforcement_work_m</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
+          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>57.56</v>
+        <v>450</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: ставка такая же, как утепление балок и торца плиты.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>roof_geotextile_technonikol_prof_150_m2</t>
+          <t>lintel_edge_insulation_work_m</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Рейка прижимная, 2 м</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>пог. м</t>
-        </is>
-      </c>
-      <c r="E178" t="n">
-        <v>90</v>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>111.76</t>
+        </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>roof_aluminum_pressure_rail_m</t>
+          <t>roof_geotextile_technonikol_prof_300_m2</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Рейка краевая, 2 м</t>
+          <t>Воронка кровельная внутренняя с обогревом (материал)</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>пог. м</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
       </c>
       <c r="E179" t="n">
-        <v>95</v>
+        <v>5000</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Добавлено 2026-08-06: материалы не читаются автоматическим скриптом (только первый лист 'Прайс по видам работ', лист с материалами 'Утеплителипленкимастика (Олег)' сюда не входит) - цена 5000 руб./шт взята оттуда напрямую, строка 32 ('Воронка кровельная (с обжимным мет. фланцем с обогревом 110х450мм)'). До этой правки код случайно получал ту же цену через устаревшее (неверное) сопоставление с работой монтажа - см. исправление в MANUAL_WORK_PRICE_CODES выше. Цена совпала случайно (обе 5000), поэтому баг был незаметен.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>roof_aluminum_edge_rail_m</t>
+          <t>roof_internal_drain_with_heating_item</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
+          <t>ПВХ мембрана Logicroof V-GR 1,5 мм (эксплуатируемая кровля)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
+          <t>рул</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
       </c>
       <c r="E180" t="n">
         <v>1146.91</v>
       </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Добавлено 2026-08-06: такая же цена, как у обычной V-RP мембраны (1146.91 руб./рул, прайс Елены лист 'Утеплителипленкимастика (Олег)' строка 29 - в прайсе V-GR и V-RP указаны с одинаковой ценой). Пользователь вписывал эту цену вручную в гугл-таблицу 2026-08-06 после того, как для ТРЦ впервые понадобилась V-GR (эксплуатируемая зона кровли) - перенесено в реестр, чтобы не терялось при пересборке.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
+          <t>roof_pvc_membrane_logicroof_vgr_1_5mm_gray_roll</t>
         </is>
       </c>
     </row>
@@ -6022,108 +6207,82 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Аэратор кровельный PVC, А75х375</t>
+          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E181" t="n">
-        <v>587</v>
-      </c>
-      <c r="H181" t="inlineStr">
-        <is>
-          <t>roof_pvc_aerator_75x375_item</t>
+        <v>6610</v>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
+          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E182" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>450</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H182" t="inlineStr">
-        <is>
-          <t>roof_crane_lifting_shift</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
+          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>1</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="E183" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>59.55</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H183" t="inlineStr">
-        <is>
-          <t>roof_internal_drain_pvc_110mm_m</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
+          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -6131,415 +6290,1077 @@
           <t>шт</t>
         </is>
       </c>
-      <c r="D184" t="n">
-        <v>1</v>
-      </c>
       <c r="E184" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>6001.23</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1.0.</t>
-        </is>
-      </c>
-      <c r="H184" t="inlineStr">
-        <is>
-          <t>roof_internal_drain_with_heating_item</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Пароизоляция основания плёнкой ПВХ</t>
+          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E185" t="n">
-        <v>77</v>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>2060</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H185" t="inlineStr">
-        <is>
-          <t>roof_vapor_barrier_installation_work_m2</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Монтаж примыкания кровли из ПВХ мембраны</t>
+          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>1</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="E186" t="n">
-        <v>700</v>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>Добавлено 2026-08-02 по сверке эталонных смет: общее линейное примыкание кровли к парапетам/стенам/ВК считается в м.п.; отдельное примыкание к вентшахтам в шт остается optional legacy.</t>
-        </is>
+        <v>23.12</v>
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_abutment_work_m</t>
+          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Монтаж примыкания к вентшахтам</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E187" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>7377.89</v>
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>roof_vent_shaft_abutment_installation_item</t>
+          <t>roof_eps100_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Установка аэратора кровельного PVC, А75х375</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E188" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
+        <v>7155.34</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>roof_pvc_aerator_75x375_installation_item</t>
+          <t>roof_eps50_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E189" t="n">
-        <v>268.4</v>
-      </c>
-      <c r="F189" s="2" t="n">
-        <v>46146</v>
+        <v>9888.67</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>roof_eps_slope_2_1_plate_a_m3</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E190" t="n">
-        <v>902.8</v>
-      </c>
-      <c r="F190" s="2" t="n">
-        <v>46146</v>
+        <v>9888.67</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>roof_eps_slope_2_1_plate_b_m3</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E191" t="n">
-        <v>264</v>
-      </c>
-      <c r="F191" s="2" t="n">
-        <v>46146</v>
+        <v>9888.67</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>roof_eps_slope_4_2_plate_j_m3</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
       </c>
       <c r="E192" t="n">
-        <v>672</v>
-      </c>
-      <c r="F192" s="2" t="n">
-        <v>46146</v>
+        <v>9888.67</v>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>roof_eps_slope_4_2_plate_k_m3</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D193" t="n">
-        <v>1</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="E193" t="n">
-        <v>512.4</v>
-      </c>
-      <c r="F193" s="2" t="n">
-        <v>46146</v>
+        <v>57.56</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_2x_36_25_item</t>
+          <t>roof_geotextile_technonikol_prof_150_m2</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
+          <t>Рейка прижимная, 2 м</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D194" t="n">
-        <v>1</v>
+          <t>пог. м</t>
+        </is>
       </c>
       <c r="E194" t="n">
-        <v>732</v>
-      </c>
-      <c r="F194" s="2" t="n">
-        <v>46146</v>
+        <v>90</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_3x_52_25_item</t>
+          <t>roof_aluminum_pressure_rail_m</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
+          <t>Плоская кровля</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>Рейка краевая, 2 м</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>пог. м</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>95</v>
+      </c>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>roof_aluminum_edge_rail_m</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Плоская кровля</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>1146.91</v>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Плоская кровля</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Аэратор кровельный PVC, А75х375</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>587</v>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>roof_pvc_aerator_75x375_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="B195" t="inlineStr">
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>1</v>
+      </c>
+      <c r="E198" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>roof_crane_lifting_shift</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>1</v>
+      </c>
+      <c r="E199" t="n">
+        <v>3000</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>roof_internal_drain_pvc_110mm_m</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Пароизоляция основания плёнкой ПВХ</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>1</v>
+      </c>
+      <c r="E200" t="n">
+        <v>77</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>roof_vapor_barrier_installation_work_m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Монтаж примыкания кровли из ПВХ мембраны</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>1</v>
+      </c>
+      <c r="E201" t="n">
+        <v>700</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-02 по сверке эталонных смет: общее линейное примыкание кровли к парапетам/стенам/ВК считается в м.п.; отдельное примыкание к вентшахтам в шт остается optional legacy.</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>roof_pvc_membrane_abutment_work_m</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Монтаж примыкания к вентшахтам</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
+      </c>
+      <c r="E202" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H202" t="inlineStr">
+        <is>
+          <t>roof_vent_shaft_abutment_installation_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>1</v>
+      </c>
+      <c r="E203" t="n">
+        <v>5000</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>roof_internal_drain_with_heating_installation_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Установка аэратора кровельного PVC, А75х375</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
+        <v>1</v>
+      </c>
+      <c r="E204" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+        </is>
+      </c>
+      <c r="H204" t="inlineStr">
+        <is>
+          <t>roof_pvc_aerator_75x375_installation_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D205" t="n">
+        <v>1</v>
+      </c>
+      <c r="E205" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="F205" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D206" t="n">
+        <v>1</v>
+      </c>
+      <c r="E206" t="n">
+        <v>902.8</v>
+      </c>
+      <c r="F206" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>264</v>
+      </c>
+      <c r="F207" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D208" t="n">
+        <v>1</v>
+      </c>
+      <c r="E208" t="n">
+        <v>672</v>
+      </c>
+      <c r="F208" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D209" t="n">
+        <v>1</v>
+      </c>
+      <c r="E209" t="n">
+        <v>512.4</v>
+      </c>
+      <c r="F209" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
+        </is>
+      </c>
+      <c r="H209" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_2x_36_25_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D210" t="n">
+        <v>1</v>
+      </c>
+      <c r="E210" t="n">
+        <v>732</v>
+      </c>
+      <c r="F210" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
+        </is>
+      </c>
+      <c r="H210" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_3x_52_25_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>Доставка вентканалов (машина/транспорт, без разгрузки)</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="D211" t="n">
+        <v>1</v>
+      </c>
+      <c r="E211" t="n">
+        <v>15000</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>ИСПРАВЛЕНО 2026-08-06: было ошибочно затёрто на 2500 через устаревшее правило MANUAL_WORK_PRICE_CODES, которое мапило комбинированную строку 'Доставка+разгрузка' (2500) на этот материальный код - двойной счёт с schiedel_delivery_unloading_work. Реальное значение 15000 подтверждено на листе ЮСВ 'АЛ 06.04 КР1,КР2 (ЕЧ) (ЮВ)', строка 235 'Доставка вентканалов': материал=15000, работа=2500 - оба параллельных блока колонок (левый/белый и правый/серый) сходятся на этой цифре, без разночтений.</t>
+        </is>
+      </c>
+      <c r="H211" t="inlineStr">
+        <is>
+          <t>schiedel_delivery_truck</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Доставка вентканалов, разгрузка вручную</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>маш</t>
+        </is>
+      </c>
+      <c r="D212" t="n">
+        <v>1</v>
+      </c>
+      <c r="E212" t="n">
+        <v>2500</v>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-06: этой строки нет в прайсе Елены отдельно (там доставка+разгрузка одной строкой = 2500) - ставка взята из реальной сметы ЮСВ, где разгрузка вручную идет отдельной строкой от доставки и стабильно равна 2500 руб./маш независимо от цены самой доставки (проверено в 2 разных листах ЮСВ: 2500/2500 и 15000/2500). По решению пользователя 2026-08-06 материал и работа считаются раздельно как более универсальный подход, а не совмещенной строкой как в АРК.</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>schiedel_delivery_unloading_work</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D213" t="n">
+        <v>1</v>
+      </c>
+      <c r="E213" t="n">
+        <v>268.4</v>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 27. h=330мм, габариты 200х250мм, вес 13кг, 63 шт на поддоне.</t>
+        </is>
+      </c>
+      <c r="H213" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_1x_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D214" t="n">
+        <v>1</v>
+      </c>
+      <c r="E214" t="n">
+        <v>902.8</v>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 30. h=330мм, габариты 500х360мм, вес 38кг, 16 шт на поддоне.</t>
+        </is>
+      </c>
+      <c r="H214" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_4x_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Вентканал CVENT 26х26 (канал + вентблок-спутник)</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D215" t="n">
+        <v>1</v>
+      </c>
+      <c r="E215" t="n">
+        <v>2663.2</v>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-06: было два кандидата на листе 'Блокпаротермшидель (Алексей)' прайса Елены - строка 33 'Вентблок CVENT 26*26 со спутником, 0.327' = 961.2 руб./шт и строка 34 'Вентиляционный канал Schiedel CVENT 500Х360Х327 26Х26' = 1702 руб./шт. Пользователь подтвердила 2026-08-06: это не два кандидата на один и тот же продукт, а два РАЗНЫХ компонента одного полного CVENT-узла (канал-модуль + его блок-спутник той же глубины 327мм) - берутся оба, цена = сумма 961.2 + 1702 = 2663.2 руб./шт. Калькулятор (CHANNEL_TYPE_SPECS['cvent'] в schiedel_vent_channels_calculator/calculator.py) хранит только ОДНУ цену на product_type=cvent, как и для 1x/2x/3x/4x - поэтому сумма зашита здесь одним числом, а не как два отдельных price_code; calculator.py не менялся. CVENT остаётся редкой строкой (Elena 2026-07-30: 'бывает достаточно редко'), ни один реальный проект её пока не использовал.</t>
+        </is>
+      </c>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_cvent_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
         <is>
           <t>Доставка вентканалов/ разгрузка в ручную на объекте</t>
         </is>
       </c>
-      <c r="C195" t="inlineStr">
+      <c r="C216" t="inlineStr">
         <is>
           <t>маш</t>
         </is>
       </c>
-      <c r="D195" t="n">
+      <c r="D216" t="n">
         <v>1</v>
       </c>
-      <c r="E195" t="inlineStr">
+      <c r="E216" t="inlineStr">
         <is>
           <t>2 500</t>
         </is>
       </c>
-      <c r="F195" t="inlineStr">
-        <is>
-          <t>2026-08-02</t>
-        </is>
-      </c>
-      <c r="G195" t="inlineStr">
-        <is>
-          <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1.0. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
-      </c>
-      <c r="H195" t="inlineStr">
-        <is>
-          <t>schiedel_delivery_truck</t>
-        </is>
-      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-08-07</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H216"/>
+  <dimension ref="A1:H217"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -504,7 +504,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -538,7 +538,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -572,7 +572,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Песок строительный</t>
+          <t>Перемещение песка вручную</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -712,19 +712,25 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1000</t>
+      <c r="D8" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 200 руб./м3 из ТРЦ (лист 'НС 29.06.26', строка 32), но это была ЛЕВАЯ/белая (клиентская) колонка. Правая/серая (реальная внутренняя себестоимость) колонка для этой же строки = 0. См. подробное объяснение серая/белая структура в комментарии к timber_formwork_installation_work_m2 выше - тот же класс ошибки. Пользователь подтвердила 2026-08-06: 0 верно, работа не тарифицируется отдельно внутри.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>sand_m3</t>
+          <t>sand_manual_moving_m3</t>
         </is>
       </c>
     </row>
@@ -736,7 +742,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Перемещение песка вручную</t>
+          <t>Песок строительный</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -748,59 +754,59 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>1400</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 200 руб./м3 из ТРЦ (лист 'НС 29.06.26', строка 32), но это была ЛЕВАЯ/белая (клиентская) колонка. Правая/серая (реальная внутренняя себестоимость) колонка для этой же строки = 0. См. подробное объяснение серая/белая структура в комментарии к timber_formwork_installation_work_m2 выше - тот же класс ошибки. Пользователь подтвердила 2026-08-06: 0 верно, работа не тарифицируется отдельно внутри.</t>
+          <t>ИСПРАВЛЕНО 2026-08-08: старое значение 1000 руб./м3 было непроверенным плейсхолдером (то же 'требуется проверка Елены' что и у formwork_consumables_m2). Реальная цена - в прайсе Елены на листе 'Бетон + песок' (строки 15-24), это ЗОНОВАЯ матрица по Москве и поставщикам: большинство зон (Евгений зоны 2-4, Алексей, Олег) = 1300 руб./м3 (20м3 машина), зона 1 (Евгений) = 1400 руб./м3. Взяла 1400 - это ровно та цена, что в реальной смете ТРЦ (строка 'Песок строительный' = 1400 руб./м3). Зонозависимость этот механизм не поддерживает - если у нового проекта другая зона/поставщик, значение нужно поправить здесь вручную, автоматически не подтянется.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>sand_manual_moving_m3</t>
+          <t>sand_m3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Земляные работы</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Закладка технологических входов коммуникаций до границы дома. Канализация, водоснабжение (ориентировочно)</t>
+          <t>Экскаватор-погрузчик JCB, аренда/материал (без работы)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D10" t="n">
         <v>1</v>
       </c>
       <c r="E10" t="n">
-        <v>350</v>
+        <v>26000</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 10. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Добавлено 2026-08-07: у 'Экскаватор-погрузчик JCB...' на первом листе прайса Елены только ОДНА цена (3500 руб./смена) - это цена РАБОТЫ (оператор), уже верно замаплена на excavator_jcb_shift. Материальной/арендной части (стоимость самого экскаватора) на первом листе нет вообще. Реальная ставка 26000 руб./смена подтверждена в 8+ независимых снимках реальных смет за несколько месяцев: ТРЦ (2026-06-29), АРК (2026-04-27), и ЮСВ на 8 разных листах/датах с 2026-02-19 по 2026-04-06 - везде одна и та же пара 26000 материал / 3500 работа для строки 'Механизированная разработка грунта, Экскаватор JCB'. До этой правки контракт (excavator_material_unit_price) ошибочно указывал на тот же registry_code, что и работа (excavator_jcb_shift), поэтому материал всегда дублировал цену работы (3500 вместо 26000).</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>communications_installation_m</t>
+          <t>excavator_jcb_shift_material</t>
         </is>
       </c>
     </row>
@@ -812,35 +818,33 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Экскаватор-погрузчик JCB (раскопка "корыта" под устройство дороги) /Контроль за механизированной разработкой грунта</t>
+          <t>Закладка технологических входов коммуникаций до границы дома. Канализация, водоснабжение (ориентировочно)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
+      <c r="E11" t="n">
+        <v>350</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 6. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 10. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>excavator_jcb_shift</t>
+          <t>communications_installation_m</t>
         </is>
       </c>
     </row>
@@ -852,33 +856,35 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Укладка геотекстиля</t>
+          <t>Экскаватор-погрузчик JCB (раскопка "корыта" под устройство дороги) /Контроль за механизированной разработкой грунта</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="n">
-        <v>35</v>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>3 500</t>
+        </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 8. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 6. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>geotextile_laying_m2</t>
+          <t>excavator_jcb_shift</t>
         </is>
       </c>
     </row>
@@ -890,33 +896,33 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Разработка грунта вручную (в т.ч. Копка траншей под коммуникации)</t>
+          <t>Укладка геотекстиля</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
       <c r="E13" t="n">
-        <v>1400</v>
+        <v>35</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 7. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 8. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>manual_excavation_m3</t>
+          <t>geotextile_laying_m2</t>
         </is>
       </c>
     </row>
@@ -928,7 +934,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Отсыпка дна котлована песком с трамбованием механизировано с применением виброплиты (коэф.упл. 1,3)</t>
+          <t>Разработка грунта вручную (в т.ч. Копка траншей под коммуникации)</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -940,33 +946,33 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 9. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 7. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>sand_filling_work_m3</t>
+          <t>manual_excavation_m3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 1</t>
+          <t>Отсыпка дна котлована песком с трамбованием механизировано с применением виброплиты (коэф.упл. 1,3)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -974,15 +980,25 @@
           <t>м3</t>
         </is>
       </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
       <c r="E15" t="n">
-        <v>7200</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>46154</v>
+        <v>1200</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Источник: первый лист нового прайса, строка 9. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>sand_filling_work_m3</t>
         </is>
       </c>
     </row>
@@ -994,7 +1010,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 1</t>
+          <t>Бетон B22.5 зона 1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1002,13 +1018,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
       <c r="E16" t="n">
-        <v>1000</v>
+        <v>7200</v>
       </c>
       <c r="F16" s="2" t="n">
         <v>46154</v>
@@ -1027,16 +1038,21 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 1</t>
+          <t>Доставка бетона B22.5 зона 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>44500</v>
+        <v>1000</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>46154</v>
@@ -1055,23 +1071,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 2</t>
+          <t>Насос 36м + гаситель зона 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6500</v>
+        <v>44500</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1099,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 2</t>
+          <t>Бетон B22.5 зона 2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1091,13 +1107,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
       <c r="E19" t="n">
-        <v>1100</v>
+        <v>6500</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>46154</v>
@@ -1116,16 +1127,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 2</t>
+          <t>Доставка бетона B22.5 зона 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>38000</v>
+        <v>1100</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>46154</v>
@@ -1144,20 +1160,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 3</t>
+          <t>Насос 36м + гаситель зона 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6500</v>
+        <v>38000</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1188,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 3</t>
+          <t>Бетон B22.5 зона 3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1177,13 +1196,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
       <c r="E22" t="n">
-        <v>750</v>
+        <v>6500</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1199,16 +1213,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 3</t>
+          <t>Доставка бетона B22.5 зона 3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>40000</v>
+        <v>750</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1224,23 +1243,20 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 4</t>
+          <t>Насос 36м + гаситель зона 3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6600</v>
-      </c>
-      <c r="F24" s="2" t="n">
-        <v>46154</v>
+        <v>40000</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1268,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 4</t>
+          <t>Бетон B22.5 зона 4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1260,13 +1276,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 8 м3</t>
-        </is>
-      </c>
       <c r="E25" t="n">
-        <v>1100</v>
+        <v>6600</v>
       </c>
       <c r="F25" s="2" t="n">
         <v>46154</v>
@@ -1285,16 +1296,21 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 4</t>
+          <t>Доставка бетона B22.5 зона 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 8 м3</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>45000</v>
+        <v>1100</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>46154</v>
@@ -1313,20 +1329,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 5</t>
+          <t>Насос 36м + гаситель зона 4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6150</v>
+        <v>45000</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1357,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 5</t>
+          <t>Бетон B22.5 зона 5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1346,13 +1365,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
       <c r="E28" t="n">
-        <v>900</v>
+        <v>6150</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1368,16 +1382,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 5</t>
+          <t>Доставка бетона B22.5 зона 5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>39500</v>
+        <v>900</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1393,20 +1412,20 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 6</t>
+          <t>Насос 36м + гаситель зона 5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6550</v>
+        <v>39500</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1437,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 6</t>
+          <t>Бетон B22.5 зона 6</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1426,13 +1445,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 8 м3</t>
-        </is>
-      </c>
       <c r="E31" t="n">
-        <v>950</v>
+        <v>6550</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1448,16 +1462,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 6</t>
+          <t>Доставка бетона B22.5 зона 6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 8 м3</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>40500</v>
+        <v>950</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1473,20 +1492,20 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 7</t>
+          <t>Насос 36м + гаситель зона 6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6550</v>
+        <v>40500</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1517,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 7</t>
+          <t>Бетон B22.5 зона 7</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1506,13 +1525,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 8 м3</t>
-        </is>
-      </c>
       <c r="E34" t="n">
-        <v>950</v>
+        <v>6550</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1528,16 +1542,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 7</t>
+          <t>Доставка бетона B22.5 зона 7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 8 м3</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>40500</v>
+        <v>950</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1553,20 +1572,20 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 8</t>
+          <t>Насос 36м + гаситель зона 7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>7690</v>
+        <v>40500</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1597,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 8</t>
+          <t>Бетон B22.5 зона 8</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1586,13 +1605,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 6 м3</t>
-        </is>
-      </c>
       <c r="E37" t="n">
-        <v>1400</v>
+        <v>7690</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1608,16 +1622,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 8</t>
+          <t>Доставка бетона B22.5 зона 8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 6 м3</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>48000</v>
+        <v>1400</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1628,30 +1647,25 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 1</t>
+          <t>Насос 36м + гаситель зона 8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>20 м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1400</v>
+        <v>48000</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1663,7 +1677,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 2</t>
+          <t>Песок 20м3 зона 1</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1677,7 +1691,7 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -1693,7 +1707,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 3</t>
+          <t>Песок 20м3 зона 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -1723,7 +1737,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 4</t>
+          <t>Песок 20м3 зона 3</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1753,7 +1767,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 5</t>
+          <t>Песок 20м3 зона 4</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1783,7 +1797,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 6</t>
+          <t>Песок 20м3 зона 5</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1813,7 +1827,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 7</t>
+          <t>Песок 20м3 зона 6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1843,7 +1857,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 8</t>
+          <t>Песок 20м3 зона 7</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1873,7 +1887,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона ГФК/ЛПК и т.д./А108</t>
+          <t>Песок 20м3 зона 8</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1898,12 +1912,12 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Бетонирование монолитной плиты перекрытия бетоном марки В22,5 (М300)</t>
+          <t>Песок 20м3 зона ГФК/ЛПК и т.д./А108</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1911,25 +1925,17 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D48" t="n">
-        <v>1</v>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>20 м3</t>
+        </is>
       </c>
       <c r="E48" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+        <v>1300</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>concrete_placing_work_m3</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1947,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Перенос, подъем бетона вручную</t>
+          <t>Бетонирование монолитной плиты перекрытия бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1952,24 +1958,22 @@
       <c r="D49" t="n">
         <v>1</v>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>5 000</t>
-        </is>
+      <c r="E49" t="n">
+        <v>12000</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>manual_concrete_lifting_m3</t>
+          <t>concrete_placing_work_m3</t>
         </is>
       </c>
     </row>
@@ -1981,65 +1985,73 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой до 250мм)</t>
+          <t>Перенос, подъем бетона вручную</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D50" t="n">
         <v>1</v>
       </c>
-      <c r="E50" t="n">
-        <v>1500</v>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>beam_concrete_placing_work_m</t>
+          <t>manual_concrete_lifting_m3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Бетон марки В22,5 (М300)</t>
+          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой до 250мм)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>6400.000000</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>1</v>
+      </c>
+      <c r="E51" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>concrete_b22_5_m3</t>
+          <t>beam_concrete_placing_work_m</t>
         </is>
       </c>
     </row>
@@ -2051,17 +2063,17 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Доставка бетона до объекта</t>
+          <t>Бетон марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>рейс</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>7500.000000</t>
+          <t>6400.000000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2071,7 +2083,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>concrete_delivery_trip</t>
+          <t>concrete_b22_5_m3</t>
         </is>
       </c>
     </row>
@@ -2083,27 +2095,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Работа бетононасоса 32м + гаситель</t>
+          <t>Доставка бетона до объекта</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>38000.000000</t>
+          <t>7500.000000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>concrete_pump_32m_shift</t>
+          <t>concrete_delivery_trip</t>
         </is>
       </c>
     </row>
@@ -2115,7 +2127,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Подача опалубки, арматуры автокраном</t>
+          <t>Работа бетононасоса 32м + гаситель</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2125,7 +2137,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>30000.000000</t>
+          <t>38000.000000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2135,7 +2147,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>crane_shift</t>
+          <t>concrete_pump_32m_shift</t>
         </is>
       </c>
     </row>
@@ -2147,17 +2159,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Экструдированный пенополистирол Пеноплэкс Основа 100х585х1185 мм</t>
+          <t>Подача опалубки, арматуры автокраном</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>9020.000000</t>
+          <t>30000.000000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2167,7 +2179,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>eps_penoplex_osnova_100_m3</t>
+          <t>crane_shift</t>
         </is>
       </c>
     </row>
@@ -2179,17 +2191,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Расходные материалы для установки опалубки (смазка; звездочки ПВХ, трубки)</t>
+          <t>Экструдированный пенополистирол Пеноплэкс Основа 100х585х1185 мм</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>9759.080000</t>
+          <t>9020.000000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2199,7 +2211,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>formwork_consumables_m2</t>
+          <t>eps_penoplex_osnova_100_m3</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2399,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -3634,7 +3646,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -3672,7 +3684,7 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -3710,7 +3722,7 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -3759,12 +3771,12 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Гидроизоляция</t>
+          <t>Устройство фундаментной плиты</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Утепление стен ЭППС 50мм, работа (ВРЕМЕННО 0 - ждет ответа Елены)</t>
+          <t>Расходные материалы для установки опалубки (смазка; звездочки ПВХ, трубки)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3776,33 +3788,33 @@
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>0</v>
+        <v>47</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ВРЕМЕННОЕ РЕШЕНИЕ 2026-08-06, требует уточнения у Елены: в смете ТРЦ утепление стен 50мм+100мм считается ОДНОЙ работой (680 руб./м2 на оба слоя сразу, лист 'НС 29.06.26' строка 73), а не двумя отдельными монтажными работами как в наших калькуляторах. АРК и ЮСВ вообще не имеют слоя 50мм на стенах (только 100мм), сверить не с чем. Поставлено 0, чтобы не задвоить деньги поверх уже существующей (возможно тоже неточной - см. eps_wall_insulation_work_m2) цены на монтаж 100мм-слоя. НЕ ИСПОЛЬЗОВАТЬ КАК ОКОНЧАТЕЛЬНОЕ ЗНАЧЕНИЕ - заменить, когда Елена ответит на вопрос от 2026-08-06 (один проход маляра на оба слоя или два отдельных).</t>
+          <t>ИСПРАВЛЕНО 2026-08-07: старое значение 9759.08 руб./м2 было непроверенным плейсхолдером (см. formwork_consumables_m2 в OBSOLETE_PREVIOUS_PRICE_CODES) - в 207 раз больше реальной цены, раздувало 'Расходные материалы для установки опалубки' на floor_slab_1/floor_slab_2 до ~1.2М/730К руб. на реальном проекте ТРЦ. Реальная ставка 47 руб./м2 подтверждена на 6 строках в 2 независимых проектах: ТРЦ (5556/118.218=47.0, 1404/29.875=47.0, 4307/91.6292=47.0, 1105/23.5=47.0) и АРК (15098/321.24=47.0, 4573/97.3=47.0) - везде площадь монтажа опалубки берётся из соседней строки того же раздела сметы.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>eps_wall_insulation_work_50_m2</t>
+          <t>formwork_consumables_m2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Гидроизоляция</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Устройство утепления низа плиты</t>
+          <t>Утепление стен ЭППС 50мм, работа (ВРЕМЕННО 0 - ждет ответа Елены)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3814,21 +3826,21 @@
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>900</v>
+        <v>0</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.</t>
+          <t>ВРЕМЕННОЕ РЕШЕНИЕ 2026-08-06, требует уточнения у Елены: в смете ТРЦ утепление стен 50мм+100мм считается ОДНОЙ работой (680 руб./м2 на оба слоя сразу, лист 'НС 29.06.26' строка 73), а не двумя отдельными монтажными работами как в наших калькуляторах. АРК и ЮСВ вообще не имеют слоя 50мм на стенах (только 100мм), сверить не с чем. Поставлено 0, чтобы не задвоить деньги поверх уже существующей (возможно тоже неточной - см. eps_wall_insulation_work_m2) цены на монтаж 100мм-слоя. НЕ ИСПОЛЬЗОВАТЬ КАК ОКОНЧАТЕЛЬНОЕ ЗНАЧЕНИЕ - заменить, когда Елена ответит на вопрос от 2026-08-06 (один проход маляра на оба слоя или два отдельных).</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>eps_bottom_slab_insulation_work_m2</t>
+          <t>eps_wall_insulation_work_50_m2</t>
         </is>
       </c>
     </row>
@@ -3840,7 +3852,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Утепление торца плиты ЭППС 100мм</t>
+          <t>Устройство утепления низа плиты</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3852,21 +3864,21 @@
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>500</v>
+        <v>900</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>eps_wall_insulation_work_m2</t>
+          <t>eps_bottom_slab_insulation_work_m2</t>
         </is>
       </c>
     </row>
@@ -3878,33 +3890,33 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовкладыша</t>
+          <t>Утепление торца плиты ЭППС 100мм</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D113" t="n">
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>thermal_insert_combined_installation_work_m</t>
+          <t>eps_wall_insulation_work_m2</t>
         </is>
       </c>
     </row>
@@ -3916,33 +3928,33 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
+          <t>Устройство и монтаж термовкладыша</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>770</v>
+        <v>100</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>roof_eps_insulation_installation_work_m2</t>
+          <t>thermal_insert_combined_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -3954,33 +3966,33 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 50 мм (для термовставок)</t>
+          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D115" t="n">
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>8800</v>
+        <v>770</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 43. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>thermal_insert_50_material_m3</t>
+          <t>roof_eps_insulation_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -3992,7 +4004,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 100 мм (для термовставок)</t>
+          <t>Пеноплэкс ГЕО 50 мм (для термовставок)</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -4004,21 +4016,21 @@
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 44. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 43. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>thermal_insert_100_material_m3</t>
+          <t>thermal_insert_50_material_m3</t>
         </is>
       </c>
     </row>
@@ -4030,33 +4042,33 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовставок 50 мм</t>
+          <t>Пеноплэкс ГЕО 100 мм (для термовставок)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>100</v>
+        <v>8900</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: новый прайс Елены содержит одну универсальную строку 'Устройство и монтаж термовкладыша' = 100 руб./мп. В реальных эталонных сметах АРК/ТРЦ/ЮСВ работа термовставок также считается по длине с этой ставкой; для production-раздельного режима 50/100 нужен отдельный price_code, поэтому цена размножена из той же универсальной строки прайса.</t>
+          <t>Источник: первый лист нового прайса, строка 44. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>thermal_insert_50_installation_work_m</t>
+          <t>thermal_insert_100_material_m3</t>
         </is>
       </c>
     </row>
@@ -4068,7 +4080,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовставок 100 мм</t>
+          <t>Устройство и монтаж термовставок 50 мм</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -4084,17 +4096,17 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: та же универсальная работа 'Устройство и монтаж термовкладыша' = 100 руб./мп из нового прайса Елены. Толщина слоя меняет материал, но не ставку монтажной работы по м.п.</t>
+          <t>Добавлено 2026-08-07: новый прайс Елены содержит одну универсальную строку 'Устройство и монтаж термовкладыша' = 100 руб./мп. В реальных эталонных сметах АРК/ТРЦ/ЮСВ работа термовставок также считается по длине с этой ставкой; для production-раздельного режима 50/100 нужен отдельный price_code, поэтому цена размножена из той же универсальной строки прайса.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>thermal_insert_100_installation_work_m</t>
+          <t>thermal_insert_50_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -4106,7 +4118,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовставок (произвольный типоразмер)</t>
+          <t>Устройство и монтаж термовставок 100 мм</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -4122,17 +4134,17 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: для режима thermal_insert_mode='items' калькулятор считает одну работу по суммарной длине всех термовставок произвольных типоразмеров. Ставка берется из той же универсальной строки нового прайса Елены 'Устройство и монтаж термовкладыша' = 100 руб./мп.</t>
+          <t>Добавлено 2026-08-07: та же универсальная работа 'Устройство и монтаж термовкладыша' = 100 руб./мп из нового прайса Елены. Толщина слоя меняет материал, но не ставку монтажной работы по м.п.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>thermal_insert_items_installation_work_m</t>
+          <t>thermal_insert_100_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -4144,63 +4156,71 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Материал термовставок (произвольный типоразмер)</t>
+          <t>Устройство и монтаж термовставок (произвольный типоразмер)</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D120" t="n">
         <v>1</v>
       </c>
       <c r="E120" t="n">
-        <v>8900</v>
+        <v>100</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: общий fallback для thermal_insert_items произвольного типоразмера. Новый прайс Елены дает Пеноплэкс ГЕО 100 мм (для термовставок) = 8900 руб./м3 и Пеноплэкс ГЕО 50 мм = 8800 руб./м3; для произвольных типоразмеров без отдельного толщинного price_code используем базовую цену 100 мм как более частый материал термовставок. Если в будущем появятся разные цены по eps_size, заменить на построчный price_code.</t>
+          <t>Добавлено 2026-08-07: для режима thermal_insert_mode='items' калькулятор считает одну работу по суммарной длине всех термовставок произвольных типоразмеров. Ставка берется из той же универсальной строки нового прайса Елены 'Устройство и монтаж термовкладыша' = 100 руб./мп.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>thermal_insert_item_material_m3</t>
+          <t>thermal_insert_items_installation_work_m</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Planter Standard Технониколь 40м2-1рул</t>
+          <t>Материал термовставок (произвольный типоразмер)</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>рул</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>4738</v>
+        <v>8900</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Добавлено 2026-08-07: общий fallback для thermal_insert_items произвольного типоразмера. Новый прайс Елены дает Пеноплэкс ГЕО 100 мм (для термовставок) = 8900 руб./м3 и Пеноплэкс ГЕО 50 мм = 8800 руб./м3; для произвольных типоразмеров без отдельного толщинного price_code используем базовую цену 100 мм как более частый материал термовставок. Если в будущем появятся разные цены по eps_size, заменить на построчный price_code.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>planter_standard_roll</t>
+          <t>thermal_insert_item_material_m3</t>
         </is>
       </c>
     </row>
@@ -4212,16 +4232,16 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PLANTERBAND 10м х 10см-1шт</t>
+          <t>Planter Standard Технониколь 40м2-1рул</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>рул</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>750</v>
+        <v>4738</v>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -4230,7 +4250,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>planterband_item</t>
+          <t>planter_standard_roll</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4262,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Праймер битумный AquaMast, 18 л-1шт</t>
+          <t>PLANTERBAND 10м х 10см-1шт</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -4251,7 +4271,7 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>2865</v>
+        <v>750</v>
       </c>
       <c r="G123" t="inlineStr">
         <is>
@@ -4260,7 +4280,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>bitumen_primer_aquamast_18l_item</t>
+          <t>planterband_item</t>
         </is>
       </c>
     </row>
@@ -4272,7 +4292,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
+          <t>Праймер битумный AquaMast, 18 л-1шт</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -4281,7 +4301,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2828.21</v>
+        <v>2865</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4290,7 +4310,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>bitumen_mastic_aquamast_18kg_item</t>
+          <t>bitumen_primer_aquamast_18l_item</t>
         </is>
       </c>
     </row>
@@ -4302,16 +4322,16 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
+          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>8800</v>
+        <v>2828.21</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4320,7 +4340,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>eps_geo_50_m3</t>
+          <t>bitumen_mastic_aquamast_18kg_item</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4352,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
+          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -4341,7 +4361,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>8900</v>
+        <v>8800</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4350,7 +4370,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>eps_geo_100_m3</t>
+          <t>eps_geo_50_m3</t>
         </is>
       </c>
     </row>
@@ -4362,16 +4382,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Клей-пена для ЭППС-1шт</t>
+          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>450</v>
+        <v>8900</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4380,7 +4400,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>eps_foam_glue_can</t>
+          <t>eps_geo_100_m3</t>
         </is>
       </c>
     </row>
@@ -4392,37 +4412,37 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
+          <t>Клей-пена для ЭППС-1шт</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>109</v>
+        <v>450</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
+          <t>Обновлено 04.05</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>geotextile_dornit_300_m2</t>
+          <t>eps_foam_glue_can</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
+          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4430,25 +4450,17 @@
           <t>м2</t>
         </is>
       </c>
-      <c r="D129" t="n">
-        <v>1</v>
-      </c>
       <c r="E129" t="n">
-        <v>350</v>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+        <v>109</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>bitumen_waterproofing_work_m2</t>
+          <t>geotextile_dornit_300_m2</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4472,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Монтаж мембраны PLANTER стандарт</t>
+          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4472,49 +4484,59 @@
         <v>1</v>
       </c>
       <c r="E130" t="n">
-        <v>100</v>
+        <v>350</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>planter_membrane_installation_work_m2</t>
+          <t>bitumen_waterproofing_work_m2</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Проволока</t>
+          <t>Монтаж мембраны PLANTER стандарт</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D131" t="n">
         <v>1</v>
       </c>
       <c r="E131" t="n">
-        <v>75</v>
+        <v>100</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
+          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>planter_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -4526,26 +4548,23 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 25 мм</t>
+          <t>Проволока</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>1п.м</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.7</v>
+        <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>155.8</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>46214</v>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>rebar_a500_d25_m</t>
+        <v>75</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
         </is>
       </c>
     </row>
@@ -4557,7 +4576,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 20мм</t>
+          <t>Арматура класса А500 диаметром 25 мм</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4569,19 +4588,14 @@
         <v>11.7</v>
       </c>
       <c r="E133" t="n">
-        <v>100.25</v>
+        <v>155.8</v>
       </c>
       <c r="F133" s="2" t="n">
         <v>46214</v>
       </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
-        </is>
-      </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>rebar_a500_d20_m</t>
+          <t>rebar_a500_d25_m</t>
         </is>
       </c>
     </row>
@@ -4593,7 +4607,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 16 мм</t>
+          <t>Арматура класса А500 диаметром 20мм</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4605,14 +4619,19 @@
         <v>11.7</v>
       </c>
       <c r="E134" t="n">
-        <v>64.90000000000001</v>
+        <v>100.25</v>
       </c>
       <c r="F134" s="2" t="n">
         <v>46214</v>
       </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
+        </is>
+      </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>rebar_a500_d16_m</t>
+          <t>rebar_a500_d20_m</t>
         </is>
       </c>
     </row>
@@ -4624,7 +4643,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 12мм</t>
+          <t>Арматура класса А500 диаметром 16 мм</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4636,14 +4655,14 @@
         <v>11.7</v>
       </c>
       <c r="E135" t="n">
-        <v>36.85</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>rebar_a500_d12_m</t>
+          <t>rebar_a500_d16_m</t>
         </is>
       </c>
     </row>
@@ -4655,7 +4674,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 10 мм</t>
+          <t>Арматура класса А500 диаметром 12мм</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4667,14 +4686,14 @@
         <v>11.7</v>
       </c>
       <c r="E136" t="n">
-        <v>27.16</v>
+        <v>36.85</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>rebar_a500_d10_m</t>
+          <t>rebar_a500_d12_m</t>
         </is>
       </c>
     </row>
@@ -4686,7 +4705,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 8 мм</t>
+          <t>Арматура класса А500 диаметром 10 мм</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4698,14 +4717,14 @@
         <v>11.7</v>
       </c>
       <c r="E137" t="n">
-        <v>18.5</v>
+        <v>27.16</v>
       </c>
       <c r="F137" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>rebar_a240_d8_m</t>
+          <t>rebar_a500_d10_m</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4736,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 6 мм</t>
+          <t>Арматура класса А240 диаметром 8 мм</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4729,47 +4748,45 @@
         <v>11.7</v>
       </c>
       <c r="E138" t="n">
-        <v>10.25</v>
+        <v>18.5</v>
       </c>
       <c r="F138" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>rebar_a240_d6_m</t>
+          <t>rebar_a240_d8_m</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Блок D 400</t>
+          <t>Арматура класса А240 диаметром 6 мм</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D139" t="inlineStr">
-        <is>
-          <t>34,56 м3</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>11.7</v>
       </c>
       <c r="E139" t="n">
-        <v>5900</v>
+        <v>10.25</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+        <v>46214</v>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>rebar_a240_d6_m</t>
         </is>
       </c>
     </row>
@@ -4781,7 +4798,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Блок D 500</t>
+          <t>Блок D 400</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4791,18 +4808,18 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>32,4 м3</t>
+          <t>34,56 м3</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5200</v>
+        <v>5900</v>
       </c>
       <c r="F140" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4831,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Блок D 400</t>
+          <t>Блок D 500</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4824,18 +4841,18 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>1,8 м3</t>
+          <t>32,4 м3</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>6300</v>
+        <v>5200</v>
       </c>
       <c r="F141" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4864,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Блок D 500</t>
+          <t>Блок D 400</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4861,7 +4878,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5800</v>
+        <v>6300</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>46146</v>
@@ -4880,101 +4897,102 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Блок D 500</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>1,8 м3</t>
+        </is>
       </c>
       <c r="E143" t="n">
-        <v>360</v>
+        <v>5800</v>
       </c>
       <c r="F143" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>block_adhesive_bag</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Кровля</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Воронка парапетная с листвоуловителем (материал)</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мешок 25 кг</t>
         </is>
       </c>
       <c r="D144" t="n">
         <v>1</v>
       </c>
       <c r="E144" t="n">
-        <v>6001.23</v>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+        <v>360</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: та же причина, что и у внутренней воронки - материалы не читаются автоматическим скриптом, цена взята напрямую из листа 'Утеплителипленкимастика (Олег)', строка 31 ('Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650') = 6001.23 руб./шт. До этой правки код ошибочно получал цену РАБОТЫ монтажа (5000 руб.) через устаревшее сопоставление в MANUAL_WORK_PRICE_CODES - реальная цена материала выше, это была настоящая ошибка в деньгах, не совпадение.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>roof_parapet_drain_item</t>
+          <t>block_adhesive_bag</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Доставка блоков, смеси</t>
+          <t>Воронка парапетная с листвоуловителем (материал)</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>28000</t>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>1</v>
+      </c>
+      <c r="E145" t="n">
+        <v>6001.23</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Добавлено 2026-08-06: та же причина, что и у внутренней воронки - материалы не читаются автоматическим скриптом, цена взята напрямую из листа 'Утеплителипленкимастика (Олег)', строка 31 ('Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650') = 6001.23 руб./шт. До этой правки код ошибочно получал цену РАБОТЫ монтажа (5000 руб.) через устаревшее сопоставление в MANUAL_WORK_PRICE_CODES - реальная цена материала выше, это была настоящая ошибка в деньгах, не совпадение.</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>block_delivery_truck</t>
+          <t>roof_parapet_drain_item</t>
         </is>
       </c>
     </row>
@@ -4986,7 +5004,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Разгрузка блоков, смеси манипулятором</t>
+          <t>Доставка блоков, смеси</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4996,7 +5014,7 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>15000</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -5006,7 +5024,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>block_unloading_manipulator_truck</t>
+          <t>block_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -5018,17 +5036,17 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Газобетонный блок D400 600x400x250 мм</t>
+          <t>Разгрузка блоков, смеси манипулятором</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
@@ -5038,7 +5056,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>gas_block_d400_m3</t>
+          <t>block_unloading_manipulator_truck</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5068,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x150x250 мм</t>
+          <t>Газобетонный блок D400 600x400x250 мм</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -5060,7 +5078,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5070,7 +5088,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>gas_block_d500_150_m3</t>
+          <t>gas_block_d400_m3</t>
         </is>
       </c>
     </row>
@@ -5082,7 +5100,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x250x250 мм</t>
+          <t>Газобетонный блок D500 600x150x250 мм</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -5092,7 +5110,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5102,7 +5120,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>gas_block_d500_m3</t>
+          <t>gas_block_d500_150_m3</t>
         </is>
       </c>
     </row>
@@ -5114,17 +5132,17 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Пескобетон М300 40 кг</t>
+          <t>Газобетонный блок D500 600x250x250 мм</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>5500</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5134,38 +5152,39 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>sand_concrete_bag</t>
+          <t>gas_block_d500_m3</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Пескобетон М300 40 кг</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>1</v>
-      </c>
-      <c r="E151" t="n">
-        <v>659.77</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>46146</v>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>sand_concrete_bag</t>
         </is>
       </c>
     </row>
@@ -5177,26 +5196,26 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Сетка 5/0.4/100</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>рулон</t>
+          <t>мешок 25 кг</t>
         </is>
       </c>
       <c r="D152" t="n">
         <v>1</v>
       </c>
       <c r="E152" t="n">
-        <v>1304.63</v>
+        <v>659.77</v>
       </c>
       <c r="F152" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5208,7 +5227,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Сетка 5/0.5/100</t>
+          <t>Сетка 5/0.4/100</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -5220,7 +5239,7 @@
         <v>1</v>
       </c>
       <c r="E153" t="n">
-        <v>1729.38</v>
+        <v>1304.63</v>
       </c>
       <c r="F153" s="2" t="n">
         <v>46146</v>
@@ -5239,26 +5258,26 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>PTH 8</t>
+          <t>Сетка 5/0.5/100</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>рулон</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>100.62</v>
+        <v>1729.38</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5270,7 +5289,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PTH 12</t>
+          <t>PTH 8</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -5279,17 +5298,17 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="E155" t="n">
-        <v>150.62</v>
+        <v>100.62</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5301,7 +5320,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PTH 20</t>
+          <t>PTH 12</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -5310,17 +5329,17 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E156" t="n">
-        <v>171.17</v>
+        <v>150.62</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5332,7 +5351,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PTH 25М</t>
+          <t>PTH 20</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5341,17 +5360,17 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E157" t="n">
-        <v>180.89</v>
+        <v>171.17</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5363,7 +5382,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PTH 38</t>
+          <t>PTH 25М</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5375,7 +5394,7 @@
         <v>60</v>
       </c>
       <c r="E158" t="n">
-        <v>155.66</v>
+        <v>180.89</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>46146</v>
@@ -5394,7 +5413,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PTH 38 Termo</t>
+          <t>PTH 38</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5406,7 +5425,7 @@
         <v>60</v>
       </c>
       <c r="E159" t="n">
-        <v>201.14</v>
+        <v>155.66</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>46146</v>
@@ -5425,7 +5444,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PTH 44</t>
+          <t>PTH 38 Termo</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5434,17 +5453,17 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E160" t="n">
-        <v>176.58</v>
+        <v>201.14</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5456,7 +5475,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PTH 51</t>
+          <t>PTH 44</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5468,7 +5487,7 @@
         <v>50</v>
       </c>
       <c r="E161" t="n">
-        <v>225.53</v>
+        <v>176.58</v>
       </c>
       <c r="F161" s="2" t="n">
         <v>46146</v>
@@ -5482,38 +5501,31 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Гидроизоляция поверхности под первый ряд блоков</t>
+          <t>PTH 51</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E162" t="n">
-        <v>100</v>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+        <v>225.53</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr">
-        <is>
-          <t>cutoff_waterproofing_under_blocks_m2</t>
+          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5525,33 +5537,33 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
+          <t>Гидроизоляция поверхности под первый ряд блоков</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D163" t="n">
         <v>1</v>
       </c>
       <c r="E163" t="n">
-        <v>450</v>
+        <v>100</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>edge_insulation_work_m</t>
+          <t>cutoff_waterproofing_under_blocks_m2</t>
         </is>
       </c>
     </row>
@@ -5563,33 +5575,33 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Укладка ЭППС 50мм под плитой</t>
+          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D164" t="n">
         <v>1</v>
       </c>
       <c r="E164" t="n">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>eps_laying_work_m2</t>
+          <t>edge_insulation_work_m</t>
         </is>
       </c>
     </row>
@@ -5601,7 +5613,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
+          <t>Укладка ЭППС 50мм под плитой</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5612,24 +5624,22 @@
       <c r="D165" t="n">
         <v>1</v>
       </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>1 200</t>
-        </is>
+      <c r="E165" t="n">
+        <v>250</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>gas_block_cladding_work_m2</t>
+          <t>eps_laying_work_m2</t>
         </is>
       </c>
     </row>
@@ -5641,33 +5651,35 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Кладка парапета из газобетонных блоков</t>
+          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D166" t="n">
         <v>1</v>
       </c>
-      <c r="E166" t="n">
-        <v>7000</v>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>1 200</t>
+        </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>gas_block_masonry_work_m3</t>
+          <t>gas_block_cladding_work_m2</t>
         </is>
       </c>
     </row>
@@ -5679,33 +5691,33 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
+          <t>Кладка парапета из газобетонных блоков</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D167" t="n">
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>1200</v>
+        <v>7000</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>lintel_concreting_work_m</t>
+          <t>gas_block_masonry_work_m3</t>
         </is>
       </c>
     </row>
@@ -5717,35 +5729,33 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
+          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D168" t="n">
         <v>1</v>
       </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
+      <c r="E168" t="n">
+        <v>1200</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>scaffolding_setup_dismantling_work_set</t>
+          <t>lintel_concreting_work_m</t>
         </is>
       </c>
     </row>
@@ -5757,33 +5767,35 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Резка блока под перемычку (U-блок)</t>
+          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D169" t="n">
         <v>1</v>
       </c>
-      <c r="E169" t="n">
-        <v>400</v>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>u_block_lintel_cutting_item</t>
+          <t>scaffolding_setup_dismantling_work_set</t>
         </is>
       </c>
     </row>
@@ -5795,33 +5807,33 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
+          <t>Резка блока под перемычку (U-блок)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D170" t="n">
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>1500</v>
+        <v>400</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>lintel_monolithic_concreting_work_m</t>
+          <t>u_block_lintel_cutting_item</t>
         </is>
       </c>
     </row>
@@ -5833,33 +5845,33 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Укладка ПВХ Мембраны</t>
+          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>1</v>
       </c>
       <c r="E171" t="n">
-        <v>630</v>
+        <v>1500</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_installation_work_m2</t>
+          <t>lintel_monolithic_concreting_work_m</t>
         </is>
       </c>
     </row>
@@ -5871,33 +5883,33 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Установка воронки парапетной</t>
+          <t>Укладка ПВХ Мембраны</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D172" t="n">
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>5000</v>
+        <v>630</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>roof_parapet_drain_installation_item</t>
+          <t>roof_pvc_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -5909,12 +5921,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Кладка вентканалов Schiedel</t>
+          <t>Установка воронки парапетной</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -5925,17 +5937,17 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>schiedel_masonry_work_m</t>
+          <t>roof_parapet_drain_installation_item</t>
         </is>
       </c>
     </row>
@@ -5947,33 +5959,33 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Блок D400 (для кладки шахты вентканалов)</t>
+          <t>Кладка вентканалов Schiedel</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D174" t="n">
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>6100</v>
+        <v>5000</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 45. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>schiedel_masonry_gas_block_d400_m3</t>
+          <t>schiedel_masonry_work_m</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5997,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Блок D500 (для кладки шахты вентканалов)</t>
+          <t>Блок D400 (для кладки шахты вентканалов)</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5997,21 +6009,21 @@
         <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>5400</v>
+        <v>6100</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 46. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 45. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>schiedel_masonry_gas_block_d500_m3</t>
+          <t>schiedel_masonry_gas_block_d400_m3</t>
         </is>
       </c>
     </row>
@@ -6023,33 +6035,33 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Штробление блоков под дополнительное усиление, армирование арматурой диаметром 10 мм</t>
+          <t>Блок D500 (для кладки шахты вентканалов)</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D176" t="n">
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>250</v>
+        <v>5400</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07 по сверке АРК/ТРЦ/ЮСВ: в эталонных сметах это платная работа в правой части себестоимости. Временная production-ставка 250 руб./мп до отдельного подтверждения Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 46. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>block_chasing_reinforcement_work_m</t>
+          <t>schiedel_masonry_gas_block_d500_m3</t>
         </is>
       </c>
     </row>
@@ -6061,7 +6073,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
+          <t>Штробление блоков под дополнительное усиление, армирование арматурой диаметром 10 мм</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -6073,91 +6085,91 @@
         <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Добавлено по ответу Елены 2026-07-30: ставка такая же, как утепление балок и торца плиты.</t>
+          <t>Добавлено 2026-08-07 по сверке АРК/ТРЦ/ЮСВ: в эталонных сметах это платная работа в правой части себестоимости. Временная production-ставка 250 руб./мп до отдельного подтверждения Елены.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>lintel_edge_insulation_work_m</t>
+          <t>block_chasing_reinforcement_work_m</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
+          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>111.76</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>1</v>
+      </c>
+      <c r="E178" t="n">
+        <v>450</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: ставка такая же, как утепление балок и торца плиты.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>roof_geotextile_technonikol_prof_300_m2</t>
+          <t>lintel_edge_insulation_work_m</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Кровля</t>
+          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Воронка кровельная внутренняя с обогревом (материал)</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>1</v>
-      </c>
-      <c r="E179" t="n">
-        <v>5000</v>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>111.76</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: материалы не читаются автоматическим скриптом (только первый лист 'Прайс по видам работ', лист с материалами 'Утеплителипленкимастика (Олег)' сюда не входит) - цена 5000 руб./шт взята оттуда напрямую, строка 32 ('Воронка кровельная (с обжимным мет. фланцем с обогревом 110х450мм)'). До этой правки код случайно получал ту же цену через устаревшее (неверное) сопоставление с работой монтажа - см. исправление в MANUAL_WORK_PRICE_CODES выше. Цена совпала случайно (обе 5000), поэтому баг был незаметен.</t>
+          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>roof_internal_drain_with_heating_item</t>
+          <t>roof_geotextile_technonikol_prof_300_m2</t>
         </is>
       </c>
     </row>
@@ -6169,58 +6181,71 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>ПВХ мембрана Logicroof V-GR 1,5 мм (эксплуатируемая кровля)</t>
+          <t>Воронка кровельная внутренняя с обогревом (материал)</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>рул</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D180" t="n">
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>1146.91</v>
+        <v>5000</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: такая же цена, как у обычной V-RP мембраны (1146.91 руб./рул, прайс Елены лист 'Утеплителипленкимастика (Олег)' строка 29 - в прайсе V-GR и V-RP указаны с одинаковой ценой). Пользователь вписывал эту цену вручную в гугл-таблицу 2026-08-06 после того, как для ТРЦ впервые понадобилась V-GR (эксплуатируемая зона кровли) - перенесено в реестр, чтобы не терялось при пересборке.</t>
+          <t>Добавлено 2026-08-06: материалы не читаются автоматическим скриптом (только первый лист 'Прайс по видам работ', лист с материалами 'Утеплителипленкимастика (Олег)' сюда не входит) - цена 5000 руб./шт взята оттуда напрямую, строка 32 ('Воронка кровельная (с обжимным мет. фланцем с обогревом 110х450мм)'). До этой правки код случайно получал ту же цену через устаревшее (неверное) сопоставление с работой монтажа - см. исправление в MANUAL_WORK_PRICE_CODES выше. Цена совпала случайно (обе 5000), поэтому баг был незаметен.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_logicroof_vgr_1_5mm_gray_roll</t>
+          <t>roof_internal_drain_with_heating_item</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
+          <t>ПВХ мембрана Logicroof V-GR 1,5 мм (эксплуатируемая кровля)</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>рул</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>1</v>
       </c>
       <c r="E181" t="n">
-        <v>6610</v>
+        <v>1146.91</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Добавлено 2026-08-06: такая же цена, как у обычной V-RP мембраны (1146.91 руб./рул, прайс Елены лист 'Утеплителипленкимастика (Олег)' строка 29 - в прайсе V-GR и V-RP указаны с одинаковой ценой). Пользователь вписывал эту цену вручную в гугл-таблицу 2026-08-06 после того, как для ТРЦ впервые понадобилась V-GR (эксплуатируемая зона кровли) - перенесено в реестр, чтобы не терялось при пересборке.</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>roof_pvc_membrane_logicroof_vgr_1_5mm_gray_roll</t>
         </is>
       </c>
     </row>
@@ -6232,20 +6257,20 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
+          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E182" t="n">
-        <v>450</v>
+        <v>6610</v>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
@@ -6257,20 +6282,20 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
+          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E183" t="n">
-        <v>59.55</v>
+        <v>450</v>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
@@ -6282,16 +6307,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
+          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>6001.23</v>
+        <v>59.55</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -6307,7 +6332,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
+          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6316,7 +6341,7 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>2060</v>
+        <v>6001.23</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
@@ -6332,20 +6357,20 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
+          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
+        <v>2060</v>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
@@ -6357,25 +6382,20 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
+          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>7377.89</v>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
+        <v>23.12</v>
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>roof_eps100_technonikol_carbon_eco_m3</t>
+          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
         </is>
       </c>
     </row>
@@ -6387,7 +6407,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -6396,7 +6416,7 @@
         </is>
       </c>
       <c r="E188" t="n">
-        <v>7155.34</v>
+        <v>7377.89</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
@@ -6405,7 +6425,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>roof_eps50_technonikol_carbon_eco_m3</t>
+          <t>roof_eps100_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
@@ -6417,7 +6437,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -6426,7 +6446,7 @@
         </is>
       </c>
       <c r="E189" t="n">
-        <v>9888.67</v>
+        <v>7155.34</v>
       </c>
       <c r="G189" t="inlineStr">
         <is>
@@ -6435,7 +6455,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_a_m3</t>
+          <t>roof_eps50_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
@@ -6447,7 +6467,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6465,7 +6485,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_b_m3</t>
+          <t>roof_eps_slope_2_1_plate_a_m3</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6497,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6495,7 +6515,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>roof_eps_slope_4_2_plate_j_m3</t>
+          <t>roof_eps_slope_2_1_plate_b_m3</t>
         </is>
       </c>
     </row>
@@ -6507,7 +6527,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6525,7 +6545,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>roof_eps_slope_4_2_plate_k_m3</t>
+          <t>roof_eps_slope_4_2_plate_j_m3</t>
         </is>
       </c>
     </row>
@@ -6537,16 +6557,16 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E193" t="n">
-        <v>57.56</v>
+        <v>9888.67</v>
       </c>
       <c r="G193" t="inlineStr">
         <is>
@@ -6555,7 +6575,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>roof_geotextile_technonikol_prof_150_m2</t>
+          <t>roof_eps_slope_4_2_plate_k_m3</t>
         </is>
       </c>
     </row>
@@ -6567,16 +6587,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Рейка прижимная, 2 м</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>пог. м</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>90</v>
+        <v>57.56</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -6585,7 +6605,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>roof_aluminum_pressure_rail_m</t>
+          <t>roof_geotextile_technonikol_prof_150_m2</t>
         </is>
       </c>
     </row>
@@ -6597,7 +6617,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Рейка краевая, 2 м</t>
+          <t>Рейка прижимная, 2 м</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -6606,7 +6626,7 @@
         </is>
       </c>
       <c r="E195" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -6615,7 +6635,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>roof_aluminum_edge_rail_m</t>
+          <t>roof_aluminum_pressure_rail_m</t>
         </is>
       </c>
     </row>
@@ -6627,16 +6647,16 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
+          <t>Рейка краевая, 2 м</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>пог. м</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>1146.91</v>
+        <v>95</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -6645,7 +6665,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
+          <t>roof_aluminum_edge_rail_m</t>
         </is>
       </c>
     </row>
@@ -6657,58 +6677,50 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Аэратор кровельный PVC, А75х375</t>
+          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>587</v>
+        <v>1146.91</v>
+      </c>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>roof_pvc_aerator_75x375_item</t>
+          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
+          <t>Аэратор кровельный PVC, А75х375</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="D198" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E198" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F198" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G198" t="inlineStr">
-        <is>
-          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
-        </is>
+        <v>587</v>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>roof_crane_lifting_shift</t>
+          <t>roof_pvc_aerator_75x375_item</t>
         </is>
       </c>
     </row>
@@ -6720,33 +6732,33 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
+          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D199" t="n">
         <v>1</v>
       </c>
       <c r="E199" t="n">
-        <v>3000</v>
+        <v>15000</v>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>roof_internal_drain_pvc_110mm_m</t>
+          <t>roof_crane_lifting_shift</t>
         </is>
       </c>
     </row>
@@ -6758,33 +6770,33 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Пароизоляция основания плёнкой ПВХ</t>
+          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D200" t="n">
         <v>1</v>
       </c>
       <c r="E200" t="n">
-        <v>77</v>
+        <v>3000</v>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>roof_vapor_barrier_installation_work_m2</t>
+          <t>roof_internal_drain_pvc_110mm_m</t>
         </is>
       </c>
     </row>
@@ -6796,33 +6808,33 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Монтаж примыкания кровли из ПВХ мембраны</t>
+          <t>Пароизоляция основания плёнкой ПВХ</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D201" t="n">
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>700</v>
+        <v>77</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-02 по сверке эталонных смет: общее линейное примыкание кровли к парапетам/стенам/ВК считается в м.п.; отдельное примыкание к вентшахтам в шт остается optional legacy.</t>
+          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_abutment_work_m</t>
+          <t>roof_vapor_barrier_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -6834,33 +6846,33 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Монтаж примыкания к вентшахтам</t>
+          <t>Монтаж примыкания кровли из ПВХ мембраны</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D202" t="n">
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Добавлено 2026-08-02 по сверке эталонных смет: общее линейное примыкание кровли к парапетам/стенам/ВК считается в м.п.; отдельное примыкание к вентшахтам в шт остается optional legacy.</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>roof_vent_shaft_abutment_installation_item</t>
+          <t>roof_pvc_membrane_abutment_work_m</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6884,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
+          <t>Монтаж примыкания к вентшахтам</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -6888,17 +6900,17 @@
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>roof_internal_drain_with_heating_installation_item</t>
+          <t>roof_vent_shaft_abutment_installation_item</t>
         </is>
       </c>
     </row>
@@ -6910,7 +6922,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Установка аэратора кровельного PVC, А75х375</t>
+          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -6922,33 +6934,33 @@
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>roof_pvc_aerator_75x375_installation_item</t>
+          <t>roof_internal_drain_with_heating_installation_item</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+          <t>Установка аэратора кровельного PVC, А75х375</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6960,14 +6972,21 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>268.4</v>
-      </c>
-      <c r="F205" s="2" t="n">
-        <v>46146</v>
+        <v>2500</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+        </is>
+      </c>
+      <c r="H205" t="inlineStr">
+        <is>
+          <t>roof_pvc_aerator_75x375_installation_item</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6998,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -6991,14 +7010,14 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>902.8</v>
+        <v>268.4</v>
       </c>
       <c r="F206" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7010,7 +7029,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7022,14 +7041,14 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>264</v>
+        <v>902.8</v>
       </c>
       <c r="F207" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7060,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
+          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7053,7 +7072,7 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>672</v>
+        <v>264</v>
       </c>
       <c r="F208" s="2" t="n">
         <v>46146</v>
@@ -7072,7 +7091,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
+          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7084,19 +7103,14 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>512.4</v>
+        <v>672</v>
       </c>
       <c r="F209" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>schiedel_vent_channel_2x_36_25_item</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7108,7 +7122,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
+          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7120,19 +7134,19 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>732</v>
+        <v>512.4</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
+          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_3x_52_25_item</t>
+          <t>schiedel_vent_channel_2x_36_25_item</t>
         </is>
       </c>
     </row>
@@ -7144,33 +7158,31 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Доставка вентканалов (машина/транспорт, без разгрузки)</t>
+          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D211" t="n">
         <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F211" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
+        <v>732</v>
+      </c>
+      <c r="F211" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: было ошибочно затёрто на 2500 через устаревшее правило MANUAL_WORK_PRICE_CODES, которое мапило комбинированную строку 'Доставка+разгрузка' (2500) на этот материальный код - двойной счёт с schiedel_delivery_unloading_work. Реальное значение 15000 подтверждено на листе ЮСВ 'АЛ 06.04 КР1,КР2 (ЕЧ) (ЮВ)', строка 235 'Доставка вентканалов': материал=15000, работа=2500 - оба параллельных блока колонок (левый/белый и правый/серый) сходятся на этой цифре, без разночтений.</t>
+          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>schiedel_delivery_truck</t>
+          <t>schiedel_vent_channel_3x_52_25_item</t>
         </is>
       </c>
     </row>
@@ -7182,7 +7194,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Доставка вентканалов, разгрузка вручную</t>
+          <t>Доставка вентканалов (машина/транспорт, без разгрузки)</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -7194,21 +7206,21 @@
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>2500</v>
+        <v>15000</v>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: этой строки нет в прайсе Елены отдельно (там доставка+разгрузка одной строкой = 2500) - ставка взята из реальной сметы ЮСВ, где разгрузка вручную идет отдельной строкой от доставки и стабильно равна 2500 руб./маш независимо от цены самой доставки (проверено в 2 разных листах ЮСВ: 2500/2500 и 15000/2500). По решению пользователя 2026-08-06 материал и работа считаются раздельно как более универсальный подход, а не совмещенной строкой как в АРК.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: было ошибочно затёрто на 2500 через устаревшее правило MANUAL_WORK_PRICE_CODES, которое мапило комбинированную строку 'Доставка+разгрузка' (2500) на этот материальный код - двойной счёт с schiedel_delivery_unloading_work. Реальное значение 15000 подтверждено на листе ЮСВ 'АЛ 06.04 КР1,КР2 (ЕЧ) (ЮВ)', строка 235 'Доставка вентканалов': материал=15000, работа=2500 - оба параллельных блока колонок (левый/белый и правый/серый) сходятся на этой цифре, без разночтений.</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>schiedel_delivery_unloading_work</t>
+          <t>schiedel_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -7220,33 +7232,33 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+          <t>Доставка вентканалов, разгрузка вручную</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="D213" t="n">
         <v>1</v>
       </c>
       <c r="E213" t="n">
-        <v>268.4</v>
+        <v>2500</v>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 27. h=330мм, габариты 200х250мм, вес 13кг, 63 шт на поддоне.</t>
+          <t>Добавлено 2026-08-06: этой строки нет в прайсе Елены отдельно (там доставка+разгрузка одной строкой = 2500) - ставка взята из реальной сметы ЮСВ, где разгрузка вручную идет отдельной строкой от доставки и стабильно равна 2500 руб./маш независимо от цены самой доставки (проверено в 2 разных листах ЮСВ: 2500/2500 и 15000/2500). По решению пользователя 2026-08-06 материал и работа считаются раздельно как более универсальный подход, а не совмещенной строкой как в АРК.</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_1x_item</t>
+          <t>schiedel_delivery_unloading_work</t>
         </is>
       </c>
     </row>
@@ -7258,7 +7270,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -7270,21 +7282,21 @@
         <v>1</v>
       </c>
       <c r="E214" t="n">
-        <v>902.8</v>
+        <v>268.4</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 30. h=330мм, габариты 500х360мм, вес 38кг, 16 шт на поддоне.</t>
+          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 27. h=330мм, габариты 200х250мм, вес 13кг, 63 шт на поддоне.</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_4x_item</t>
+          <t>schiedel_vent_channel_1x_item</t>
         </is>
       </c>
     </row>
@@ -7296,7 +7308,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Вентканал CVENT 26х26 (канал + вентблок-спутник)</t>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -7308,59 +7320,97 @@
         <v>1</v>
       </c>
       <c r="E215" t="n">
-        <v>2663.2</v>
+        <v>902.8</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: было два кандидата на листе 'Блокпаротермшидель (Алексей)' прайса Елены - строка 33 'Вентблок CVENT 26*26 со спутником, 0.327' = 961.2 руб./шт и строка 34 'Вентиляционный канал Schiedel CVENT 500Х360Х327 26Х26' = 1702 руб./шт. Пользователь подтвердила 2026-08-06: это не два кандидата на один и тот же продукт, а два РАЗНЫХ компонента одного полного CVENT-узла (канал-модуль + его блок-спутник той же глубины 327мм) - берутся оба, цена = сумма 961.2 + 1702 = 2663.2 руб./шт. Калькулятор (CHANNEL_TYPE_SPECS['cvent'] в schiedel_vent_channels_calculator/calculator.py) хранит только ОДНУ цену на product_type=cvent, как и для 1x/2x/3x/4x - поэтому сумма зашита здесь одним числом, а не как два отдельных price_code; calculator.py не менялся. CVENT остаётся редкой строкой (Elena 2026-07-30: 'бывает достаточно редко'), ни один реальный проект её пока не использовал.</t>
+          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 30. h=330мм, габариты 500х360мм, вес 38кг, 16 шт на поддоне.</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_cvent_item</t>
+          <t>schiedel_vent_channel_4x_item</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Вентканал CVENT 26х26 (канал + вентблок-спутник)</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D216" t="n">
+        <v>1</v>
+      </c>
+      <c r="E216" t="n">
+        <v>2663.2</v>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-06: было два кандидата на листе 'Блокпаротермшидель (Алексей)' прайса Елены - строка 33 'Вентблок CVENT 26*26 со спутником, 0.327' = 961.2 руб./шт и строка 34 'Вентиляционный канал Schiedel CVENT 500Х360Х327 26Х26' = 1702 руб./шт. Пользователь подтвердила 2026-08-06: это не два кандидата на один и тот же продукт, а два РАЗНЫХ компонента одного полного CVENT-узла (канал-модуль + его блок-спутник той же глубины 327мм) - берутся оба, цена = сумма 961.2 + 1702 = 2663.2 руб./шт. Калькулятор (CHANNEL_TYPE_SPECS['cvent'] в schiedel_vent_channels_calculator/calculator.py) хранит только ОДНУ цену на product_type=cvent, как и для 1x/2x/3x/4x - поэтому сумма зашита здесь одним числом, а не как два отдельных price_code; calculator.py не менялся. CVENT остаётся редкой строкой (Elena 2026-07-30: 'бывает достаточно редко'), ни один реальный проект её пока не использовал.</t>
+        </is>
+      </c>
+      <c r="H216" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_cvent_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="B216" t="inlineStr">
+      <c r="B217" t="inlineStr">
         <is>
           <t>Доставка вентканалов/ разгрузка в ручную на объекте</t>
         </is>
       </c>
-      <c r="C216" t="inlineStr">
+      <c r="C217" t="inlineStr">
         <is>
           <t>маш</t>
         </is>
       </c>
-      <c r="D216" t="n">
-        <v>1</v>
-      </c>
-      <c r="E216" t="inlineStr">
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="inlineStr">
         <is>
           <t>2 500</t>
         </is>
       </c>
-      <c r="F216" t="inlineStr">
-        <is>
-          <t>2026-08-07</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
         <is>
           <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
-      <c r="H216" t="inlineStr"/>
+      <c r="H217" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H217"/>
+  <dimension ref="A1:H219"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -813,24 +813,24 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Земляные работы</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Закладка технологических входов коммуникаций до границы дома. Канализация, водоснабжение (ориентировочно)</t>
+          <t>Пиломатериал обрезной для устройства опалубки ГОСТ</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>350</v>
+        <v>21500</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -839,12 +839,12 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 10. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>ИСПРАВЛЕНО 2026-08-08: старое значение 21499.997319 не было ошибкой по сути (подтверждено по смете АРК - там та же позиция 21500 руб./м3), но само число было 'Добавлено из калькулятора MVP' - какой-то старый расчёт цена_доски/объём_доски, никогда не бывшее настоящей строкой прайса, с некрасивым хвостом из 6 знаков после запятой. Округлила до чистых 21500 - число то же самое по сути, просто без мусора.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>communications_installation_m</t>
+          <t>timber_m3</t>
         </is>
       </c>
     </row>
@@ -856,21 +856,19 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Экскаватор-погрузчик JCB (раскопка "корыта" под устройство дороги) /Контроль за механизированной разработкой грунта</t>
+          <t>Закладка технологических входов коммуникаций до границы дома. Канализация, водоснабжение (ориентировочно)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>1</v>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>3 500</t>
-        </is>
+      <c r="E12" t="n">
+        <v>350</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -879,12 +877,12 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 6. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 10. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>excavator_jcb_shift</t>
+          <t>communications_installation_m</t>
         </is>
       </c>
     </row>
@@ -896,19 +894,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Укладка геотекстиля</t>
+          <t>Экскаватор-погрузчик JCB (раскопка "корыта" под устройство дороги) /Контроль за механизированной разработкой грунта</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D13" t="n">
         <v>1</v>
       </c>
-      <c r="E13" t="n">
-        <v>35</v>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>3 500</t>
+        </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -917,12 +917,12 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 8. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 6. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>geotextile_laying_m2</t>
+          <t>excavator_jcb_shift</t>
         </is>
       </c>
     </row>
@@ -934,19 +934,19 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Разработка грунта вручную (в т.ч. Копка траншей под коммуникации)</t>
+          <t>Укладка геотекстиля</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D14" t="n">
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1400</v>
+        <v>35</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -955,12 +955,12 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 7. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 8. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>manual_excavation_m3</t>
+          <t>geotextile_laying_m2</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Отсыпка дна котлована песком с трамбованием механизировано с применением виброплиты (коэф.упл. 1,3)</t>
+          <t>Разработка грунта вручную (в т.ч. Копка траншей под коммуникации)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -984,7 +984,7 @@
         <v>1</v>
       </c>
       <c r="E15" t="n">
-        <v>1200</v>
+        <v>1400</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -993,24 +993,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 9. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 7. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>sand_filling_work_m3</t>
+          <t>manual_excavation_m3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Бетон</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 1</t>
+          <t>Отсыпка дна котлована песком с трамбованием механизировано с применением виброплиты (коэф.упл. 1,3)</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1018,15 +1018,25 @@
           <t>м3</t>
         </is>
       </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
       <c r="E16" t="n">
-        <v>7200</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>46154</v>
+        <v>1200</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Источник: первый лист нового прайса, строка 9. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>sand_filling_work_m3</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1048,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 1</t>
+          <t>Бетон B22.5 зона 1</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1046,13 +1056,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
       <c r="E17" t="n">
-        <v>1000</v>
+        <v>7200</v>
       </c>
       <c r="F17" s="2" t="n">
         <v>46154</v>
@@ -1071,16 +1076,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 1</t>
+          <t>Доставка бетона B22.5 зона 1</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>44500</v>
+        <v>1000</v>
       </c>
       <c r="F18" s="2" t="n">
         <v>46154</v>
@@ -1099,23 +1109,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 2</t>
+          <t>Насос 36м + гаситель зона 1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6500</v>
+        <v>44500</v>
       </c>
       <c r="F19" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Оникс Бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1137,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 2</t>
+          <t>Бетон B22.5 зона 2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1135,13 +1145,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
       <c r="E20" t="n">
-        <v>1100</v>
+        <v>6500</v>
       </c>
       <c r="F20" s="2" t="n">
         <v>46154</v>
@@ -1160,16 +1165,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 2</t>
+          <t>Доставка бетона B22.5 зона 2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>38000</v>
+        <v>1100</v>
       </c>
       <c r="F21" s="2" t="n">
         <v>46154</v>
@@ -1188,20 +1198,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 3</t>
+          <t>Насос 36м + гаситель зона 2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6500</v>
+        <v>38000</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Росбетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1226,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 3</t>
+          <t>Бетон B22.5 зона 3</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1221,13 +1234,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
       <c r="E23" t="n">
-        <v>750</v>
+        <v>6500</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1243,16 +1251,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 3</t>
+          <t>Доставка бетона B22.5 зона 3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>40000</v>
+        <v>750</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1268,23 +1281,20 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 4</t>
+          <t>Насос 36м + гаситель зона 3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6600</v>
-      </c>
-      <c r="F25" s="2" t="n">
-        <v>46154</v>
+        <v>40000</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: РБУ 1 Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1306,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 4</t>
+          <t>Бетон B22.5 зона 4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1304,13 +1314,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 8 м3</t>
-        </is>
-      </c>
       <c r="E26" t="n">
-        <v>1100</v>
+        <v>6600</v>
       </c>
       <c r="F26" s="2" t="n">
         <v>46154</v>
@@ -1329,16 +1334,21 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 4</t>
+          <t>Доставка бетона B22.5 зона 4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 8 м3</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>45000</v>
+        <v>1100</v>
       </c>
       <c r="F27" s="2" t="n">
         <v>46154</v>
@@ -1357,20 +1367,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 5</t>
+          <t>Насос 36м + гаситель зона 4</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6150</v>
+        <v>45000</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1395,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 5</t>
+          <t>Бетон B22.5 зона 5</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1390,13 +1403,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 7 м3</t>
-        </is>
-      </c>
       <c r="E29" t="n">
-        <v>900</v>
+        <v>6150</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1412,16 +1420,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 5</t>
+          <t>Доставка бетона B22.5 зона 5</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 7 м3</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>39500</v>
+        <v>900</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1437,20 +1450,20 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 6</t>
+          <t>Насос 36м + гаситель зона 5</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6550</v>
+        <v>39500</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Куб Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1462,7 +1475,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 6</t>
+          <t>Бетон B22.5 зона 6</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1470,13 +1483,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 8 м3</t>
-        </is>
-      </c>
       <c r="E32" t="n">
-        <v>950</v>
+        <v>6550</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1492,16 +1500,21 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 6</t>
+          <t>Доставка бетона B22.5 зона 6</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 8 м3</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>40500</v>
+        <v>950</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1517,20 +1530,20 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 7</t>
+          <t>Насос 36м + гаситель зона 6</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6550</v>
+        <v>40500</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Гранд бетон/Гарант бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1555,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 7</t>
+          <t>Бетон B22.5 зона 7</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1550,13 +1563,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 8 м3</t>
-        </is>
-      </c>
       <c r="E35" t="n">
-        <v>950</v>
+        <v>6550</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1572,16 +1580,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 7</t>
+          <t>Доставка бетона B22.5 зона 7</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 8 м3</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>40500</v>
+        <v>950</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1597,20 +1610,20 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Бетон B22.5 зона 8</t>
+          <t>Насос 36м + гаситель зона 7</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>7690</v>
+        <v>40500</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
+          <t>Поставщик: Гарант бетон/Гранд бетон Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
@@ -1622,7 +1635,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Доставка бетона B22.5 зона 8</t>
+          <t>Бетон B22.5 зона 8</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1630,13 +1643,8 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Минимальный миксер 6 м3</t>
-        </is>
-      </c>
       <c r="E38" t="n">
-        <v>1400</v>
+        <v>7690</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1652,16 +1660,21 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Насос 36м + гаситель зона 8</t>
+          <t>Доставка бетона B22.5 зона 8</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Минимальный миксер 6 м3</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>48000</v>
+        <v>1400</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -1672,60 +1685,63 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Бетон</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 1</t>
+          <t>Насос 36м + гаситель зона 8</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>20 м3</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1400</v>
+        <v>48000</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>Поставщик: МЖБК/Забетоном Вариант поставщика/зоны. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для бетона, доставки и насоса.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Песок</t>
+          <t>Ж/Б монолитная плита перекрытия 2-го этажа</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 2</t>
+          <t>Работа бетононасоса (верхний уровень: 2-й этаж+) (ВРЕМЕННО - среднее по проектам)</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>20 м3</t>
-        </is>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1300</v>
+        <v>39833</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
+          <t>ВРЕМЕННО 2026-08-08: верхний уровень (2-й этаж и выше) - реально используется насос БОЛЬШЕГО размера, чем на фундаменте/1-м этаже (см. concrete_pump_32m_shift). ТРЦ='36м'=39500, АРК='40м'(плита перекрытия)=42000, ЮСВ='32м+гаситель'=38000 (не различает уровни) -&gt; среднее (39500+42000+38000)/3=39833.33, округлено до 39833. Новый registry_code, добавлен вместе с fixed 2026-08-08 разделением concrete_pump_32m_shift по разделам (было общее на все 3 раздела).</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>concrete_pump_32m_shift_floor_slab_2</t>
         </is>
       </c>
     </row>
@@ -1737,7 +1753,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 3</t>
+          <t>Песок 20м3 зона 1</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -1751,7 +1767,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1300</v>
+        <v>1400</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -1767,7 +1783,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 4</t>
+          <t>Песок 20м3 зона 2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -1797,7 +1813,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 5</t>
+          <t>Песок 20м3 зона 3</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -1827,7 +1843,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 6</t>
+          <t>Песок 20м3 зона 4</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1857,7 +1873,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 7</t>
+          <t>Песок 20м3 зона 5</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -1887,7 +1903,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона 8</t>
+          <t>Песок 20м3 зона 6</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -1917,7 +1933,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Песок 20м3 зона ГФК/ЛПК и т.д./А108</t>
+          <t>Песок 20м3 зона 7</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -1942,12 +1958,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Бетонирование монолитной плиты перекрытия бетоном марки В22,5 (М300)</t>
+          <t>Песок 20м3 зона 8</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1955,37 +1971,29 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D49" t="n">
-        <v>1</v>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>20 м3</t>
+        </is>
       </c>
       <c r="E49" t="n">
-        <v>12000</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>1300</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>concrete_placing_work_m3</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Песок</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Перенос, подъем бетона вручную</t>
+          <t>Песок 20м3 зона ГФК/ЛПК и т.д./А108</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -1993,27 +2001,17 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="D50" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>5 000</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>20 м3</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>1300</v>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>manual_concrete_lifting_m3</t>
+          <t>Вариант поставки по зоне. price_code не проставлен автоматически: нужно правило выбора зоны/поставщика для sand_m3.</t>
         </is>
       </c>
     </row>
@@ -2025,19 +2023,19 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой до 250мм)</t>
+          <t>Бетонирование монолитной плиты перекрытия бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D51" t="n">
         <v>1</v>
       </c>
       <c r="E51" t="n">
-        <v>1500</v>
+        <v>12000</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -2046,24 +2044,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 27. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>beam_concrete_placing_work_m</t>
+          <t>concrete_placing_work_m3</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Бетон марки В22,5 (М300)</t>
+          <t>Перенос, подъем бетона вручную</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2071,51 +2069,65 @@
           <t>м3</t>
         </is>
       </c>
+      <c r="D52" t="n">
+        <v>1</v>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6400.000000</t>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+          <t>Источник: первый лист нового прайса, строка 23. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>concrete_b22_5_m3</t>
+          <t>manual_concrete_lifting_m3</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Доставка бетона до объекта</t>
+          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой до 250мм)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>рейс</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>7500.000000</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>1</v>
+      </c>
+      <c r="E53" t="n">
+        <v>1500</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+          <t>Источник: первый лист нового прайса, строка 28. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>concrete_delivery_trip</t>
+          <t>beam_concrete_placing_work_m</t>
         </is>
       </c>
     </row>
@@ -2127,7 +2139,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Работа бетононасоса 32м + гаситель</t>
+          <t>Подача опалубки, арматуры автокраном</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2137,7 +2149,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>38000.000000</t>
+          <t>30000.000000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2147,7 +2159,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>concrete_pump_32m_shift</t>
+          <t>crane_shift</t>
         </is>
       </c>
     </row>
@@ -2159,17 +2171,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Подача опалубки, арматуры автокраном</t>
+          <t>Экструдированный пенополистирол Пеноплэкс Основа 100х585х1185 мм</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>смена</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>30000.000000</t>
+          <t>9020.000000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2179,7 +2191,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>crane_shift</t>
+          <t>eps_penoplex_osnova_100_m3</t>
         </is>
       </c>
     </row>
@@ -2191,17 +2203,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Экструдированный пенополистирол Пеноплэкс Основа 100х585х1185 мм</t>
+          <t>Доставка, вывоз опалубки манипулятором</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>9020.000000</t>
+          <t>20000.000000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2211,7 +2223,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>eps_penoplex_osnova_100_m3</t>
+          <t>formwork_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -2223,17 +2235,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Доставка, вывоз опалубки манипулятором</t>
+          <t>Комплект опалубки (телескопические стойки, унивилки, треноги, водостойкая фанера, поперечные и продольные балки двутавровые)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>20000.000000</t>
+          <t>600.000000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2243,7 +2255,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>formwork_delivery_truck</t>
+          <t>formwork_rental_m2</t>
         </is>
       </c>
     </row>
@@ -2255,17 +2267,17 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Комплект опалубки (телескопические стойки, унивилки, треноги, водостойкая фанера, поперечные и продольные балки двутавровые)</t>
+          <t>Доставка арматуры, металла</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>600.000000</t>
+          <t>22000.000000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2275,7 +2287,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>formwork_rental_m2</t>
+          <t>metal_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -2287,17 +2299,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Доставка арматуры, металла</t>
+          <t>Технический надзор</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>-</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>22000.000000</t>
+          <t>5000.000000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2307,7 +2319,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>metal_delivery_truck</t>
+          <t>technical_supervision_fixed</t>
         </is>
       </c>
     </row>
@@ -2319,27 +2331,33 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Технический надзор</t>
+          <t>Работа бетононасоса (нижний уровень: фундамент/1-й этаж) (ВРЕМЕННО - среднее по проектам)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>5000.000000</t>
+          <t>смена</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" t="n">
+        <v>37500</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>ВРЕМЕННО 2026-08-08: плита 1-го этажа заливается с той же высоты, что и фундамент - в ТРЦ и АРК используется насос того же (меньшего) размера, что для фундамента (см. concrete_pump_32m_shift). Та же группа проектных значений: ТРЦ='28м'=36500, АРК='36м'=38000, ЮСВ='32м+гаситель'=38000 -&gt; среднее 37500. Новый registry_code, добавлен вместе с fixed 2026-08-08 разделением concrete_pump_32m_shift по разделам (было общее на все 3 раздела: foundation_slab/floor_slab_1/floor_slab_2).</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>technical_supervision_fixed</t>
+          <t>concrete_pump_32m_shift_floor_slab_1</t>
         </is>
       </c>
     </row>
@@ -2351,7 +2369,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Пиломатериал обрезной для устройства опалубки ГОСТ</t>
+          <t>Пиломатериал обрезной для устройства опалубки ГОСТ (для опалубки монолитных перемычек)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2359,57 +2377,53 @@
           <t>м3</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>21499.997319</t>
+      <c r="D61" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" t="n">
+        <v>21500</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Добавлено 2026-08-06: та же цена, что и timber_m3 - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>timber_m3</t>
+          <t>lintel_formwork_timber_m3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Ж/Б монолитная плита перекрытия 1-го этажа</t>
+          <t>Пиломатериал</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Пиломатериал обрезной для устройства опалубки ГОСТ (для опалубки монолитных перемычек)</t>
+          <t>Доска обрезная 25х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D62" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E62" t="n">
-        <v>21499.997319</v>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>265</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>46154</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: та же цена, что и timber_m3 - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>lintel_formwork_timber_m3</t>
+          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
         </is>
       </c>
     </row>
@@ -2421,7 +2435,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Доска обрезная 25х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 25х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2430,7 +2444,7 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>265</v>
+        <v>397</v>
       </c>
       <c r="F63" s="2" t="n">
         <v>46154</v>
@@ -2449,7 +2463,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Доска обрезная 25х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 50х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2458,7 +2472,7 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>397</v>
+        <v>530</v>
       </c>
       <c r="F64" s="2" t="n">
         <v>46154</v>
@@ -2477,7 +2491,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 50х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2486,7 +2500,7 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>530</v>
+        <v>795</v>
       </c>
       <c r="F65" s="2" t="n">
         <v>46154</v>
@@ -2505,7 +2519,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная 50х200х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2514,7 +2528,7 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>795</v>
+        <v>1093</v>
       </c>
       <c r="F66" s="2" t="n">
         <v>46154</v>
@@ -2533,7 +2547,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Доска обрезная 50х200х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной 100х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2561,7 +2575,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Брус обрезной 100х100х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной 100х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2570,7 +2584,7 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1093</v>
+        <v>1590</v>
       </c>
       <c r="F68" s="2" t="n">
         <v>46154</v>
@@ -2589,7 +2603,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Брус обрезной 100х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной 150х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2598,7 +2612,7 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1590</v>
+        <v>2500</v>
       </c>
       <c r="F69" s="2" t="n">
         <v>46154</v>
@@ -2617,7 +2631,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Брус обрезной 150х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска сухая строганная 50х300х6000мм</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2626,7 +2640,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2500</v>
+        <v>3800</v>
       </c>
       <c r="F70" s="2" t="n">
         <v>46154</v>
@@ -2645,7 +2659,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 50х300х6000мм</t>
+          <t>Доска сухая строганная 20х90х6000мм</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2654,7 +2668,7 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3800</v>
+        <v>360</v>
       </c>
       <c r="F71" s="2" t="n">
         <v>46154</v>
@@ -2673,7 +2687,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 20х90х6000мм</t>
+          <t>Доска сухая строганная 20х140х6000мм</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2682,7 +2696,7 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>360</v>
+        <v>540</v>
       </c>
       <c r="F72" s="2" t="n">
         <v>46154</v>
@@ -2701,7 +2715,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 20х140х6000мм</t>
+          <t>Доска сухая строганная 45х90х6000мм</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2710,7 +2724,7 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>540</v>
+        <v>682</v>
       </c>
       <c r="F73" s="2" t="n">
         <v>46154</v>
@@ -2729,7 +2743,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х90х6000мм</t>
+          <t>Доска сухая строганная 45х140х6000мм</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2738,7 +2752,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>682</v>
+        <v>1022</v>
       </c>
       <c r="F74" s="2" t="n">
         <v>46154</v>
@@ -2757,7 +2771,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х140х6000мм</t>
+          <t>Доска сухая строганная 45х190х6000мм</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2766,7 +2780,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1022</v>
+        <v>1406</v>
       </c>
       <c r="F75" s="2" t="n">
         <v>46154</v>
@@ -2785,7 +2799,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Доска сухая строганная 45х190х6000мм</t>
+          <t>Брус сухой строганный 90х90х6000мм</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2813,7 +2827,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 90х90х6000мм</t>
+          <t>Брус сухой строганный 90х140х6000мм</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2822,7 +2836,7 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>1406</v>
+        <v>2045</v>
       </c>
       <c r="F77" s="2" t="n">
         <v>46154</v>
@@ -2841,7 +2855,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 90х140х6000мм</t>
+          <t>Брус сухой строганный 140х140х6000мм</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2850,7 +2864,7 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>2045</v>
+        <v>3214</v>
       </c>
       <c r="F78" s="2" t="n">
         <v>46154</v>
@@ -2869,7 +2883,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 140х140х6000мм</t>
+          <t>Брус сухой строганный 140х190х6000мм</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2878,7 +2892,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3214</v>
+        <v>4500</v>
       </c>
       <c r="F79" s="2" t="n">
         <v>46154</v>
@@ -2897,7 +2911,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 140х190х6000мм</t>
+          <t>Брус сухой строганный 50х50х3000мм</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2906,7 +2920,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4500</v>
+        <v>200</v>
       </c>
       <c r="F80" s="2" t="n">
         <v>46154</v>
@@ -2925,7 +2939,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 50х50х3000мм</t>
+          <t>Брус сухой строганный 45х45х3000мм</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2934,7 +2948,7 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>200</v>
+        <v>175</v>
       </c>
       <c r="F81" s="2" t="n">
         <v>46154</v>
@@ -2953,7 +2967,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 45х45х3000мм</t>
+          <t>Брус сухой строганный 40х50х3000мм</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2981,7 +2995,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Брус сухой строганный 40х50х3000мм</t>
+          <t>Доска обрезная с антисептированием 25х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2990,7 +3004,7 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>175</v>
+        <v>310</v>
       </c>
       <c r="F83" s="2" t="n">
         <v>46154</v>
@@ -3009,7 +3023,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 25х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 25х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3018,7 +3032,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>310</v>
+        <v>465</v>
       </c>
       <c r="F84" s="2" t="n">
         <v>46154</v>
@@ -3037,7 +3051,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 25х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 50х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3046,7 +3060,7 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>465</v>
+        <v>621</v>
       </c>
       <c r="F85" s="2" t="n">
         <v>46154</v>
@@ -3065,7 +3079,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 50х100х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием  50х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3074,7 +3088,7 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>621</v>
+        <v>931</v>
       </c>
       <c r="F86" s="2" t="n">
         <v>46154</v>
@@ -3093,7 +3107,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием  50х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска обрезная с антисептированием 50х200х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3102,7 +3116,7 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>931</v>
+        <v>1281</v>
       </c>
       <c r="F87" s="2" t="n">
         <v>46154</v>
@@ -3121,7 +3135,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Доска обрезная с антисептированием 50х200х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной с антисептированием 100х100х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3149,7 +3163,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 100х100х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной с антисептированием 100х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3158,7 +3172,7 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1281</v>
+        <v>1863</v>
       </c>
       <c r="F89" s="2" t="n">
         <v>46154</v>
@@ -3177,7 +3191,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 100х150х6000мм 1-сорт ГОСТ</t>
+          <t>Брус обрезной с антисептированием 150х150х6000мм 1-сорт ГОСТ</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3186,7 +3200,7 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1863</v>
+        <v>2928</v>
       </c>
       <c r="F90" s="2" t="n">
         <v>46154</v>
@@ -3205,7 +3219,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Брус обрезной с антисептированием 150х150х6000мм 1-сорт ГОСТ</t>
+          <t>Доска сухая строганная с антисептированием 50х300х6000мм</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3214,7 +3228,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>2928</v>
+        <v>4200</v>
       </c>
       <c r="F91" s="2" t="n">
         <v>46154</v>
@@ -3233,7 +3247,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 50х300х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 20х90х6000мм</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3242,7 +3256,7 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>4200</v>
+        <v>420</v>
       </c>
       <c r="F92" s="2" t="n">
         <v>46154</v>
@@ -3261,7 +3275,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 20х90х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 20х140х6000мм</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3270,7 +3284,7 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>420</v>
+        <v>620</v>
       </c>
       <c r="F93" s="2" t="n">
         <v>46154</v>
@@ -3289,7 +3303,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 20х140х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 45х90х6000мм</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3298,7 +3312,7 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>620</v>
+        <v>772</v>
       </c>
       <c r="F94" s="2" t="n">
         <v>46154</v>
@@ -3317,7 +3331,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х90х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 45х140х6000мм</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3326,7 +3340,7 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>772</v>
+        <v>1159</v>
       </c>
       <c r="F95" s="2" t="n">
         <v>46154</v>
@@ -3345,7 +3359,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х140х6000мм</t>
+          <t>Доска сухая строганная с антисептированием 45х190х6000мм</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3354,7 +3368,7 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1159</v>
+        <v>1593</v>
       </c>
       <c r="F96" s="2" t="n">
         <v>46154</v>
@@ -3373,7 +3387,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Доска сухая строганная с антисептированием 45х190х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 90х90х6000мм</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3401,7 +3415,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 90х90х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 90х140х6000мм</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3410,7 +3424,7 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1593</v>
+        <v>2318</v>
       </c>
       <c r="F98" s="2" t="n">
         <v>46154</v>
@@ -3429,7 +3443,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 90х140х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 140х140х6000мм</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3438,7 +3452,7 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2318</v>
+        <v>3642</v>
       </c>
       <c r="F99" s="2" t="n">
         <v>46154</v>
@@ -3457,7 +3471,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 140х140х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 140х190х6000мм</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3466,7 +3480,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3642</v>
+        <v>5100</v>
       </c>
       <c r="F100" s="2" t="n">
         <v>46154</v>
@@ -3485,7 +3499,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 140х190х6000мм</t>
+          <t>Брус сухой строганный с антисептированием 50х50х3000мм</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3494,7 +3508,7 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5100</v>
+        <v>270</v>
       </c>
       <c r="F101" s="2" t="n">
         <v>46154</v>
@@ -3513,7 +3527,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 50х50х3000мм</t>
+          <t>Брус сухой строганный с антисептированием 45х45х3000мм</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3522,7 +3536,7 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>270</v>
+        <v>220</v>
       </c>
       <c r="F102" s="2" t="n">
         <v>46154</v>
@@ -3541,7 +3555,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 45х45х3000мм</t>
+          <t>Брус сухой строганный с антисептированием 40х50х3000мм</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3569,7 +3583,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Брус сухой строганный с антисептированием 40х50х3000мм</t>
+          <t>Фанера 1,52х1,52*18</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3578,14 +3592,19 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220</v>
+        <v>1400</v>
       </c>
       <c r="F104" s="2" t="n">
         <v>46154</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Каталожная позиция поставщика. price_code добавляется только если калькулятор ссылается на эту конкретную номенклатуру.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>plywood_1520x1520_18mm_sheet</t>
         </is>
       </c>
     </row>
@@ -3597,52 +3616,57 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Фанера 1,52х1,52*18</t>
+          <t>Фанера 1,52х1,52*18 (для опалубки монолитных перемычек)</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
           <t>шт</t>
         </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
       </c>
       <c r="E105" t="n">
         <v>1400</v>
       </c>
-      <c r="F105" s="2" t="n">
-        <v>46154</v>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+          <t>Добавлено 2026-08-06: тот же лист фанеры, что и plywood_1520x1520_18mm_sheet (прайс Елены, лист 'Пиломатериалы (Олег)', строка 23) - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>plywood_1520x1520_18mm_sheet</t>
+          <t>lintel_formwork_plywood_sheet</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Пиломатериал</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Фанера 1,52х1,52*18 (для опалубки монолитных перемычек)</t>
+          <t>Монтаж опалубки из доски для отбортовки плиты</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D106" t="n">
         <v>1</v>
       </c>
       <c r="E106" t="n">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
@@ -3651,24 +3675,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: тот же лист фанеры, что и plywood_1520x1520_18mm_sheet (прайс Елены, лист 'Пиломатериалы (Олег)', строка 23) - отдельный price_code нужен калькулятору перемычек load_bearing_walls_lintels_calculator.py.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 580 руб./м2 из ТРЦ (лист 'НС 29.06.26', строка 42), но это была ЛЕВАЯ/белая (клиентская) колонка сметы. У каждой строки в реальных сметах два параллельных блока колонок - левый (белый, с накруткой для клиента) и правый (серый, настоящая внутренняя себестоимость Елены; в ТРЦ правый блок физически закрашен заливкой, в АРК/ЮСВ заливки нет, но структура та же и подтверждается арифметикой - левое/правое = Коэф-т Рентабельности листа, обычно 1.32). Правая/серая колонка для этой строки = 0 в ТРЦ. Пользователь подтвердила 2026-08-06: 0 - это реальный ответ, эта работа у Елены отдельно не тарифицируется внутри (входит в другую работу/бригадо-день), клиенту просто показывается отдельной строкой для формы.</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>lintel_formwork_plywood_sheet</t>
+          <t>timber_formwork_installation_work_m2</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Устройство фундаментной плиты</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Монтаж опалубки из доски для отбортовки плиты</t>
+          <t>Демонтаж опалубки после завершения бетонирования</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3689,12 +3713,12 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 580 руб./м2 из ТРЦ (лист 'НС 29.06.26', строка 42), но это была ЛЕВАЯ/белая (клиентская) колонка сметы. У каждой строки в реальных сметах два параллельных блока колонок - левый (белый, с накруткой для клиента) и правый (серый, настоящая внутренняя себестоимость Елены; в ТРЦ правый блок физически закрашен заливкой, в АРК/ЮСВ заливки нет, но структура та же и подтверждается арифметикой - левое/правое = Коэф-т Рентабельности листа, обычно 1.32). Правая/серая колонка для этой строки = 0 в ТРЦ. Пользователь подтвердила 2026-08-06: 0 - это реальный ответ, эта работа у Елены отдельно не тарифицируется внутри (входит в другую работу/бригадо-день), клиенту просто показывается отдельной строкой для формы.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 120 руб./м2 из АРК/ЮСВ (левая/белая колонка на нескольких строках 'Демонтаж опалубки после завершения бетонирования'). Проверила правую/серую колонку в АРК на тех же строках - везде 0. Тот же класс ошибки, что и timber_formwork_installation_work_m2/sand_manual_moving_m3 (см. их комментарии). Пользователь подтвердила 2026-08-06: 0 верно.</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>timber_formwork_installation_work_m2</t>
+          <t>formwork_dismantling_work_m2</t>
         </is>
       </c>
     </row>
@@ -3706,33 +3730,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Демонтаж опалубки после завершения бетонирования</t>
+          <t>Устройство и монтаж термовкладыша 150*400*250мм шаг 200мм</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>1</v>
-      </c>
-      <c r="E108" t="n">
-        <v>0</v>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>100</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: изначально взяла 120 руб./м2 из АРК/ЮСВ (левая/белая колонка на нескольких строках 'Демонтаж опалубки после завершения бетонирования'). Проверила правую/серую колонку в АРК на тех же строках - везде 0. Тот же класс ошибки, что и timber_formwork_installation_work_m2/sand_manual_moving_m3 (см. их комментарии). Пользователь подтвердила 2026-08-06: 0 верно.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>formwork_dismantling_work_m2</t>
+          <t>thermal_insert_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -3744,27 +3762,33 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовкладыша 150*400*250мм шаг 200мм</t>
+          <t>Расходные материалы для установки опалубки (смазка; звездочки ПВХ, трубки)</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>100</t>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>1</v>
+      </c>
+      <c r="E109" t="n">
+        <v>47</v>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>ИСПРАВЛЕНО 2026-08-07: старое значение 9759.08 руб./м2 было непроверенным плейсхолдером (см. formwork_consumables_m2 в OBSOLETE_PREVIOUS_PRICE_CODES) - в 207 раз больше реальной цены, раздувало 'Расходные материалы для установки опалубки' на floor_slab_1/floor_slab_2 до ~1.2М/730К руб. на реальном проекте ТРЦ. Реальная ставка 47 руб./м2 подтверждена на 6 строках в 2 независимых проектах: ТРЦ (5556/118.218=47.0, 1404/29.875=47.0, 4307/91.6292=47.0, 1105/23.5=47.0) и АРК (15098/321.24=47.0, 4573/97.3=47.0) - везде площадь монтажа опалубки берётся из соседней строки того же раздела сметы.</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>thermal_insert_installation_work_m</t>
+          <t>formwork_consumables_m2</t>
         </is>
       </c>
     </row>
@@ -3776,19 +3800,19 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Расходные материалы для установки опалубки (смазка; звездочки ПВХ, трубки)</t>
+          <t>Бетон марки В22,5 (М300) (ВРЕМЕННО - среднее по проектам, до внедрения зон)</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D110" t="n">
         <v>1</v>
       </c>
       <c r="E110" t="n">
-        <v>47</v>
+        <v>6275</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3797,36 +3821,36 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-07: старое значение 9759.08 руб./м2 было непроверенным плейсхолдером (см. formwork_consumables_m2 в OBSOLETE_PREVIOUS_PRICE_CODES) - в 207 раз больше реальной цены, раздувало 'Расходные материалы для установки опалубки' на floor_slab_1/floor_slab_2 до ~1.2М/730К руб. на реальном проекте ТРЦ. Реальная ставка 47 руб./м2 подтверждена на 6 строках в 2 независимых проектах: ТРЦ (5556/118.218=47.0, 1404/29.875=47.0, 4307/91.6292=47.0, 1105/23.5=47.0) и АРК (15098/321.24=47.0, 4573/97.3=47.0) - везде площадь монтажа опалубки берётся из соседней строки того же раздела сметы.</t>
+          <t>ВРЕМЕННО 2026-08-08: цена бетона зонозависима (актуальный прайс Елены даёт зоны 6150-7690 руб./м3), готового зонного механизма пока нет. Взято простое среднее по 2 реальным проектам: ТРЦ=6600, АРК=5950 -&gt; (6600+5950)/2=6275. Заменить, когда появится зонная логика или прямое указание, в какой зоне проект.</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>formwork_consumables_m2</t>
+          <t>concrete_b22_5_m3</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Гидроизоляция</t>
+          <t>Устройство фундаментной плиты</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Утепление стен ЭППС 50мм, работа (ВРЕМЕННО 0 - ждет ответа Елены)</t>
+          <t>Доставка бетона до объекта (ВРЕМЕННО - среднее по проектам)</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>рейс</t>
         </is>
       </c>
       <c r="D111" t="n">
         <v>1</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>6225</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
@@ -3835,36 +3859,36 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>ВРЕМЕННОЕ РЕШЕНИЕ 2026-08-06, требует уточнения у Елены: в смете ТРЦ утепление стен 50мм+100мм считается ОДНОЙ работой (680 руб./м2 на оба слоя сразу, лист 'НС 29.06.26' строка 73), а не двумя отдельными монтажными работами как в наших калькуляторах. АРК и ЮСВ вообще не имеют слоя 50мм на стенах (только 100мм), сверить не с чем. Поставлено 0, чтобы не задвоить деньги поверх уже существующей (возможно тоже неточной - см. eps_wall_insulation_work_m2) цены на монтаж 100мм-слоя. НЕ ИСПОЛЬЗОВАТЬ КАК ОКОНЧАТЕЛЬНОЕ ЗНАЧЕНИЕ - заменить, когда Елена ответит на вопрос от 2026-08-06 (один проход маляра на оба слоя или два отдельных).</t>
+          <t>ВРЕМЕННО 2026-08-08: та же зонозависимость, что у concrete_b22_5_m3. Актуальный прайс Елены даёт цену доставки ЗА М3 (не за рейс, единицы не совпадают с этим price_code), поэтому усреднила напрямую реальные рейсовые цены из 2 проектов: ТРЦ=7200, АРК=5250 -&gt; (7200+5250)/2=6225. Заменить, когда появится зонная логика.</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>eps_wall_insulation_work_50_m2</t>
+          <t>concrete_delivery_trip</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Устройство фундаментной плиты</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Устройство утепления низа плиты</t>
+          <t>Работа бетононасоса (нижний уровень: фундамент/1-й этаж) (ВРЕМЕННО - среднее по проектам)</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D112" t="n">
         <v>1</v>
       </c>
       <c r="E112" t="n">
-        <v>900</v>
+        <v>37500</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3873,24 +3897,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.</t>
+          <t>ВРЕМЕННО 2026-08-08: нашли реальную систему - размер/цена насоса зависит от высоты заливки, не от проекта. В ТРЦ и АРК фундамент+1й этаж используют насос МЕНЬШЕГО размера, чем 2й этаж+ (см. concrete_pump_32m_shift_floor_slab_2). ЮСВ не различает уровни (один насос везде) - закономерность реальная, но не универсальная. Нижний уровень: ТРЦ='28м'=36500, АРК='36м'(фундамент)=38000, ЮСВ='32м+гаситель'=38000 -&gt; среднее (36500+38000+38000)/3=37500. Раньше этот же код делился между foundation_slab/floor_slab_1/floor_slab_2 - теперь у каждого раздела свой code, см. floor_slab_1/floor_slab_2 контракты.</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>eps_bottom_slab_insulation_work_m2</t>
+          <t>concrete_pump_32m_shift</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Гидроизоляция</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Утепление торца плиты ЭППС 100мм</t>
+          <t>Утепление стен ЭППС 50мм, работа (ВРЕМЕННО 0 - ждет ответа Елены)</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3902,7 +3926,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3911,12 +3935,12 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>ВРЕМЕННОЕ РЕШЕНИЕ 2026-08-06, требует уточнения у Елены: в смете ТРЦ утепление стен 50мм+100мм считается ОДНОЙ работой (680 руб./м2 на оба слоя сразу, лист 'НС 29.06.26' строка 73), а не двумя отдельными монтажными работами как в наших калькуляторах. АРК и ЮСВ вообще не имеют слоя 50мм на стенах (только 100мм), сверить не с чем. Поставлено 0, чтобы не задвоить деньги поверх уже существующей (возможно тоже неточной - см. eps_wall_insulation_work_m2) цены на монтаж 100мм-слоя. НЕ ИСПОЛЬЗОВАТЬ КАК ОКОНЧАТЕЛЬНОЕ ЗНАЧЕНИЕ - заменить, когда Елена ответит на вопрос от 2026-08-06 (один проход маляра на оба слоя или два отдельных).</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>eps_wall_insulation_work_m2</t>
+          <t>eps_wall_insulation_work_50_m2</t>
         </is>
       </c>
     </row>
@@ -3928,19 +3952,19 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовкладыша</t>
+          <t>Устройство утепления низа плиты</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D114" t="n">
         <v>1</v>
       </c>
       <c r="E114" t="n">
-        <v>100</v>
+        <v>900</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3949,12 +3973,12 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 31. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>thermal_insert_combined_installation_work_m</t>
+          <t>eps_bottom_slab_insulation_work_m2</t>
         </is>
       </c>
     </row>
@@ -3966,7 +3990,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
+          <t>Утепление торца плиты ЭППС 100мм</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3978,7 +4002,7 @@
         <v>1</v>
       </c>
       <c r="E115" t="n">
-        <v>770</v>
+        <v>500</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3987,12 +4011,12 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 16. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>roof_eps_insulation_installation_work_m2</t>
+          <t>eps_wall_insulation_work_m2</t>
         </is>
       </c>
     </row>
@@ -4004,19 +4028,19 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 50 мм (для термовставок)</t>
+          <t>Устройство и монтаж термовкладыша</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D116" t="n">
         <v>1</v>
       </c>
       <c r="E116" t="n">
-        <v>8800</v>
+        <v>100</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -4025,12 +4049,12 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 43. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 13. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>thermal_insert_50_material_m3</t>
+          <t>thermal_insert_combined_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -4042,19 +4066,19 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 100 мм (для термовставок)</t>
+          <t>Утепление кровельного покрытия ЭППС (1 слой -100мм, 2 слой -100мм (50мм), 3 слой - разуклонка)</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D117" t="n">
         <v>1</v>
       </c>
       <c r="E117" t="n">
-        <v>8900</v>
+        <v>770</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -4063,12 +4087,12 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 44. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 33. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>thermal_insert_100_material_m3</t>
+          <t>roof_eps_insulation_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -4080,19 +4104,19 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовставок 50 мм</t>
+          <t>Пеноплэкс ГЕО 50 мм (для термовставок)</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D118" t="n">
         <v>1</v>
       </c>
       <c r="E118" t="n">
-        <v>100</v>
+        <v>8800</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
@@ -4101,12 +4125,12 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: новый прайс Елены содержит одну универсальную строку 'Устройство и монтаж термовкладыша' = 100 руб./мп. В реальных эталонных сметах АРК/ТРЦ/ЮСВ работа термовставок также считается по длине с этой ставкой; для production-раздельного режима 50/100 нужен отдельный price_code, поэтому цена размножена из той же универсальной строки прайса.</t>
+          <t>Источник: первый лист нового прайса, строка 43. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>thermal_insert_50_installation_work_m</t>
+          <t>thermal_insert_50_material_m3</t>
         </is>
       </c>
     </row>
@@ -4118,19 +4142,19 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовставок 100 мм</t>
+          <t>Пеноплэкс ГЕО 100 мм (для термовставок)</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D119" t="n">
         <v>1</v>
       </c>
       <c r="E119" t="n">
-        <v>100</v>
+        <v>8900</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
@@ -4139,12 +4163,12 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: та же универсальная работа 'Устройство и монтаж термовкладыша' = 100 руб./мп из нового прайса Елены. Толщина слоя меняет материал, но не ставку монтажной работы по м.п.</t>
+          <t>Источник: первый лист нового прайса, строка 44. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>thermal_insert_100_installation_work_m</t>
+          <t>thermal_insert_100_material_m3</t>
         </is>
       </c>
     </row>
@@ -4156,7 +4180,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Устройство и монтаж термовставок (произвольный типоразмер)</t>
+          <t>Устройство и монтаж термовставок 50 мм</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -4177,12 +4201,12 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: для режима thermal_insert_mode='items' калькулятор считает одну работу по суммарной длине всех термовставок произвольных типоразмеров. Ставка берется из той же универсальной строки нового прайса Елены 'Устройство и монтаж термовкладыша' = 100 руб./мп.</t>
+          <t>Добавлено 2026-08-07: новый прайс Елены содержит одну универсальную строку 'Устройство и монтаж термовкладыша' = 100 руб./мп. В реальных эталонных сметах АРК/ТРЦ/ЮСВ работа термовставок также считается по длине с этой ставкой; для production-раздельного режима 50/100 нужен отдельный price_code, поэтому цена размножена из той же универсальной строки прайса.</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>thermal_insert_items_installation_work_m</t>
+          <t>thermal_insert_50_installation_work_m</t>
         </is>
       </c>
     </row>
@@ -4194,19 +4218,19 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Материал термовставок (произвольный типоразмер)</t>
+          <t>Устройство и монтаж термовставок 100 мм</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D121" t="n">
         <v>1</v>
       </c>
       <c r="E121" t="n">
-        <v>8900</v>
+        <v>100</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
@@ -4215,72 +4239,88 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07: общий fallback для thermal_insert_items произвольного типоразмера. Новый прайс Елены дает Пеноплэкс ГЕО 100 мм (для термовставок) = 8900 руб./м3 и Пеноплэкс ГЕО 50 мм = 8800 руб./м3; для произвольных типоразмеров без отдельного толщинного price_code используем базовую цену 100 мм как более частый материал термовставок. Если в будущем появятся разные цены по eps_size, заменить на построчный price_code.</t>
+          <t>Добавлено 2026-08-07: та же универсальная работа 'Устройство и монтаж термовкладыша' = 100 руб./мп из нового прайса Елены. Толщина слоя меняет материал, но не ставку монтажной работы по м.п.</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>thermal_insert_item_material_m3</t>
+          <t>thermal_insert_100_installation_work_m</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Planter Standard Технониколь 40м2-1рул</t>
+          <t>Устройство и монтаж термовставок (произвольный типоразмер)</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>рул</t>
-        </is>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>1</v>
       </c>
       <c r="E122" t="n">
-        <v>4738</v>
+        <v>100</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Добавлено 2026-08-07: для режима thermal_insert_mode='items' калькулятор считает одну работу по суммарной длине всех термовставок произвольных типоразмеров. Ставка берется из той же универсальной строки нового прайса Елены 'Устройство и монтаж термовкладыша' = 100 руб./мп.</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>planter_standard_roll</t>
+          <t>thermal_insert_items_installation_work_m</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Фундамент</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PLANTERBAND 10м х 10см-1шт</t>
+          <t>Материал термовставок (произвольный типоразмер)</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>1</v>
       </c>
       <c r="E123" t="n">
-        <v>750</v>
+        <v>8900</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Обновлено 04.05</t>
+          <t>Добавлено 2026-08-07: общий fallback для thermal_insert_items произвольного типоразмера. Новый прайс Елены дает Пеноплэкс ГЕО 100 мм (для термовставок) = 8900 руб./м3 и Пеноплэкс ГЕО 50 мм = 8800 руб./м3; для произвольных типоразмеров без отдельного толщинного price_code используем базовую цену 100 мм как более частый материал термовставок. Если в будущем появятся разные цены по eps_size, заменить на построчный price_code.</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>planterband_item</t>
+          <t>thermal_insert_item_material_m3</t>
         </is>
       </c>
     </row>
@@ -4292,16 +4332,16 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Праймер битумный AquaMast, 18 л-1шт</t>
+          <t>Planter Standard Технониколь 40м2-1рул</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>рул</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>2865</v>
+        <v>4738</v>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -4310,7 +4350,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>bitumen_primer_aquamast_18l_item</t>
+          <t>planter_standard_roll</t>
         </is>
       </c>
     </row>
@@ -4322,7 +4362,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
+          <t>PLANTERBAND 10м х 10см-1шт</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4331,7 +4371,7 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>2828.21</v>
+        <v>750</v>
       </c>
       <c r="G125" t="inlineStr">
         <is>
@@ -4340,7 +4380,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>bitumen_mastic_aquamast_18kg_item</t>
+          <t>planterband_item</t>
         </is>
       </c>
     </row>
@@ -4352,16 +4392,16 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
+          <t>Праймер битумный AquaMast, 18 л-1шт</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>8800</v>
+        <v>2865</v>
       </c>
       <c r="G126" t="inlineStr">
         <is>
@@ -4370,7 +4410,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>eps_geo_50_m3</t>
+          <t>bitumen_primer_aquamast_18l_item</t>
         </is>
       </c>
     </row>
@@ -4382,16 +4422,16 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
+          <t>Мастика гидроизоляционная битумная для фундаментов AquaMast, 18 кг.-1шт</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>8900</v>
+        <v>2828.21</v>
       </c>
       <c r="G127" t="inlineStr">
         <is>
@@ -4400,7 +4440,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>eps_geo_100_m3</t>
+          <t>bitumen_mastic_aquamast_18kg_item</t>
         </is>
       </c>
     </row>
@@ -4412,16 +4452,16 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Клей-пена для ЭППС-1шт</t>
+          <t>Пеноплэкс ГЕО 50 мм-1м3</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>450</v>
+        <v>8800</v>
       </c>
       <c r="G128" t="inlineStr">
         <is>
@@ -4430,7 +4470,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>eps_foam_glue_can</t>
+          <t>eps_geo_50_m3</t>
         </is>
       </c>
     </row>
@@ -4442,75 +4482,67 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
+          <t>Пеноплэкс ГЕО 100 мм-1м3</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>109</v>
+        <v>8900</v>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
+          <t>Обновлено 04.05</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>geotextile_dornit_300_m2</t>
+          <t>eps_geo_100_m3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
+          <t>Клей-пена для ЭППС-1шт</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E130" t="n">
-        <v>350</v>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>450</v>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Обновлено 04.05</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>bitumen_waterproofing_work_m2</t>
+          <t>eps_foam_glue_can</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Фундамент</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Монтаж мембраны PLANTER стандарт</t>
+          <t>Геотекстиль Дорнит 300 г.м2 (100м2)</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4518,84 +4550,93 @@
           <t>м2</t>
         </is>
       </c>
-      <c r="D131" t="n">
-        <v>1</v>
-      </c>
       <c r="E131" t="n">
-        <v>100</v>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>109</v>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.</t>
+          <t>Цена приведена к единице калькулятора: м2; ранее в прайсе была строка за рулон.</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>planter_membrane_installation_work_m2</t>
+          <t>geotextile_dornit_300_m2</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Проволока</t>
+          <t>Гидроизоляция торца фундаментной плиты битумной мастикой в 2 слоя</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>кг</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D132" t="n">
         <v>1</v>
       </c>
       <c r="E132" t="n">
-        <v>75</v>
+        <v>350</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
+          <t>Источник: первый лист нового прайса, строка 15. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>bitumen_waterproofing_work_m2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Арматура</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 25 мм</t>
+          <t>Монтаж мембраны PLANTER стандарт</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>1п.м</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.7</v>
+        <v>1</v>
       </c>
       <c r="E133" t="n">
-        <v>155.8</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>46214</v>
+        <v>100</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>Источник: первый лист нового прайса, строка 11. Исходное кол-во: 1.</t>
+        </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>rebar_a500_d25_m</t>
+          <t>planter_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -4607,31 +4648,23 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 20мм</t>
+          <t>Проволока</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>1п.м</t>
+          <t>кг</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.7</v>
+        <v>1</v>
       </c>
       <c r="E134" t="n">
-        <v>100.25</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>46214</v>
+        <v>75</v>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr">
-        <is>
-          <t>rebar_a500_d20_m</t>
+          <t>price_code пока не сопоставлен; требуется ручная проверка связи с калькулятором.</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4676,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 16 мм</t>
+          <t>Арматура класса А500 диаметром 25 мм</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4655,14 +4688,14 @@
         <v>11.7</v>
       </c>
       <c r="E135" t="n">
-        <v>64.90000000000001</v>
+        <v>155.8</v>
       </c>
       <c r="F135" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>rebar_a500_d16_m</t>
+          <t>rebar_a500_d25_m</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4707,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 12мм</t>
+          <t>Арматура класса А500 диаметром 20мм</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4686,14 +4719,19 @@
         <v>11.7</v>
       </c>
       <c r="E136" t="n">
-        <v>36.85</v>
+        <v>100.25</v>
       </c>
       <c r="F136" s="2" t="n">
         <v>46214</v>
       </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>price_code сопоставлен 2026-07-20 (rebar_a500_d20_m), проверено связью с калькулятором floor_slab_2/floor_slab_1.</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>rebar_a500_d12_m</t>
+          <t>rebar_a500_d20_m</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4743,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Арматура класса А500 диаметром 10 мм</t>
+          <t>Арматура класса А500 диаметром 16 мм</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4717,14 +4755,14 @@
         <v>11.7</v>
       </c>
       <c r="E137" t="n">
-        <v>27.16</v>
+        <v>64.90000000000001</v>
       </c>
       <c r="F137" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>rebar_a500_d10_m</t>
+          <t>rebar_a500_d16_m</t>
         </is>
       </c>
     </row>
@@ -4736,7 +4774,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 8 мм</t>
+          <t>Арматура класса А500 диаметром 12мм</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4748,14 +4786,14 @@
         <v>11.7</v>
       </c>
       <c r="E138" t="n">
-        <v>18.5</v>
+        <v>36.85</v>
       </c>
       <c r="F138" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>rebar_a240_d8_m</t>
+          <t>rebar_a500_d12_m</t>
         </is>
       </c>
     </row>
@@ -4767,7 +4805,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Арматура класса А240 диаметром 6 мм</t>
+          <t>Арматура класса А500 диаметром 10 мм</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4779,80 +4817,76 @@
         <v>11.7</v>
       </c>
       <c r="E139" t="n">
-        <v>10.25</v>
+        <v>27.16</v>
       </c>
       <c r="F139" s="2" t="n">
         <v>46214</v>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>rebar_a240_d6_m</t>
+          <t>rebar_a500_d10_m</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Блок D 400</t>
+          <t>Арматура класса А240 диаметром 8 мм</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>34,56 м3</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>11.7</v>
       </c>
       <c r="E140" t="n">
-        <v>5900</v>
+        <v>18.5</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+        <v>46214</v>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>rebar_a240_d8_m</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Газобетон</t>
+          <t>Арматура</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Блок D 500</t>
+          <t>Арматура класса А240 диаметром 6 мм</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
-      </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>32,4 м3</t>
-        </is>
+          <t>1п.м</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11.7</v>
       </c>
       <c r="E141" t="n">
-        <v>5200</v>
+        <v>10.25</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+        <v>46214</v>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>rebar_a240_d6_m</t>
         </is>
       </c>
     </row>
@@ -4874,18 +4908,18 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>1,8 м3</t>
+          <t>34,56 м3</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>6300</v>
+        <v>5900</v>
       </c>
       <c r="F142" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>с 15.05; Вместимость в машину: 34,56 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -4907,18 +4941,18 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>1,8 м3</t>
+          <t>32,4 м3</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5800</v>
+        <v>5200</v>
       </c>
       <c r="F143" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>С 15.05; Вместимость в машину: 32,4 м3 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -4930,133 +4964,135 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Блок D 400</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>1,8 м3</t>
+        </is>
       </c>
       <c r="E144" t="n">
-        <v>360</v>
+        <v>6300</v>
       </c>
       <c r="F144" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H144" t="inlineStr">
-        <is>
-          <t>block_adhesive_bag</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Кровля</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Воронка парапетная с листвоуловителем (материал)</t>
+          <t>Блок D 500</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>1</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>1,8 м3</t>
+        </is>
       </c>
       <c r="E145" t="n">
-        <v>6001.23</v>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>5800</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: та же причина, что и у внутренней воронки - материалы не читаются автоматическим скриптом, цена взята напрямую из листа 'Утеплителипленкимастика (Олег)', строка 31 ('Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650') = 6001.23 руб./шт. До этой правки код ошибочно получал цену РАБОТЫ монтажа (5000 руб.) через устаревшее сопоставление в MANUAL_WORK_PRICE_CODES - реальная цена материала выше, это была настоящая ошибка в деньгах, не совпадение.</t>
-        </is>
-      </c>
-      <c r="H145" t="inlineStr">
-        <is>
-          <t>roof_parapet_drain_item</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Газобетон</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Доставка блоков, смеси</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>28000</t>
-        </is>
+          <t>мешок 25 кг</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>360</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>block_delivery_truck</t>
+          <t>block_adhesive_bag</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Несущие стены и перемычки</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Разгрузка блоков, смеси манипулятором</t>
+          <t>Воронка парапетная с листвоуловителем (материал)</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>маш</t>
-        </is>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>15000</t>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+      <c r="E147" t="n">
+        <v>6001.23</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+          <t>Добавлено 2026-08-06: та же причина, что и у внутренней воронки - материалы не читаются автоматическим скриптом, цена взята напрямую из листа 'Утеплителипленкимастика (Олег)', строка 31 ('Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650') = 6001.23 руб./шт. До этой правки код ошибочно получал цену РАБОТЫ монтажа (5000 руб.) через устаревшее сопоставление в MANUAL_WORK_PRICE_CODES - реальная цена материала выше, это была настоящая ошибка в деньгах, не совпадение.</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>block_unloading_manipulator_truck</t>
+          <t>roof_parapet_drain_item</t>
         </is>
       </c>
     </row>
@@ -5068,17 +5104,17 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Газобетонный блок D400 600x400x250 мм</t>
+          <t>Доставка блоков, смеси</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>6000</t>
+          <t>28000</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
@@ -5088,7 +5124,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>gas_block_d400_m3</t>
+          <t>block_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -5100,17 +5136,17 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x150x250 мм</t>
+          <t>Разгрузка блоков, смеси манипулятором</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -5120,7 +5156,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>gas_block_d500_150_m3</t>
+          <t>block_unloading_manipulator_truck</t>
         </is>
       </c>
     </row>
@@ -5132,7 +5168,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Газобетонный блок D500 600x250x250 мм</t>
+          <t>Газобетонный блок D400 600x400x250 мм</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -5142,7 +5178,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>5500</t>
+          <t>6000</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -5152,7 +5188,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>gas_block_d500_m3</t>
+          <t>gas_block_d400_m3</t>
         </is>
       </c>
     </row>
@@ -5164,17 +5200,17 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Пескобетон М300 40 кг</t>
+          <t>Газобетонный блок D500 600x150x250 мм</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>375</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -5184,69 +5220,71 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>sand_concrete_bag</t>
+          <t>gas_block_d500_150_m3</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Клей</t>
+          <t>Газобетонный блок D500 600x250x250 мм</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>мешок 25 кг</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>1</v>
-      </c>
-      <c r="E152" t="n">
-        <v>659.77</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>46146</v>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>5500</t>
+        </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>gas_block_d500_m3</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Поротерм</t>
+          <t>Несущие стены и перемычки</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Сетка 5/0.4/100</t>
+          <t>Пескобетон М300 40 кг</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>рулон</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>1</v>
-      </c>
-      <c r="E153" t="n">
-        <v>1304.63</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>46146</v>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Перенесено из rows_to_add, статус: needs_review. Добавлено из калькулятора MVP, требуется проверка Елены Требуется проверка Елены.</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>sand_concrete_bag</t>
         </is>
       </c>
     </row>
@@ -5258,26 +5296,26 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Сетка 5/0.5/100</t>
+          <t>Клей</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>рулон</t>
+          <t>мешок 25 кг</t>
         </is>
       </c>
       <c r="D154" t="n">
         <v>1</v>
       </c>
       <c r="E154" t="n">
-        <v>1729.38</v>
+        <v>659.77</v>
       </c>
       <c r="F154" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5289,26 +5327,26 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>PTH 8</t>
+          <t>Сетка 5/0.4/100</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>рулон</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>120</v>
+        <v>1</v>
       </c>
       <c r="E155" t="n">
-        <v>100.62</v>
+        <v>1304.63</v>
       </c>
       <c r="F155" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5320,26 +5358,26 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>PTH 12</t>
+          <t>Сетка 5/0.5/100</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>рулон</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>80</v>
+        <v>1</v>
       </c>
       <c r="E156" t="n">
-        <v>150.62</v>
+        <v>1729.38</v>
       </c>
       <c r="F156" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5351,7 +5389,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>PTH 20</t>
+          <t>PTH 8</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -5360,17 +5398,17 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>72</v>
+        <v>120</v>
       </c>
       <c r="E157" t="n">
-        <v>171.17</v>
+        <v>100.62</v>
       </c>
       <c r="F157" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 2640 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5420,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>PTH 25М</t>
+          <t>PTH 12</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -5391,17 +5429,17 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="E158" t="n">
-        <v>180.89</v>
+        <v>150.62</v>
       </c>
       <c r="F158" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1760 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5451,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>PTH 38</t>
+          <t>PTH 20</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -5422,17 +5460,17 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="E159" t="n">
-        <v>155.66</v>
+        <v>171.17</v>
       </c>
       <c r="F159" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1368 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5482,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PTH 38 Termo</t>
+          <t>PTH 25М</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -5456,7 +5494,7 @@
         <v>60</v>
       </c>
       <c r="E160" t="n">
-        <v>201.14</v>
+        <v>180.89</v>
       </c>
       <c r="F160" s="2" t="n">
         <v>46146</v>
@@ -5475,7 +5513,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PTH 44</t>
+          <t>PTH 38</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -5484,17 +5522,17 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E161" t="n">
-        <v>176.58</v>
+        <v>155.66</v>
       </c>
       <c r="F161" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5506,7 +5544,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>PTH 51</t>
+          <t>PTH 38 Termo</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -5515,93 +5553,79 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E162" t="n">
-        <v>225.53</v>
+        <v>201.14</v>
       </c>
       <c r="F162" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: 1320 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Гидроизоляция поверхности под первый ряд блоков</t>
+          <t>PTH 44</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E163" t="n">
-        <v>100</v>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>176.58</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>cutoff_waterproofing_under_blocks_m2</t>
+          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Поротерм</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
+          <t>PTH 51</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="E164" t="n">
-        <v>450</v>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>225.53</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.</t>
-        </is>
-      </c>
-      <c r="H164" t="inlineStr">
-        <is>
-          <t>edge_insulation_work_m</t>
+          <t>Вместимость в машину: 1100 Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5637,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Укладка ЭППС 50мм под плитой</t>
+          <t>Гидроизоляция поверхности под первый ряд блоков</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -5625,7 +5649,7 @@
         <v>1</v>
       </c>
       <c r="E165" t="n">
-        <v>250</v>
+        <v>100</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
@@ -5634,12 +5658,12 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 18. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>eps_laying_work_m2</t>
+          <t>cutoff_waterproofing_under_blocks_m2</t>
         </is>
       </c>
     </row>
@@ -5651,21 +5675,19 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
+          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D166" t="n">
         <v>1</v>
       </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>1 200</t>
-        </is>
+      <c r="E166" t="n">
+        <v>450</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
@@ -5674,12 +5696,12 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 30. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>gas_block_cladding_work_m2</t>
+          <t>edge_insulation_work_m</t>
         </is>
       </c>
     </row>
@@ -5691,19 +5713,19 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Кладка парапета из газобетонных блоков</t>
+          <t>Укладка ЭППС 50мм под плитой</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D167" t="n">
         <v>1</v>
       </c>
       <c r="E167" t="n">
-        <v>7000</v>
+        <v>250</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
@@ -5712,12 +5734,12 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 12. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>gas_block_masonry_work_m3</t>
+          <t>eps_laying_work_m2</t>
         </is>
       </c>
     </row>
@@ -5729,19 +5751,21 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
+          <t>Обкладка дымохода и вентканалов толщ. 150мм из из газобетонных блоков</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D168" t="n">
         <v>1</v>
       </c>
-      <c r="E168" t="n">
-        <v>1200</v>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>1 200</t>
+        </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
@@ -5750,12 +5774,12 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 25. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>lintel_concreting_work_m</t>
+          <t>gas_block_cladding_work_m2</t>
         </is>
       </c>
     </row>
@@ -5767,21 +5791,19 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
+          <t>Кладка парапета из газобетонных блоков</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>компл</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D169" t="n">
         <v>1</v>
       </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>20 000</t>
-        </is>
+      <c r="E169" t="n">
+        <v>7000</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
@@ -5790,12 +5812,12 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 24. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>scaffolding_setup_dismantling_work_set</t>
+          <t>gas_block_masonry_work_m3</t>
         </is>
       </c>
     </row>
@@ -5807,19 +5829,19 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Резка блока под перемычку (U-блок)</t>
+          <t>Бетонирование перемычек в U блоке бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D170" t="n">
         <v>1</v>
       </c>
       <c r="E170" t="n">
-        <v>400</v>
+        <v>1200</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
@@ -5828,12 +5850,12 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.</t>
+          <t>Источник: первый лист нового прайса, строка 21. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>u_block_lintel_cutting_item</t>
+          <t>lintel_concreting_work_m</t>
         </is>
       </c>
     </row>
@@ -5845,19 +5867,21 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
+          <t>Устройство лесов, подмостей для кладки, демонтаж лесов после завершения работ</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>компл</t>
         </is>
       </c>
       <c r="D171" t="n">
         <v>1</v>
       </c>
-      <c r="E171" t="n">
-        <v>1500</v>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>20 000</t>
+        </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
@@ -5866,12 +5890,12 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 17. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>lintel_monolithic_concreting_work_m</t>
+          <t>scaffolding_setup_dismantling_work_set</t>
         </is>
       </c>
     </row>
@@ -5883,19 +5907,19 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Укладка ПВХ Мембраны</t>
+          <t>Резка блока под перемычку (U-блок)</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D172" t="n">
         <v>1</v>
       </c>
       <c r="E172" t="n">
-        <v>630</v>
+        <v>400</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
@@ -5904,12 +5928,12 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 20. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_installation_work_m2</t>
+          <t>u_block_lintel_cutting_item</t>
         </is>
       </c>
     </row>
@@ -5921,19 +5945,19 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Установка воронки парапетной</t>
+          <t>Бетонирование монолитных перемычек бетоном марки В22,5 (М300)</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D173" t="n">
         <v>1</v>
       </c>
       <c r="E173" t="n">
-        <v>5000</v>
+        <v>1500</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
@@ -5942,12 +5966,12 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 22. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>roof_parapet_drain_installation_item</t>
+          <t>lintel_monolithic_concreting_work_m</t>
         </is>
       </c>
     </row>
@@ -5959,19 +5983,19 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Кладка вентканалов Schiedel</t>
+          <t>Укладка ПВХ Мембраны</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D174" t="n">
         <v>1</v>
       </c>
       <c r="E174" t="n">
-        <v>5000</v>
+        <v>630</v>
       </c>
       <c r="F174" t="inlineStr">
         <is>
@@ -5980,12 +6004,12 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 34. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>schiedel_masonry_work_m</t>
+          <t>roof_pvc_membrane_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -5997,19 +6021,19 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Блок D400 (для кладки шахты вентканалов)</t>
+          <t>Установка воронки парапетной</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D175" t="n">
         <v>1</v>
       </c>
       <c r="E175" t="n">
-        <v>6100</v>
+        <v>5000</v>
       </c>
       <c r="F175" t="inlineStr">
         <is>
@@ -6018,12 +6042,12 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 45. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 37. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>schiedel_masonry_gas_block_d400_m3</t>
+          <t>roof_parapet_drain_installation_item</t>
         </is>
       </c>
     </row>
@@ -6035,19 +6059,19 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Блок D500 (для кладки шахты вентканалов)</t>
+          <t>Кладка вентканалов Schiedel</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D176" t="n">
         <v>1</v>
       </c>
       <c r="E176" t="n">
-        <v>5400</v>
+        <v>5000</v>
       </c>
       <c r="F176" t="inlineStr">
         <is>
@@ -6056,12 +6080,12 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 46. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 41. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>schiedel_masonry_gas_block_d500_m3</t>
+          <t>schiedel_masonry_work_m</t>
         </is>
       </c>
     </row>
@@ -6073,19 +6097,19 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Штробление блоков под дополнительное усиление, армирование арматурой диаметром 10 мм</t>
+          <t>Блок D400 (для кладки шахты вентканалов)</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D177" t="n">
         <v>1</v>
       </c>
       <c r="E177" t="n">
-        <v>250</v>
+        <v>6100</v>
       </c>
       <c r="F177" t="inlineStr">
         <is>
@@ -6094,12 +6118,12 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-07 по сверке АРК/ТРЦ/ЮСВ: в эталонных сметах это платная работа в правой части себестоимости. Временная production-ставка 250 руб./мп до отдельного подтверждения Елены.</t>
+          <t>Источник: первый лист нового прайса, строка 45. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>block_chasing_reinforcement_work_m</t>
+          <t>schiedel_masonry_gas_block_d400_m3</t>
         </is>
       </c>
     </row>
@@ -6111,19 +6135,19 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
+          <t>Блок D500 (для кладки шахты вентканалов)</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>мп</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="D178" t="n">
         <v>1</v>
       </c>
       <c r="E178" t="n">
-        <v>450</v>
+        <v>5400</v>
       </c>
       <c r="F178" t="inlineStr">
         <is>
@@ -6132,68 +6156,74 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>Добавлено по ответу Елены 2026-07-30: ставка такая же, как утепление балок и торца плиты.</t>
+          <t>Источник: первый лист нового прайса, строка 46. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>lintel_edge_insulation_work_m</t>
+          <t>schiedel_masonry_gas_block_d500_m3</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
+          <t>Штробление блоков под дополнительное усиление, армирование арматурой диаметром 10 мм</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>м2</t>
-        </is>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>111.76</t>
+          <t>мп</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>1</v>
+      </c>
+      <c r="E179" t="n">
+        <v>250</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
+          <t>Добавлено 2026-08-07 по сверке АРК/ТРЦ/ЮСВ: в эталонных сметах это платная работа в правой части себестоимости. Временная production-ставка 250 руб./мп до отдельного подтверждения Елены.</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>roof_geotextile_technonikol_prof_300_m2</t>
+          <t>block_chasing_reinforcement_work_m</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Кровля</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Воронка кровельная внутренняя с обогревом (материал)</t>
+          <t>Устройство утепления по наружной стороне торцов плиты, балок, перемычек</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D180" t="n">
         <v>1</v>
       </c>
       <c r="E180" t="n">
-        <v>5000</v>
+        <v>450</v>
       </c>
       <c r="F180" t="inlineStr">
         <is>
@@ -6202,100 +6232,120 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: материалы не читаются автоматическим скриптом (только первый лист 'Прайс по видам работ', лист с материалами 'Утеплителипленкимастика (Олег)' сюда не входит) - цена 5000 руб./шт взята оттуда напрямую, строка 32 ('Воронка кровельная (с обжимным мет. фланцем с обогревом 110х450мм)'). До этой правки код случайно получал ту же цену через устаревшее (неверное) сопоставление с работой монтажа - см. исправление в MANUAL_WORK_PRICE_CODES выше. Цена совпала случайно (обе 5000), поэтому баг был незаметен.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: ставка такая же, как утепление балок и торца плиты.</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>roof_internal_drain_with_heating_item</t>
+          <t>lintel_edge_insulation_work_m</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Кровля</t>
+          <t>КРОВЕЛЬНОЕ ПОКРЫТИЕ ДОМА</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>ПВХ мембрана Logicroof V-GR 1,5 мм (эксплуатируемая кровля)</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 300, 2х50м</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>рул</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>1</v>
-      </c>
-      <c r="E181" t="n">
-        <v>1146.91</v>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>111.76</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: такая же цена, как у обычной V-RP мембраны (1146.91 руб./рул, прайс Елены лист 'Утеплителипленкимастика (Олег)' строка 29 - в прайсе V-GR и V-RP указаны с одинаковой ценой). Пользователь вписывал эту цену вручную в гугл-таблицу 2026-08-06 после того, как для ТРЦ впервые понадобилась V-GR (эксплуатируемая зона кровли) - перенесено в реестр, чтобы не терялось при пересборке.</t>
+          <t>Перенесено из rows_to_add, статус: requires_decision. Добавлено из калькулятора MVP, требуется проверка Елены Требуется решение по смыслу/единице перед production-использованием.</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_logicroof_vgr_1_5mm_gray_roll</t>
+          <t>roof_geotextile_technonikol_prof_300_m2</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
+          <t>Воронка кровельная внутренняя с обогревом (материал)</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>м3</t>
-        </is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>1</v>
       </c>
       <c r="E182" t="n">
-        <v>6610</v>
+        <v>5000</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Добавлено 2026-08-06: материалы не читаются автоматическим скриптом (только первый лист 'Прайс по видам работ', лист с материалами 'Утеплителипленкимастика (Олег)' сюда не входит) - цена 5000 руб./шт взята оттуда напрямую, строка 32 ('Воронка кровельная (с обжимным мет. фланцем с обогревом 110х450мм)'). До этой правки код случайно получал ту же цену через устаревшее (неверное) сопоставление с работой монтажа - см. исправление в MANUAL_WORK_PRICE_CODES выше. Цена совпала случайно (обе 5000), поэтому баг был незаметен.</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>roof_internal_drain_with_heating_item</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Плоская кровля</t>
+          <t>Кровля</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
+          <t>ПВХ мембрана Logicroof V-GR 1,5 мм (эксплуатируемая кровля)</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>шт</t>
-        </is>
+          <t>рул</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>1</v>
       </c>
       <c r="E183" t="n">
-        <v>450</v>
+        <v>1146.91</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>Добавлено 2026-08-06: такая же цена, как у обычной V-RP мембраны (1146.91 руб./рул, прайс Елены лист 'Утеплителипленкимастика (Олег)' строка 29 - в прайсе V-GR и V-RP указаны с одинаковой ценой). Пользователь вписывал эту цену вручную в гугл-таблицу 2026-08-06 после того, как для ТРЦ впервые понадобилась V-GR (эксплуатируемая зона кровли) - перенесено в реестр, чтобы не терялось при пересборке.</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>roof_pvc_membrane_logicroof_vgr_1_5mm_gray_roll</t>
         </is>
       </c>
     </row>
@@ -6307,16 +6357,16 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
+          <t>Пеноплэкс ОСНОВА Т-15, 1185х585х100, (0,2772)</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E184" t="n">
-        <v>59.55</v>
+        <v>6610</v>
       </c>
       <c r="G184" t="inlineStr">
         <is>
@@ -6332,7 +6382,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
+          <t>Клей пена однокомп. в аэрозольной упак.PENOPLEX FASTFIX</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -6341,11 +6391,11 @@
         </is>
       </c>
       <c r="E185" t="n">
-        <v>6001.23</v>
+        <v>450</v>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу. Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
@@ -6357,16 +6407,16 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
+          <t>Стеклохолст ТехноНИКОЛЬ 100 гр/м2 (400м/рул)</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2060</v>
+        <v>59.55</v>
       </c>
       <c r="G186" t="inlineStr">
         <is>
@@ -6382,20 +6432,20 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
+          <t>Воронка парапетная с листвоуловителем и отводом VC-PVC, для ПВХ мембран, 100х100х650</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E187" t="n">
-        <v>23.12</v>
-      </c>
-      <c r="H187" t="inlineStr">
-        <is>
-          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
+        <v>6001.23</v>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
@@ -6407,25 +6457,20 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
+          <t>Цементно-стружечная плита (ЦСП I) толщина 12 мм 3200х1200 - 1шт</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="E188" t="n">
-        <v>7377.89</v>
+        <v>2060</v>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
-      </c>
-      <c r="H188" t="inlineStr">
-        <is>
-          <t>roof_eps100_technonikol_carbon_eco_m3</t>
+          <t>Позиция кровельного прайса. price_code не проставлен автоматически, если текущие калькуляторы пока не используют эту строку напрямую.</t>
         </is>
       </c>
     </row>
@@ -6437,25 +6482,20 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
+          <t>Пленка пароизоляционная ТехноНИКОЛЬ 120 мкм  (150 м2/рул)</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>м3</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E189" t="n">
-        <v>7155.34</v>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
-        </is>
+        <v>23.12</v>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>roof_eps50_technonikol_carbon_eco_m3</t>
+          <t>roof_vapor_barrier_film_technonikol_120mk_m2</t>
         </is>
       </c>
     </row>
@@ -6467,7 +6507,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х100-L</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -6476,7 +6516,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>9888.67</v>
+        <v>7377.89</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -6485,7 +6525,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_a_m3</t>
+          <t>roof_eps100_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
@@ -6497,7 +6537,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF 1180х580х50-L</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -6506,7 +6546,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>9888.67</v>
+        <v>7155.34</v>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -6515,7 +6555,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>roof_eps_slope_2_1_plate_b_m3</t>
+          <t>roof_eps50_technonikol_carbon_eco_m3</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6567,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент А, 1200х600х10/35 (0,2916)</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -6545,7 +6585,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>roof_eps_slope_4_2_plate_j_m3</t>
+          <t>roof_eps_slope_2_1_plate_a_m3</t>
         </is>
       </c>
     </row>
@@ -6557,7 +6597,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
+          <t>ТЕХНОНИКОЛЬ XPS CARBON PROF SLOPE- 2,1%  Элемент В, 1200х600х35/60 (0,2736)</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -6575,7 +6615,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>roof_eps_slope_4_2_plate_k_m3</t>
+          <t>roof_eps_slope_2_1_plate_b_m3</t>
         </is>
       </c>
     </row>
@@ -6587,16 +6627,16 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент J 1200х600х10/35</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E194" t="n">
-        <v>57.56</v>
+        <v>9888.67</v>
       </c>
       <c r="G194" t="inlineStr">
         <is>
@@ -6605,7 +6645,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>roof_geotextile_technonikol_prof_150_m2</t>
+          <t>roof_eps_slope_4_2_plate_j_m3</t>
         </is>
       </c>
     </row>
@@ -6617,16 +6657,16 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Рейка прижимная, 2 м</t>
+          <t>Плиты пенополистирольные экструдированные XPS ТЕХНОНИКОЛЬ CARBON PROF SLOPE- 4,2% Элемент К 1200х600х35/60</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>пог. м</t>
+          <t>м3</t>
         </is>
       </c>
       <c r="E195" t="n">
-        <v>90</v>
+        <v>9888.67</v>
       </c>
       <c r="G195" t="inlineStr">
         <is>
@@ -6635,7 +6675,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>roof_aluminum_pressure_rail_m</t>
+          <t>roof_eps_slope_4_2_plate_k_m3</t>
         </is>
       </c>
     </row>
@@ -6647,16 +6687,16 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Рейка краевая, 2 м</t>
+          <t>Геотекстиль ТЕХНОНИКОЛЬ ПРОФ Кровля 150, 2х50м</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>пог. м</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="E196" t="n">
-        <v>95</v>
+        <v>57.56</v>
       </c>
       <c r="G196" t="inlineStr">
         <is>
@@ -6665,7 +6705,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>roof_aluminum_edge_rail_m</t>
+          <t>roof_geotextile_technonikol_prof_150_m2</t>
         </is>
       </c>
     </row>
@@ -6677,16 +6717,16 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
+          <t>Рейка прижимная, 2 м</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>пог. м</t>
         </is>
       </c>
       <c r="E197" t="n">
-        <v>1146.91</v>
+        <v>90</v>
       </c>
       <c r="G197" t="inlineStr">
         <is>
@@ -6695,7 +6735,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
+          <t>roof_aluminum_pressure_rail_m</t>
         </is>
       </c>
     </row>
@@ -6707,96 +6747,80 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Аэратор кровельный PVC, А75х375</t>
+          <t>Рейка краевая, 2 м</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>пог. м</t>
         </is>
       </c>
       <c r="E198" t="n">
-        <v>587</v>
+        <v>95</v>
+      </c>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
+        </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>roof_pvc_aerator_75x375_item</t>
+          <t>roof_aluminum_edge_rail_m</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
+          <t>ПВХ Logicroof V-RP 1,5мм cерая, 2,10х20 м (42м 2/рул)</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>смена</t>
-        </is>
-      </c>
-      <c r="D199" t="n">
-        <v>1</v>
+          <t>м2</t>
+        </is>
       </c>
       <c r="E199" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F199" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>1146.91</v>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>price_code проставлен автоматически по точному совпадению номенклатуры; проверьте цену/единицу.</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>roof_crane_lifting_shift</t>
+          <t>roof_pvc_membrane_logicroof_vrp_1_5mm_gray_roll</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Работы</t>
+          <t>Плоская кровля</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
+          <t>Аэратор кровельный PVC, А75х375</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>мп</t>
-        </is>
-      </c>
-      <c r="D200" t="n">
-        <v>1</v>
+          <t>шт</t>
+        </is>
       </c>
       <c r="E200" t="n">
-        <v>3000</v>
-      </c>
-      <c r="F200" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
-      </c>
-      <c r="G200" t="inlineStr">
-        <is>
-          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.</t>
-        </is>
+        <v>587</v>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>roof_internal_drain_pvc_110mm_m</t>
+          <t>roof_pvc_aerator_75x375_item</t>
         </is>
       </c>
     </row>
@@ -6808,19 +6832,19 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Пароизоляция основания плёнкой ПВХ</t>
+          <t>Подъем материалов автокраном / разгрузка материала в ручную</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>м2</t>
+          <t>смена</t>
         </is>
       </c>
       <c r="D201" t="n">
         <v>1</v>
       </c>
       <c r="E201" t="n">
-        <v>77</v>
+        <v>15000</v>
       </c>
       <c r="F201" t="inlineStr">
         <is>
@@ -6829,12 +6853,12 @@
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 40. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>roof_vapor_barrier_installation_work_m2</t>
+          <t>roof_crane_lifting_shift</t>
         </is>
       </c>
     </row>
@@ -6846,7 +6870,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Монтаж примыкания кровли из ПВХ мембраны</t>
+          <t>Устройство внутреннего водостока (ПВХ Ф110мм) (ориентировочно)</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -6858,7 +6882,7 @@
         <v>1</v>
       </c>
       <c r="E202" t="n">
-        <v>700</v>
+        <v>3000</v>
       </c>
       <c r="F202" t="inlineStr">
         <is>
@@ -6867,12 +6891,12 @@
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-02 по сверке эталонных смет: общее линейное примыкание кровли к парапетам/стенам/ВК считается в м.п.; отдельное примыкание к вентшахтам в шт остается optional legacy.</t>
+          <t>Источник: первый лист нового прайса, строка 39. Исходное кол-во: 1.</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>roof_pvc_membrane_abutment_work_m</t>
+          <t>roof_internal_drain_pvc_110mm_m</t>
         </is>
       </c>
     </row>
@@ -6884,19 +6908,19 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Монтаж примыкания к вентшахтам</t>
+          <t>Пароизоляция основания плёнкой ПВХ</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>м2</t>
         </is>
       </c>
       <c r="D203" t="n">
         <v>1</v>
       </c>
       <c r="E203" t="n">
-        <v>5000</v>
+        <v>77</v>
       </c>
       <c r="F203" t="inlineStr">
         <is>
@@ -6905,12 +6929,12 @@
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Источник: первый лист нового прайса, строка 32. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>roof_vent_shaft_abutment_installation_item</t>
+          <t>roof_vapor_barrier_installation_work_m2</t>
         </is>
       </c>
     </row>
@@ -6922,19 +6946,19 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
+          <t>Монтаж примыкания кровли из ПВХ мембраны</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>мп</t>
         </is>
       </c>
       <c r="D204" t="n">
         <v>1</v>
       </c>
       <c r="E204" t="n">
-        <v>5000</v>
+        <v>700</v>
       </c>
       <c r="F204" t="inlineStr">
         <is>
@@ -6943,12 +6967,12 @@
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+          <t>Добавлено 2026-08-02 по сверке эталонных смет: общее линейное примыкание кровли к парапетам/стенам/ВК считается в м.п.; отдельное примыкание к вентшахтам в шт остается optional legacy.</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>roof_internal_drain_with_heating_installation_item</t>
+          <t>roof_pvc_membrane_abutment_work_m</t>
         </is>
       </c>
     </row>
@@ -6960,7 +6984,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Установка аэратора кровельного PVC, А75х375</t>
+          <t>Монтаж примыкания к вентшахтам</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -6972,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="E205" t="n">
-        <v>2500</v>
+        <v>5000</v>
       </c>
       <c r="F205" t="inlineStr">
         <is>
@@ -6981,24 +7005,24 @@
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+          <t>Источник: первый лист нового прайса, строка 36. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>roof_pvc_aerator_75x375_installation_item</t>
+          <t>roof_vent_shaft_abutment_installation_item</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+          <t>Установка воронки кровельной (с обжимным мет. фланцем с обогревом 110х450мм) (без пробивки отверстий)</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -7010,26 +7034,33 @@
         <v>1</v>
       </c>
       <c r="E206" t="n">
-        <v>268.4</v>
-      </c>
-      <c r="F206" s="2" t="n">
-        <v>46146</v>
+        <v>5000</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Источник: первый лист нового прайса, строка 38. Исходное кол-во: 1. price_code задан ручной картой normalize_elena_price_registry.py.</t>
+        </is>
+      </c>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>roof_internal_drain_with_heating_installation_item</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Schiedel</t>
+          <t>Работы</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+          <t>Установка аэратора кровельного PVC, А75х375</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -7041,14 +7072,21 @@
         <v>1</v>
       </c>
       <c r="E207" t="n">
-        <v>902.8</v>
-      </c>
-      <c r="F207" s="2" t="n">
-        <v>46146</v>
+        <v>2500</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Добавлено по ответу Елены 2026-07-30: 587 руб. — материал аэратора, работа отдельно 2500 руб./шт.</t>
+        </is>
+      </c>
+      <c r="H207" t="inlineStr">
+        <is>
+          <t>roof_pvc_aerator_75x375_installation_item</t>
         </is>
       </c>
     </row>
@@ -7060,7 +7098,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -7072,14 +7110,14 @@
         <v>1</v>
       </c>
       <c r="E208" t="n">
-        <v>264</v>
+        <v>268.4</v>
       </c>
       <c r="F208" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: h=330мм, габариты 200×250мм, вес 13кг, 63 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7129,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -7103,14 +7141,14 @@
         <v>1</v>
       </c>
       <c r="E209" t="n">
-        <v>672</v>
+        <v>902.8</v>
       </c>
       <c r="F209" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
+          <t>Вместимость в машину: h=330мм, габариты 500×360мм, вес 38кг, 16 шт на поддоне Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7122,7 +7160,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
+          <t>Вентиляционный канал одноходовой VENT 16/25-1X, 0.33 пм</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -7134,19 +7172,14 @@
         <v>1</v>
       </c>
       <c r="E210" t="n">
-        <v>512.4</v>
+        <v>264</v>
       </c>
       <c r="F210" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
-        </is>
-      </c>
-      <c r="H210" t="inlineStr">
-        <is>
-          <t>schiedel_vent_channel_2x_36_25_item</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7158,7 +7191,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
+          <t>Вентиляционный канал двухходовой VENT 16/50-2X, 0.33 пм</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -7170,19 +7203,14 @@
         <v>1</v>
       </c>
       <c r="E211" t="n">
-        <v>732</v>
+        <v>672</v>
       </c>
       <c r="F211" s="2" t="n">
         <v>46146</v>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
-        </is>
-      </c>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>schiedel_vent_channel_3x_52_25_item</t>
+          <t>Каталожная/поставщическая позиция. price_code не проставлен автоматически, если нет однозначной связи с текущей строкой калькулятора.</t>
         </is>
       </c>
     </row>
@@ -7194,33 +7222,31 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Доставка вентканалов (машина/транспорт, без разгрузки)</t>
+          <t>Вентиляционный канал двухходовой VENT 25/36, 0.33 пм</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D212" t="n">
         <v>1</v>
       </c>
       <c r="E212" t="n">
-        <v>15000</v>
-      </c>
-      <c r="F212" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>512.4</v>
+      </c>
+      <c r="F212" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>ИСПРАВЛЕНО 2026-08-06: было ошибочно затёрто на 2500 через устаревшее правило MANUAL_WORK_PRICE_CODES, которое мапило комбинированную строку 'Доставка+разгрузка' (2500) на этот материальный код - двойной счёт с schiedel_delivery_unloading_work. Реальное значение 15000 подтверждено на листе ЮСВ 'АЛ 06.04 КР1,КР2 (ЕЧ) (ЮВ)', строка 235 'Доставка вентканалов': материал=15000, работа=2500 - оба параллельных блока колонок (левый/белый и правый/серый) сходятся на этой цифре, без разночтений.</t>
+          <t>Вместимость в машину: h=330мм, габариты 250×360мм, вес 21кг, 36 шт на поддоне</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>schiedel_delivery_truck</t>
+          <t>schiedel_vent_channel_2x_36_25_item</t>
         </is>
       </c>
     </row>
@@ -7232,33 +7258,31 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Доставка вентканалов, разгрузка вручную</t>
+          <t>Вентиляционный канал трехходовой VENT 25/52, 0.33 пм</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>маш</t>
+          <t>шт</t>
         </is>
       </c>
       <c r="D213" t="n">
         <v>1</v>
       </c>
       <c r="E213" t="n">
-        <v>2500</v>
-      </c>
-      <c r="F213" t="inlineStr">
-        <is>
-          <t>2026-08-08</t>
-        </is>
+        <v>732</v>
+      </c>
+      <c r="F213" s="2" t="n">
+        <v>46146</v>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: этой строки нет в прайсе Елены отдельно (там доставка+разгрузка одной строкой = 2500) - ставка взята из реальной сметы ЮСВ, где разгрузка вручную идет отдельной строкой от доставки и стабильно равна 2500 руб./маш независимо от цены самой доставки (проверено в 2 разных листах ЮСВ: 2500/2500 и 15000/2500). По решению пользователя 2026-08-06 материал и работа считаются раздельно как более универсальный подход, а не совмещенной строкой как в АРК.</t>
+          <t>Вместимость в машину: h=330мм, габариты 520×250мм, вес 31кг, 20 шт на поддоне</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>schiedel_delivery_unloading_work</t>
+          <t>schiedel_vent_channel_3x_52_25_item</t>
         </is>
       </c>
     </row>
@@ -7270,19 +7294,19 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
+          <t>Доставка вентканалов (машина/транспорт, без разгрузки)</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="D214" t="n">
         <v>1</v>
       </c>
       <c r="E214" t="n">
-        <v>268.4</v>
+        <v>15000</v>
       </c>
       <c r="F214" t="inlineStr">
         <is>
@@ -7291,12 +7315,12 @@
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 27. h=330мм, габариты 200х250мм, вес 13кг, 63 шт на поддоне.</t>
+          <t>ИСПРАВЛЕНО 2026-08-06: было ошибочно затёрто на 2500 через устаревшее правило MANUAL_WORK_PRICE_CODES, которое мапило комбинированную строку 'Доставка+разгрузка' (2500) на этот материальный код - двойной счёт с schiedel_delivery_unloading_work. Реальное значение 15000 подтверждено на листе ЮСВ 'АЛ 06.04 КР1,КР2 (ЕЧ) (ЮВ)', строка 235 'Доставка вентканалов': материал=15000, работа=2500 - оба параллельных блока колонок (левый/белый и правый/серый) сходятся на этой цифре, без разночтений.</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_1x_item</t>
+          <t>schiedel_delivery_truck</t>
         </is>
       </c>
     </row>
@@ -7308,19 +7332,19 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+          <t>Доставка вентканалов, разгрузка вручную</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>шт</t>
+          <t>маш</t>
         </is>
       </c>
       <c r="D215" t="n">
         <v>1</v>
       </c>
       <c r="E215" t="n">
-        <v>902.8</v>
+        <v>2500</v>
       </c>
       <c r="F215" t="inlineStr">
         <is>
@@ -7329,12 +7353,12 @@
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 30. h=330мм, габариты 500х360мм, вес 38кг, 16 шт на поддоне.</t>
+          <t>Добавлено 2026-08-06: этой строки нет в прайсе Елены отдельно (там доставка+разгрузка одной строкой = 2500) - ставка взята из реальной сметы ЮСВ, где разгрузка вручную идет отдельной строкой от доставки и стабильно равна 2500 руб./маш независимо от цены самой доставки (проверено в 2 разных листах ЮСВ: 2500/2500 и 15000/2500). По решению пользователя 2026-08-06 материал и работа считаются раздельно как более универсальный подход, а не совмещенной строкой как в АРК.</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_4x_item</t>
+          <t>schiedel_delivery_unloading_work</t>
         </is>
       </c>
     </row>
@@ -7346,7 +7370,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Вентканал CVENT 26х26 (канал + вентблок-спутник)</t>
+          <t>Вентиляционный канал одноходовой VENT 20/25, 0.33 пм</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -7358,7 +7382,7 @@
         <v>1</v>
       </c>
       <c r="E216" t="n">
-        <v>2663.2</v>
+        <v>268.4</v>
       </c>
       <c r="F216" t="inlineStr">
         <is>
@@ -7367,50 +7391,126 @@
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>Добавлено 2026-08-06: было два кандидата на листе 'Блокпаротермшидель (Алексей)' прайса Елены - строка 33 'Вентблок CVENT 26*26 со спутником, 0.327' = 961.2 руб./шт и строка 34 'Вентиляционный канал Schiedel CVENT 500Х360Х327 26Х26' = 1702 руб./шт. Пользователь подтвердила 2026-08-06: это не два кандидата на один и тот же продукт, а два РАЗНЫХ компонента одного полного CVENT-узла (канал-модуль + его блок-спутник той же глубины 327мм) - берутся оба, цена = сумма 961.2 + 1702 = 2663.2 руб./шт. Калькулятор (CHANNEL_TYPE_SPECS['cvent'] в schiedel_vent_channels_calculator/calculator.py) хранит только ОДНУ цену на product_type=cvent, как и для 1x/2x/3x/4x - поэтому сумма зашита здесь одним числом, а не как два отдельных price_code; calculator.py не менялся. CVENT остаётся редкой строкой (Elena 2026-07-30: 'бывает достаточно редко'), ни один реальный проект её пока не использовал.</t>
+          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 27. h=330мм, габариты 200х250мм, вес 13кг, 63 шт на поддоне.</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>schiedel_vent_channel_cvent_item</t>
+          <t>schiedel_vent_channel_1x_item</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Вентиляционный канал четырехходовой VENT 36/50, 0.33 пм</t>
+        </is>
+      </c>
+      <c r="C217" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D217" t="n">
+        <v>1</v>
+      </c>
+      <c r="E217" t="n">
+        <v>902.8</v>
+      </c>
+      <c r="F217" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-06: лист 'Блокпаротермшидель (Алексей)' прайса Елены, строка 30. h=330мм, габариты 500х360мм, вес 38кг, 16 шт на поддоне.</t>
+        </is>
+      </c>
+      <c r="H217" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_4x_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>Schiedel</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>Вентканал CVENT 26х26 (канал + вентблок-спутник)</t>
+        </is>
+      </c>
+      <c r="C218" t="inlineStr">
+        <is>
+          <t>шт</t>
+        </is>
+      </c>
+      <c r="D218" t="n">
+        <v>1</v>
+      </c>
+      <c r="E218" t="n">
+        <v>2663.2</v>
+      </c>
+      <c r="F218" t="inlineStr">
+        <is>
+          <t>2026-08-08</t>
+        </is>
+      </c>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-06: было два кандидата на листе 'Блокпаротермшидель (Алексей)' прайса Елены - строка 33 'Вентблок CVENT 26*26 со спутником, 0.327' = 961.2 руб./шт и строка 34 'Вентиляционный канал Schiedel CVENT 500Х360Х327 26Х26' = 1702 руб./шт. Пользователь подтвердила 2026-08-06: это не два кандидата на один и тот же продукт, а два РАЗНЫХ компонента одного полного CVENT-узла (канал-модуль + его блок-спутник той же глубины 327мм) - берутся оба, цена = сумма 961.2 + 1702 = 2663.2 руб./шт. Калькулятор (CHANNEL_TYPE_SPECS['cvent'] в schiedel_vent_channels_calculator/calculator.py) хранит только ОДНУ цену на product_type=cvent, как и для 1x/2x/3x/4x - поэтому сумма зашита здесь одним числом, а не как два отдельных price_code; calculator.py не менялся. CVENT остаётся редкой строкой (Elena 2026-07-30: 'бывает достаточно редко'), ни один реальный проект её пока не использовал.</t>
+        </is>
+      </c>
+      <c r="H218" t="inlineStr">
+        <is>
+          <t>schiedel_vent_channel_cvent_item</t>
+        </is>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
           <t>Работы</t>
         </is>
       </c>
-      <c r="B217" t="inlineStr">
+      <c r="B219" t="inlineStr">
         <is>
           <t>Доставка вентканалов/ разгрузка в ручную на объекте</t>
         </is>
       </c>
-      <c r="C217" t="inlineStr">
+      <c r="C219" t="inlineStr">
         <is>
           <t>маш</t>
         </is>
       </c>
-      <c r="D217" t="n">
-        <v>1</v>
-      </c>
-      <c r="E217" t="inlineStr">
+      <c r="D219" t="n">
+        <v>1</v>
+      </c>
+      <c r="E219" t="inlineStr">
         <is>
           <t>2 500</t>
         </is>
       </c>
-      <c r="F217" t="inlineStr">
+      <c r="F219" t="inlineStr">
         <is>
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="G217" t="inlineStr">
+      <c r="G219" t="inlineStr">
         <is>
           <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
-      <c r="H217" t="inlineStr"/>
+      <c r="H219" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -3914,7 +3914,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Утепление стен ЭППС 50мм, работа (ВРЕМЕННО 0 - ждет ответа Елены)</t>
+          <t>Утепление стен ЭППС 50мм, работа</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3926,7 +3926,7 @@
         <v>1</v>
       </c>
       <c r="E113" t="n">
-        <v>0</v>
+        <v>500</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
@@ -3935,7 +3935,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>ВРЕМЕННОЕ РЕШЕНИЕ 2026-08-06, требует уточнения у Елены: в смете ТРЦ утепление стен 50мм+100мм считается ОДНОЙ работой (680 руб./м2 на оба слоя сразу, лист 'НС 29.06.26' строка 73), а не двумя отдельными монтажными работами как в наших калькуляторах. АРК и ЮСВ вообще не имеют слоя 50мм на стенах (только 100мм), сверить не с чем. Поставлено 0, чтобы не задвоить деньги поверх уже существующей (возможно тоже неточной - см. eps_wall_insulation_work_m2) цены на монтаж 100мм-слоя. НЕ ИСПОЛЬЗОВАТЬ КАК ОКОНЧАТЕЛЬНОЕ ЗНАЧЕНИЕ - заменить, когда Елена ответит на вопрос от 2026-08-06 (один проход маляра на оба слоя или два отдельных).</t>
+          <t>ИСПРАВЛЕНО 2026-08-08 (ответ Елены на вопрос от 2026-08-06): это не 'один проход на оба слоя' - работа утепления не зависит от толщины плиты ЭППС, ставка за м2 одинаковая что для 50мм, что для 100мм слоя (это разные площади/конструкции, не два слоя друг на друге). Раньше стояло 0 из опасения задвоить деньги поверх ставки 100мм-слоя - опасение снято, задвоения нет, т.к. 50мм и 100мм всегда считаются по СВОИМ отдельным площадям. Ставка = eps_wall_insulation_work_m2 (500 руб./м2).</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H219"/>
+  <dimension ref="A1:H221"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,6 @@
           <t>Источник: первый лист нового прайса, строка 3. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -546,7 +545,6 @@
           <t>Источник: первый лист нового прайса, строка 4. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -7510,7 +7508,82 @@
           <t>Источник: первый лист нового прайса, строка 42. Исходное кол-во: 1. price_code не найден автоматически: нужно сопоставить вручную.</t>
         </is>
       </c>
-      <c r="H219" t="inlineStr"/>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Гидроизоляция поверхности под первый ряд блоков, материал</t>
+        </is>
+      </c>
+      <c r="C220" t="inlineStr">
+        <is>
+          <t>м2</t>
+        </is>
+      </c>
+      <c r="D220" t="n">
+        <v>1</v>
+      </c>
+      <c r="E220" t="n">
+        <v>250</v>
+      </c>
+      <c r="F220" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-09: material_unit_price ошибочно делил один registry_code с work_unit_price (cutoff_waterproofing_under_blocks_m2=100), из-за чего материал был занижен. Реальная цена материала подтверждена на ТРЦ и АРК (оба проекта: мат=250, работа=100, серый/реальный столбец) - см. отчёт 04_load_bearing_walls_lintels.md.</t>
+        </is>
+      </c>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>cutoff_waterproofing_material_m2</t>
+        </is>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Технический надзор (стены/перемычки)</t>
+        </is>
+      </c>
+      <c r="C221" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D221" t="n">
+        <v>1</v>
+      </c>
+      <c r="E221" t="n">
+        <v>10000</v>
+      </c>
+      <c r="F221" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-09: technical_supervision_amount ошибочно делил один registry_code (technical_supervision_fixed=5000) со строкой из раздела плиты фундамента. Реальная цена для раздела стен/перемычек подтверждена на ТРЦ (серый/реальный столбец) = 10000 - см. отчёт 04_load_bearing_walls_lintels.md.</t>
+        </is>
+      </c>
+      <c r="H221" t="inlineStr">
+        <is>
+          <t>technical_supervision_walls_lintels</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/output/price_registry_filled_v4.xlsx
+++ b/output/price_registry_filled_v4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H221"/>
+  <dimension ref="A1:H222"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7585,6 +7585,44 @@
         </is>
       </c>
     </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>Работы</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Бетонирование балки бетоном марки В22,5 (М300) (высотой более 250мм)</t>
+        </is>
+      </c>
+      <c r="C222" t="inlineStr">
+        <is>
+          <t>м3</t>
+        </is>
+      </c>
+      <c r="D222" t="n">
+        <v>1</v>
+      </c>
+      <c r="E222" t="n">
+        <v>25000</v>
+      </c>
+      <c r="F222" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>Добавлено 2026-08-09: строка 29 первого листа нового прайса Елены существовала, но никогда не была сопоставлена ни с одним price_code (калькулятор её не запрашивал - до 2026-07-28 было решено считать все балки одной ставкой по длине, без деления по высоте). Реальные ТРЦ и АРК смет обе делят балки по высоте с разными ставками и единицами (мп/м3) - см. reports/trc_vs_original_comparison/05_floor_slab_1.md. Подтверждено 2026-08-09.</t>
+        </is>
+      </c>
+      <c r="H222" t="inlineStr">
+        <is>
+          <t>beam_concrete_placing_work_m3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
